--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="99">
-  <si>
-    <t>מעקב מחירי סופרמרקט - 2026-09-12</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="88">
+  <si>
+    <t>מעקב מחירי סופרמרקט - 2026-09-13</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -97,7 +97,10 @@
     <t>ביצים L (מנורמל ל-12 יח')</t>
   </si>
   <si>
-    <t>15.6%</t>
+    <t>8.2%</t>
+  </si>
+  <si>
+    <t>⬇ -1.24 ₪</t>
   </si>
   <si>
     <t>קוקה קולה זירו 1.5 ליטר</t>
@@ -115,9 +118,6 @@
     <t>יין סגל אדום יבש 750 מ"ל</t>
   </si>
   <si>
-    <t>22.50 (2 ב-45)</t>
-  </si>
-  <si>
     <t>20.1%</t>
   </si>
   <si>
@@ -127,9 +127,6 @@
     <t>37.50 (2 ב-75)</t>
   </si>
   <si>
-    <t>40.00 (2 ב-80)</t>
-  </si>
-  <si>
     <t>6.5%</t>
   </si>
   <si>
@@ -139,24 +136,15 @@
     <t>9.00 (2 ב-18)</t>
   </si>
   <si>
-    <t>11.00 (2 ב-22)</t>
-  </si>
-  <si>
     <t>חמאת בוטנים טבעית בטר אנד דיפרנט 350 גרם</t>
   </si>
   <si>
-    <t>15.90</t>
-  </si>
-  <si>
     <t>17.8%</t>
   </si>
   <si>
     <t>ספגטי אסם 500 גרם</t>
   </si>
   <si>
-    <t>6.00 (4 ב-24)</t>
-  </si>
-  <si>
     <t>38.0%</t>
   </si>
   <si>
@@ -166,108 +154,87 @@
     <t>6.50 (2 ב-13)</t>
   </si>
   <si>
-    <t>7.50 (2 ב-15)</t>
-  </si>
-  <si>
     <t>20.2%</t>
   </si>
   <si>
     <t>דבש טבעי עמק חפר 350 גרם</t>
   </si>
   <si>
+    <t>47.3%</t>
+  </si>
+  <si>
+    <t>רביולי גבינה קלאסי שטראוס 400 גרם</t>
+  </si>
+  <si>
+    <t>17.5%</t>
+  </si>
+  <si>
+    <t>ניקיון וטואלטיקה</t>
+  </si>
+  <si>
+    <t>מגבות נייר ניקול 6 גלילים</t>
+  </si>
+  <si>
+    <t>21.6%</t>
+  </si>
+  <si>
+    <t>נייר טואלט לילי פסטל 32 גלילים</t>
+  </si>
+  <si>
+    <t>9.1%</t>
+  </si>
+  <si>
+    <t>אקונומיקה סנו גאוול 4 ליטר</t>
+  </si>
+  <si>
+    <t>11.2%</t>
+  </si>
+  <si>
+    <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
+  </si>
+  <si>
+    <t>12.00 (2 ב-24)</t>
+  </si>
+  <si>
+    <t>5.5%</t>
+  </si>
+  <si>
+    <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
+  </si>
+  <si>
+    <t>9.90</t>
+  </si>
+  <si>
+    <t>21.7%</t>
+  </si>
+  <si>
+    <t>מגבוני האגיס ללא בישום 4X56</t>
+  </si>
+  <si>
+    <t>15.00 (2 ב-30)</t>
+  </si>
+  <si>
+    <t>20.9%</t>
+  </si>
+  <si>
+    <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
+  </si>
+  <si>
     <t>14.90</t>
   </si>
   <si>
-    <t>47.3%</t>
-  </si>
-  <si>
-    <t>רביולי גבינה קלאסי שטראוס 400 גרם</t>
-  </si>
-  <si>
-    <t>15.00 (2 ב-30)</t>
-  </si>
-  <si>
-    <t>18.00 (2 ב-36)</t>
-  </si>
-  <si>
-    <t>17.5%</t>
-  </si>
-  <si>
-    <t>ניקיון וטואלטיקה</t>
-  </si>
-  <si>
-    <t>מגבות נייר ניקול 6 גלילים</t>
-  </si>
-  <si>
-    <t>21.6%</t>
-  </si>
-  <si>
-    <t>נייר טואלט לילי פסטל 32 גלילים</t>
-  </si>
-  <si>
-    <t>9.1%</t>
-  </si>
-  <si>
-    <t>אקונומיקה סנו גאוול 4 ליטר</t>
-  </si>
-  <si>
-    <t>11.2%</t>
-  </si>
-  <si>
-    <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
-  </si>
-  <si>
-    <t>12.00 (2 ב-24)</t>
-  </si>
-  <si>
-    <t>5.5%</t>
-  </si>
-  <si>
-    <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
-  </si>
-  <si>
-    <t>7.40</t>
-  </si>
-  <si>
-    <t>16.90</t>
-  </si>
-  <si>
-    <t>21.7%</t>
-  </si>
-  <si>
-    <t>מגבוני האגיס ללא בישום 4X56</t>
-  </si>
-  <si>
-    <t>20.9%</t>
-  </si>
-  <si>
-    <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
-  </si>
-  <si>
-    <t>22.00 (2 ב-44)</t>
-  </si>
-  <si>
     <t>18.6%</t>
   </si>
   <si>
     <t>שמפו פנטן משקם 600 מ"ל</t>
   </si>
   <si>
-    <t>19.90</t>
-  </si>
-  <si>
     <t>34.8%</t>
   </si>
   <si>
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
-    <t>29.90</t>
-  </si>
-  <si>
-    <t>36.67 (3 ב-110)</t>
-  </si>
-  <si>
     <t>15.1%</t>
   </si>
   <si>
@@ -304,10 +271,10 @@
     <t/>
   </si>
   <si>
-    <t>17.9%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-12 מול 2026-09-11 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>17.7%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-13 מול 2026-09-12 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -339,7 +306,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -378,6 +345,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -394,16 +366,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -423,12 +395,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -784,7 +760,8 @@
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="10" width="20" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1032,13 +1009,13 @@
         <v>13</v>
       </c>
       <c r="D10" s="7">
-        <v>15.48</v>
+        <v>14.24</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="8">
-        <v>2.41</v>
+        <v>1.17</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>28</v>
@@ -1049,13 +1026,13 @@
       <c r="I10" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="9" t="s">
-        <v>16</v>
+      <c r="J10" s="11" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="5">
         <v>8.2</v>
@@ -1073,7 +1050,7 @@
         <v>1.3</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>15</v>
@@ -1087,7 +1064,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="5">
         <v>9.9</v>
@@ -1105,7 +1082,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>15</v>
@@ -1119,7 +1096,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="5">
         <v>19.9</v>
@@ -1130,8 +1107,8 @@
       <c r="D13" s="7">
         <v>24.9</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>34</v>
+      <c r="E13" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F13" s="8">
         <v>5</v>
@@ -1162,14 +1139,14 @@
       <c r="D14" s="7">
         <v>45.9</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>38</v>
+      <c r="E14" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F14" s="8">
         <v>3</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>15</v>
@@ -1183,19 +1160,19 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="5">
         <v>11.9</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" s="7">
         <v>14.9</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>42</v>
+      <c r="E15" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F15" s="8">
         <v>3</v>
@@ -1215,7 +1192,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" s="5">
         <v>13.9</v>
@@ -1226,14 +1203,14 @@
       <c r="D16" s="7">
         <v>16.9</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>44</v>
+      <c r="E16" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F16" s="8">
         <v>3</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>15</v>
@@ -1247,7 +1224,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B17" s="5">
         <v>4.9</v>
@@ -1258,14 +1235,14 @@
       <c r="D17" s="7">
         <v>7.9</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>47</v>
+      <c r="E17" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F17" s="8">
         <v>3</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>15</v>
@@ -1279,25 +1256,25 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B18" s="5">
         <v>7.9</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D18" s="7">
         <v>9.9</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>51</v>
+      <c r="E18" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F18" s="8">
         <v>2</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>15</v>
@@ -1311,7 +1288,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B19" s="5">
         <v>8.9</v>
@@ -1322,14 +1299,14 @@
       <c r="D19" s="7">
         <v>16.9</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>54</v>
+      <c r="E19" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F19" s="8">
         <v>8</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>15</v>
@@ -1343,25 +1320,25 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B20" s="5">
         <v>18.9</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>57</v>
+      <c r="C20" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="D20" s="7">
         <v>22.9</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>58</v>
+      <c r="E20" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F20" s="8">
         <v>4</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>15</v>
@@ -1375,7 +1352,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1389,7 +1366,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B22" s="5">
         <v>10.9</v>
@@ -1407,7 +1384,7 @@
         <v>3</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>15</v>
@@ -1421,7 +1398,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B23" s="5">
         <v>39.9</v>
@@ -1439,7 +1416,7 @@
         <v>4</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>15</v>
@@ -1453,7 +1430,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B24" s="5">
         <v>15.9</v>
@@ -1471,7 +1448,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>15</v>
@@ -1485,13 +1462,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B25" s="5">
         <v>18.8</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D25" s="7">
         <v>19.9</v>
@@ -1503,7 +1480,7 @@
         <v>1.1</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>15</v>
@@ -1517,25 +1494,25 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B26" s="5">
         <v>14.8</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D26" s="7">
         <v>18.9</v>
       </c>
-      <c r="E26" s="10" t="s">
-        <v>72</v>
+      <c r="E26" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F26" s="8">
         <v>4.1</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>15</v>
@@ -1549,13 +1526,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B27" s="5">
         <v>19.7</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D27" s="7">
         <v>24.9</v>
@@ -1567,7 +1544,7 @@
         <v>5.2</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>15</v>
@@ -1581,25 +1558,25 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B28" s="5">
         <v>21.9</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="D28" s="7">
         <v>26.9</v>
       </c>
-      <c r="E28" s="10" t="s">
-        <v>77</v>
+      <c r="E28" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F28" s="8">
         <v>5</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>15</v>
@@ -1613,13 +1590,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B29" s="5">
         <v>14.94</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>80</v>
+      <c r="C29" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="D29" s="7">
         <v>22.9</v>
@@ -1631,7 +1608,7 @@
         <v>7.96</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>15</v>
@@ -1645,25 +1622,25 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B30" s="5">
         <v>41.5</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>83</v>
+      <c r="C30" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="D30" s="7">
         <v>48.9</v>
       </c>
-      <c r="E30" s="10" t="s">
-        <v>84</v>
+      <c r="E30" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F30" s="8">
         <v>7.4</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>15</v>
@@ -1677,7 +1654,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1691,7 +1668,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B32" s="5">
         <v>15.9</v>
@@ -1723,7 +1700,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B33" s="5">
         <v>4.9</v>
@@ -1741,7 +1718,7 @@
         <v>4</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>15</v>
@@ -1755,7 +1732,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B34" s="5">
         <v>4.9</v>
@@ -1773,7 +1750,7 @@
         <v>4</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>15</v>
@@ -1787,7 +1764,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B35" s="5">
         <v>9.9</v>
@@ -1805,7 +1782,7 @@
         <v>3</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>15</v>
@@ -1819,7 +1796,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B36" s="5">
         <v>4.9</v>
@@ -1837,7 +1814,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>15</v>
@@ -1850,50 +1827,50 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B37" s="12">
+      <c r="A37" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="13">
         <v>488.61</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D37" s="12">
-        <v>595.13</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="F37" s="12">
-        <v>106.52</v>
-      </c>
-      <c r="G37" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="H37" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="J37" s="13" t="s">
-        <v>96</v>
+      <c r="C37" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="13">
+        <v>593.89</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F37" s="13">
+        <v>105.28</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
+      <c r="A38" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="99">
   <si>
     <t>מוצר</t>
   </si>
@@ -52,6 +52,9 @@
     <t>—</t>
   </si>
   <si>
+    <t>2%</t>
+  </si>
+  <si>
     <t>אושר עד</t>
   </si>
   <si>
@@ -61,9 +64,15 @@
     <t>קוטג' תנובה 5% 250 גרם</t>
   </si>
   <si>
+    <t>7.8%</t>
+  </si>
+  <si>
     <t>גבינה צהובה 9% פרוסות 200 גרם</t>
   </si>
   <si>
+    <t>6.7%</t>
+  </si>
+  <si>
     <t>מאכל ושתיה סגורים</t>
   </si>
   <si>
@@ -73,24 +82,42 @@
     <t>23.00 (2 ב-46)</t>
   </si>
   <si>
+    <t>22.3%</t>
+  </si>
+  <si>
     <t>קפה נמס טסטרס צויס 200 גרם</t>
   </si>
   <si>
+    <t>10%</t>
+  </si>
+  <si>
     <t>ביצים L (מנורמל ל-12 יח')</t>
   </si>
   <si>
+    <t>8.2%</t>
+  </si>
+  <si>
     <t>קוקה קולה זירו 1.5 ליטר</t>
   </si>
   <si>
+    <t>13.7%</t>
+  </si>
+  <si>
     <t>סירופ יכין פטל דיאט 1 ליטר</t>
   </si>
   <si>
+    <t>28.8%</t>
+  </si>
+  <si>
     <t>יין סגל אדום יבש 750 מ"ל</t>
   </si>
   <si>
     <t>22.50 (2 ב-45)</t>
   </si>
   <si>
+    <t>20.1%</t>
+  </si>
+  <si>
     <t>יין טפרברג מוסקטו לבן 750 מ"ל</t>
   </si>
   <si>
@@ -100,6 +127,9 @@
     <t>40.00 (2 ב-80)</t>
   </si>
   <si>
+    <t>6.5%</t>
+  </si>
+  <si>
     <t>שיבולת שועל קוואקר 500 גרם</t>
   </si>
   <si>
@@ -115,12 +145,18 @@
     <t>15.90</t>
   </si>
   <si>
+    <t>17.8%</t>
+  </si>
+  <si>
     <t>ספגטי אסם 500 גרם</t>
   </si>
   <si>
     <t>6.00 (4 ב-24)</t>
   </si>
   <si>
+    <t>38%</t>
+  </si>
+  <si>
     <t>פסטה פנה ריגטה ברילה 500 גרם</t>
   </si>
   <si>
@@ -130,36 +166,57 @@
     <t>7.50 (2 ב-15)</t>
   </si>
   <si>
+    <t>20.2%</t>
+  </si>
+  <si>
     <t>דבש טבעי עמק חפר 350 גרם</t>
   </si>
   <si>
     <t>14.90</t>
   </si>
   <si>
+    <t>47.3%</t>
+  </si>
+  <si>
     <t>רביולי גבינה קלאסי שטראוס 400 גרם</t>
   </si>
   <si>
     <t>18.00 (2 ב-36)</t>
   </si>
   <si>
+    <t>17.5%</t>
+  </si>
+  <si>
     <t>ניקיון וטואלטיקה</t>
   </si>
   <si>
     <t>מגבות נייר ניקול 6 גלילים</t>
   </si>
   <si>
+    <t>21.6%</t>
+  </si>
+  <si>
     <t>נייר טואלט לילי פסטל 32 גלילים</t>
   </si>
   <si>
+    <t>9.1%</t>
+  </si>
+  <si>
     <t>אקונומיקה סנו גאוול 4 ליטר</t>
   </si>
   <si>
+    <t>11.2%</t>
+  </si>
+  <si>
     <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
   </si>
   <si>
     <t>12.00 (2 ב-24)</t>
   </si>
   <si>
+    <t>5.5%</t>
+  </si>
+  <si>
     <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
   </si>
   <si>
@@ -169,6 +226,9 @@
     <t>16.90</t>
   </si>
   <si>
+    <t>21.7%</t>
+  </si>
+  <si>
     <t>מגבוני האגיס ללא בישום 4X56</t>
   </si>
   <si>
@@ -178,21 +238,36 @@
     <t>16.67 (3 ב-50)</t>
   </si>
   <si>
+    <t>20.9%</t>
+  </si>
+  <si>
     <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
   </si>
   <si>
     <t>22.00 (2 ב-44)</t>
   </si>
   <si>
+    <t>18.6%</t>
+  </si>
+  <si>
     <t>שמפו פנטן משקם 600 מ"ל</t>
   </si>
   <si>
+    <t>34.8%</t>
+  </si>
+  <si>
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
+    <t>31.90</t>
+  </si>
+  <si>
     <t>33.33 (3 ב-100)</t>
   </si>
   <si>
+    <t>15.1%</t>
+  </si>
+  <si>
     <t>פירות וירקות</t>
   </si>
   <si>
@@ -202,31 +277,43 @@
     <t>עגבניה (ק"ג)</t>
   </si>
   <si>
+    <t>22.5%</t>
+  </si>
+  <si>
+    <t>⬆ +2.00 ₪</t>
+  </si>
+  <si>
     <t>מלפפון (ק"ג)</t>
   </si>
   <si>
     <t>בננות (ק"ג)</t>
   </si>
   <si>
+    <t>23.3%</t>
+  </si>
+  <si>
     <t>בצל יבש (ק"ג)</t>
   </si>
   <si>
+    <t>16.9%</t>
+  </si>
+  <si>
     <t>סה"כ</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-14 מול 2026-09-13 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>17.1%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-15 מול 2026-09-14 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
@@ -247,7 +334,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -286,6 +373,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -302,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -311,43 +403,27 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -692,13 +768,13 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="10" width="22" customWidth="1"/>
+    <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -748,104 +824,104 @@
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>7.2</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>7.35</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="3">
         <v>0.15</v>
       </c>
-      <c r="G3" s="8">
-        <v>0.02</v>
+      <c r="G3" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="5">
+      <c r="A4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="4">
         <v>5.9</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>6.4</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="3">
         <v>0.5</v>
       </c>
-      <c r="G4" s="8">
-        <v>0.078</v>
+      <c r="G4" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="5">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4">
         <v>19.5</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>20.9</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="3">
         <v>1.4</v>
       </c>
-      <c r="G5" s="8">
-        <v>0.067</v>
+      <c r="G5" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -858,424 +934,424 @@
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="5">
+      <c r="A7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="4">
         <v>20.9</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>26.9</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="E7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="3">
         <v>6</v>
       </c>
-      <c r="G7" s="8">
-        <v>0.223</v>
+      <c r="G7" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="5">
+      <c r="A8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="4">
         <v>35.9</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>39.9</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="3">
         <v>4</v>
       </c>
-      <c r="G8" s="8">
-        <v>0.1</v>
+      <c r="G8" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="5">
+      <c r="A9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="4">
         <v>13.07</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>14.24</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="3">
         <v>1.17</v>
       </c>
-      <c r="G9" s="8">
-        <v>0.08199999999999999</v>
+      <c r="G9" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="5">
+      <c r="A10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="4">
         <v>8.2</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>9.5</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="3">
         <v>1.3</v>
       </c>
-      <c r="G10" s="8">
-        <v>0.13699999999999998</v>
+      <c r="G10" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="5">
+      <c r="A11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="4">
         <v>9.9</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>13.9</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="3">
         <v>4</v>
       </c>
-      <c r="G11" s="8">
-        <v>0.28800000000000003</v>
+      <c r="G11" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="5">
+      <c r="A12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="4">
         <v>19.9</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>24.9</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="E12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="3">
         <v>5</v>
       </c>
-      <c r="G12" s="8">
-        <v>0.201</v>
+      <c r="G12" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="5">
+      <c r="A13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="4">
         <v>42.9</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="5">
         <v>45.9</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="E13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="3">
         <v>3</v>
       </c>
-      <c r="G13" s="8">
-        <v>0.065</v>
+      <c r="G13" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="5">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="4">
         <v>11.9</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="5">
         <v>14.9</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="7">
+      <c r="E14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="3">
         <v>3</v>
       </c>
-      <c r="G14" s="8">
-        <v>0.201</v>
+      <c r="G14" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="5">
+      <c r="A15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="4">
         <v>13.9</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>16.9</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="7">
+      <c r="E15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="3">
         <v>3</v>
       </c>
-      <c r="G15" s="8">
-        <v>0.17800000000000002</v>
+      <c r="G15" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="5">
+      <c r="A16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="4">
         <v>4.9</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <v>7.9</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" s="7">
+      <c r="E16" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="3">
         <v>3</v>
       </c>
-      <c r="G16" s="8">
-        <v>0.38</v>
+      <c r="G16" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="5">
+      <c r="A17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="4">
         <v>7.9</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="5">
         <v>9.9</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="7">
+      <c r="E17" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="3">
         <v>2</v>
       </c>
-      <c r="G17" s="8">
-        <v>0.20199999999999999</v>
+      <c r="G17" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="5">
+      <c r="A18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="4">
         <v>8.9</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <v>16.9</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="7">
+      <c r="E18" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="3">
         <v>8</v>
       </c>
-      <c r="G18" s="8">
-        <v>0.473</v>
+      <c r="G18" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="5">
+      <c r="A19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="4">
         <v>18.9</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>22.9</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" s="7">
+      <c r="E19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="3">
         <v>4</v>
       </c>
-      <c r="G19" s="8">
-        <v>0.175</v>
+      <c r="G19" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1288,296 +1364,296 @@
       <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="5">
+      <c r="A21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="4">
         <v>10.9</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="5">
         <v>13.9</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="3">
         <v>3</v>
       </c>
-      <c r="G21" s="8">
-        <v>0.21600000000000003</v>
+      <c r="G21" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="5">
+      <c r="A22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="4">
         <v>39.9</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="5">
         <v>43.9</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="3">
         <v>4</v>
       </c>
-      <c r="G22" s="8">
-        <v>0.091</v>
+      <c r="G22" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="5">
+      <c r="A23" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="4">
         <v>15.9</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="5">
         <v>17.9</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="3">
         <v>2</v>
       </c>
-      <c r="G23" s="8">
-        <v>0.11199999999999999</v>
+      <c r="G23" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="5">
+      <c r="A24" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="4">
         <v>18.8</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="5">
         <v>19.9</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="3">
         <v>1.1</v>
       </c>
-      <c r="G24" s="8">
-        <v>0.055</v>
+      <c r="G24" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="5">
+      <c r="A25" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="4">
         <v>14.8</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="5">
         <v>18.9</v>
       </c>
-      <c r="E25" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" s="7">
+      <c r="E25" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="3">
         <v>4.1</v>
       </c>
-      <c r="G25" s="8">
-        <v>0.217</v>
+      <c r="G25" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="5">
+      <c r="A26" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="4">
         <v>19.7</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="5">
+        <v>24.9</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="4">
+        <v>21.9</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="6">
-        <v>24.9</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="7">
-        <v>5.2</v>
-      </c>
-      <c r="G26" s="8">
-        <v>0.209</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" s="5">
-        <v>21.9</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="D27" s="5">
         <v>26.9</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="3">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="4">
+        <v>14.94</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="5">
+        <v>22.9</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F27" s="7">
-        <v>5</v>
-      </c>
-      <c r="G27" s="8">
-        <v>0.18600000000000003</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B28" s="5">
-        <v>14.94</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="6">
-        <v>22.9</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F28" s="7">
+      <c r="F28" s="3">
         <v>7.96</v>
       </c>
-      <c r="G28" s="8">
-        <v>0.348</v>
+      <c r="G28" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="5">
+      <c r="A29" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="4">
         <v>41.5</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="5">
         <v>48.9</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F29" s="7">
+      <c r="E29" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F29" s="3">
         <v>7.4</v>
       </c>
-      <c r="G29" s="8">
-        <v>0.151</v>
+      <c r="G29" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1590,210 +1666,210 @@
       <c r="J30" s="2"/>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" s="5">
+      <c r="A31" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="4">
         <v>15.9</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="5">
         <v>19.9</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="3">
         <v>4</v>
       </c>
-      <c r="G31" s="8">
-        <v>0.201</v>
+      <c r="G31" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="5">
+      <c r="A32" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" s="4">
+        <v>6.9</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="5">
+        <v>8.9</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="3">
+        <v>2</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="4">
+        <v>6.9</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="5">
+        <v>8.9</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="3">
+        <v>2</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="4">
+        <v>9.9</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="5">
+        <v>12.9</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="3">
+        <v>3</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" s="4">
         <v>4.9</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="6">
-        <v>8.9</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="7">
-        <v>4</v>
-      </c>
-      <c r="G32" s="8">
-        <v>0.449</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" s="5">
-        <v>4.9</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="6">
-        <v>8.9</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="7">
-        <v>4</v>
-      </c>
-      <c r="G33" s="8">
-        <v>0.449</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B34" s="5">
-        <v>9.9</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="6">
-        <v>12.9</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="7">
-        <v>3</v>
-      </c>
-      <c r="G34" s="8">
-        <v>0.233</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B35" s="5">
-        <v>4.9</v>
-      </c>
       <c r="C35" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="5">
         <v>5.9</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="3">
         <v>1</v>
       </c>
-      <c r="G35" s="8">
-        <v>0.16899999999999998</v>
+      <c r="G35" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B36" s="12">
-        <v>488.61</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D36" s="12">
+      <c r="A36" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" s="10">
+        <v>492.61</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D36" s="10">
         <v>593.89</v>
       </c>
-      <c r="E36" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="F36" s="12">
-        <v>105.28</v>
-      </c>
-      <c r="G36" s="14">
-        <v>0.177</v>
-      </c>
-      <c r="H36" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I36" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="J36" s="13" t="s">
-        <v>67</v>
+      <c r="E36" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F36" s="9">
+        <v>101.28</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
+      <c r="A37" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="100">
   <si>
     <t>מוצר</t>
   </si>
@@ -181,6 +181,9 @@
     <t>רביולי גבינה קלאסי שטראוס 400 גרם</t>
   </si>
   <si>
+    <t>17.00 (2 ב-34)</t>
+  </si>
+  <si>
     <t>18.00 (2 ב-36)</t>
   </si>
   <si>
@@ -277,10 +280,10 @@
     <t>עגבניה (ק"ג)</t>
   </si>
   <si>
-    <t>22.5%</t>
-  </si>
-  <si>
-    <t>⬆ +2.00 ₪</t>
+    <t>33.7%</t>
+  </si>
+  <si>
+    <t>⬇ -1.00 ₪</t>
   </si>
   <si>
     <t>מלפפון (ק"ג)</t>
@@ -304,10 +307,10 @@
     <t/>
   </si>
   <si>
-    <t>17.1%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-15 מול 2026-09-14 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>17.4%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-16 מול 2026-09-15 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -373,7 +376,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -402,24 +405,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -823,29 +814,29 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>7.2</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="5">
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4">
         <v>7.35</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="3">
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="5">
         <v>0.15</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="6" t="s">
@@ -855,29 +846,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>5.9</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="5">
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4">
         <v>6.4</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="3">
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="5">
         <v>0.5</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -887,29 +878,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>19.5</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="4">
         <v>20.9</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="3">
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="5">
         <v>1.4</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="6" t="s">
@@ -933,29 +924,29 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>20.9</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="4">
         <v>26.9</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="5">
         <v>6</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="6" t="s">
@@ -965,29 +956,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>35.9</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="4">
         <v>39.9</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="5">
         <v>4</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="6" t="s">
@@ -997,29 +988,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>13.07</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="4">
         <v>14.24</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="5">
         <v>1.17</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="6" t="s">
@@ -1029,29 +1020,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>8.2</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="4">
         <v>9.5</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="5">
         <v>1.3</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" t="s">
         <v>14</v>
       </c>
       <c r="I10" s="6" t="s">
@@ -1061,29 +1052,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>9.9</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="4">
         <v>13.9</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="3">
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5">
         <v>4</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" t="s">
         <v>31</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="6" t="s">
@@ -1093,29 +1084,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>19.9</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="4">
         <v>24.9</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="5">
         <v>5</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" t="s">
         <v>14</v>
       </c>
       <c r="I12" s="6" t="s">
@@ -1125,29 +1116,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>42.9</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>45.9</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="5">
         <v>3</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" t="s">
         <v>14</v>
       </c>
       <c r="I13" s="6" t="s">
@@ -1157,29 +1148,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="3">
         <v>11.9</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>14.9</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="5">
         <v>3</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" t="s">
         <v>14</v>
       </c>
       <c r="I14" s="6" t="s">
@@ -1189,29 +1180,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="3">
         <v>13.9</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="4">
         <v>16.9</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="5">
         <v>3</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" t="s">
         <v>14</v>
       </c>
       <c r="I15" s="6" t="s">
@@ -1221,29 +1212,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="3">
         <v>4.9</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="4">
         <v>7.9</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="5">
         <v>3</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" t="s">
         <v>47</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" t="s">
         <v>14</v>
       </c>
       <c r="I16" s="6" t="s">
@@ -1253,29 +1244,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="3">
         <v>7.9</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <v>9.9</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="5">
         <v>2</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" t="s">
         <v>51</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="H17" t="s">
         <v>14</v>
       </c>
       <c r="I17" s="6" t="s">
@@ -1285,29 +1276,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="3">
         <v>8.9</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="4">
         <v>16.9</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="5">
         <v>8</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" t="s">
         <v>54</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" t="s">
         <v>14</v>
       </c>
       <c r="I18" s="6" t="s">
@@ -1317,29 +1308,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="3">
         <v>18.9</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="4">
         <v>22.9</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="3">
+        <v>57</v>
+      </c>
+      <c r="F19" s="5">
         <v>4</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H19" s="3" t="s">
+      <c r="G19" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" t="s">
         <v>14</v>
       </c>
       <c r="I19" s="6" t="s">
@@ -1351,7 +1342,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1363,29 +1354,29 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="4">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="3">
         <v>10.9</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="4">
         <v>13.9</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="5">
         <v>3</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H21" s="3" t="s">
+      <c r="G21" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" t="s">
         <v>14</v>
       </c>
       <c r="I21" s="6" t="s">
@@ -1395,29 +1386,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="4">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="3">
         <v>39.9</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="4">
         <v>43.9</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="5">
         <v>4</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H22" s="3" t="s">
+      <c r="G22" t="s">
+        <v>63</v>
+      </c>
+      <c r="H22" t="s">
         <v>14</v>
       </c>
       <c r="I22" s="6" t="s">
@@ -1427,29 +1418,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="4">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" s="3">
         <v>15.9</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="4">
         <v>17.9</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="5">
         <v>2</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H23" s="3" t="s">
+      <c r="G23" t="s">
+        <v>65</v>
+      </c>
+      <c r="H23" t="s">
         <v>14</v>
       </c>
       <c r="I23" s="6" t="s">
@@ -1459,29 +1450,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="4">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="3">
         <v>18.8</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="5">
+        <v>67</v>
+      </c>
+      <c r="D24" s="4">
         <v>19.9</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="5">
         <v>1.1</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H24" s="3" t="s">
+      <c r="G24" t="s">
+        <v>68</v>
+      </c>
+      <c r="H24" t="s">
         <v>14</v>
       </c>
       <c r="I24" s="6" t="s">
@@ -1491,29 +1482,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="4">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="3">
         <v>14.8</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" s="5">
+        <v>70</v>
+      </c>
+      <c r="D25" s="4">
         <v>18.9</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F25" s="3">
+        <v>71</v>
+      </c>
+      <c r="F25" s="5">
         <v>4.1</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="H25" s="3" t="s">
+      <c r="G25" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25" t="s">
         <v>14</v>
       </c>
       <c r="I25" s="6" t="s">
@@ -1523,29 +1514,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B26" s="4">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="3">
         <v>19.7</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D26" s="5">
+        <v>74</v>
+      </c>
+      <c r="D26" s="4">
         <v>24.9</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26" s="3">
+        <v>75</v>
+      </c>
+      <c r="F26" s="5">
         <v>5.2</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="H26" s="3" t="s">
+      <c r="G26" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" t="s">
         <v>14</v>
       </c>
       <c r="I26" s="6" t="s">
@@ -1555,29 +1546,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" s="4">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" s="3">
         <v>21.9</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="4">
         <v>26.9</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F27" s="3">
+        <v>78</v>
+      </c>
+      <c r="F27" s="5">
         <v>5</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H27" s="3" t="s">
+      <c r="G27" t="s">
+        <v>79</v>
+      </c>
+      <c r="H27" t="s">
         <v>14</v>
       </c>
       <c r="I27" s="6" t="s">
@@ -1587,29 +1578,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" s="4">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="3">
         <v>14.94</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="4">
         <v>22.9</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F28" s="3">
+        <v>57</v>
+      </c>
+      <c r="F28" s="5">
         <v>7.96</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H28" s="3" t="s">
+      <c r="G28" t="s">
+        <v>81</v>
+      </c>
+      <c r="H28" t="s">
         <v>14</v>
       </c>
       <c r="I28" s="6" t="s">
@@ -1619,29 +1610,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B29" s="4">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="3">
         <v>41.5</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29" s="5">
+        <v>83</v>
+      </c>
+      <c r="D29" s="4">
         <v>48.9</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F29" s="3">
+        <v>84</v>
+      </c>
+      <c r="F29" s="5">
         <v>7.4</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H29" s="3" t="s">
+      <c r="G29" t="s">
+        <v>85</v>
+      </c>
+      <c r="H29" t="s">
         <v>14</v>
       </c>
       <c r="I29" s="6" t="s">
@@ -1653,7 +1644,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1665,29 +1656,29 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
     </row>
-    <row r="31" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B31" s="4">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="3">
         <v>15.9</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="4">
         <v>19.9</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="3">
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="5">
         <v>4</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" t="s">
         <v>34</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="H31" t="s">
         <v>14</v>
       </c>
       <c r="I31" s="6" t="s">
@@ -1697,93 +1688,93 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B32" s="4">
-        <v>6.9</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="5">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="3">
+        <v>5.9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="4">
         <v>8.9</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="3">
-        <v>2</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="H32" s="3" t="s">
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="5">
+        <v>3</v>
+      </c>
+      <c r="G32" t="s">
+        <v>89</v>
+      </c>
+      <c r="H32" t="s">
         <v>14</v>
       </c>
       <c r="I32" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="3">
+        <v>5.9</v>
+      </c>
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="4">
+        <v>8.9</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="5">
+        <v>3</v>
+      </c>
+      <c r="G33" t="s">
         <v>89</v>
       </c>
-      <c r="J32" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="H33" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B33" s="4">
-        <v>6.9</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="5">
-        <v>8.9</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="3">
-        <v>2</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>89</v>
-      </c>
       <c r="J33" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="4">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="3">
         <v>9.9</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="5">
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="4">
         <v>12.9</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="3">
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="5">
         <v>3</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H34" s="3" t="s">
+      <c r="G34" t="s">
+        <v>93</v>
+      </c>
+      <c r="H34" t="s">
         <v>14</v>
       </c>
       <c r="I34" s="6" t="s">
@@ -1793,29 +1784,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B35" s="4">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="3">
         <v>4.9</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="4">
         <v>5.9</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="5">
         <v>1</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H35" s="3" t="s">
+      <c r="G35" t="s">
+        <v>95</v>
+      </c>
+      <c r="H35" t="s">
         <v>14</v>
       </c>
       <c r="I35" s="6" t="s">
@@ -1827,39 +1818,39 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B36" s="10">
-        <v>492.61</v>
+        <v>490.61</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D36" s="10">
         <v>593.89</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F36" s="9">
-        <v>101.28</v>
+        <v>103.28</v>
       </c>
       <c r="G36" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="H36" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>96</v>
-      </c>
       <c r="J36" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="98">
   <si>
     <t>מוצר</t>
   </si>
@@ -52,7 +52,7 @@
     <t>—</t>
   </si>
   <si>
-    <t>2%</t>
+    <t>2.0%</t>
   </si>
   <si>
     <t>אושר עד</t>
@@ -88,7 +88,7 @@
     <t>קפה נמס טסטרס צויס 200 גרם</t>
   </si>
   <si>
-    <t>10%</t>
+    <t>10.0%</t>
   </si>
   <si>
     <t>ביצים L (מנורמל ל-12 יח')</t>
@@ -154,7 +154,7 @@
     <t>6.00 (4 ב-24)</t>
   </si>
   <si>
-    <t>38%</t>
+    <t>38.0%</t>
   </si>
   <si>
     <t>פסטה פנה ריגטה ברילה 500 גרם</t>
@@ -181,7 +181,7 @@
     <t>רביולי גבינה קלאסי שטראוס 400 גרם</t>
   </si>
   <si>
-    <t>17.00 (2 ב-34)</t>
+    <t>15.00 (2 ב-30)</t>
   </si>
   <si>
     <t>18.00 (2 ב-36)</t>
@@ -235,9 +235,6 @@
     <t>מגבוני האגיס ללא בישום 4X56</t>
   </si>
   <si>
-    <t>15.00 (2 ב-30)</t>
-  </si>
-  <si>
     <t>16.67 (3 ב-50)</t>
   </si>
   <si>
@@ -283,9 +280,6 @@
     <t>33.7%</t>
   </si>
   <si>
-    <t>⬇ -1.00 ₪</t>
-  </si>
-  <si>
     <t>מלפפון (ק"ג)</t>
   </si>
   <si>
@@ -310,7 +304,7 @@
     <t>17.4%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-16 מול 2026-09-15 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-17 מול 2026-09-16 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -337,7 +331,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -376,16 +370,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -393,28 +382,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -758,7 +782,7 @@
   <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -768,7 +792,7 @@
     <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -800,7 +824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -814,103 +838,103 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>7.2</v>
       </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="C3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="6">
         <v>7.35</v>
       </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="5">
+      <c r="E3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="7">
         <v>0.15</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="H3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>5.9</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="C4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6">
         <v>6.4</v>
       </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="E4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="7">
         <v>0.5</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="H4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>19.5</v>
       </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="C5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="6">
         <v>20.9</v>
       </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="E5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="7">
         <v>1.4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -924,423 +948,423 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>20.9</v>
       </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="C7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="6">
         <v>26.9</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="7">
         <v>6</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="H7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>35.9</v>
       </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="C8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="6">
         <v>39.9</v>
       </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="E8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="7">
         <v>4</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="H8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>13.07</v>
       </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="4">
+      <c r="C9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="6">
         <v>14.24</v>
       </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="E9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="7">
         <v>1.17</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="H9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>8.2</v>
       </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="C10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="6">
         <v>9.5</v>
       </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="5">
+      <c r="E10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="7">
         <v>1.3</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="H10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="4">
         <v>9.9</v>
       </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="4">
+      <c r="C11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="6">
         <v>13.9</v>
       </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="5">
+      <c r="E11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="7">
         <v>4</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="H11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>19.9</v>
       </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="C12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="6">
         <v>24.9</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="7">
         <v>5</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="H12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="4">
         <v>42.9</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="6">
         <v>45.9</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="7">
         <v>3</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="H13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="4">
         <v>11.9</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="6">
         <v>14.9</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="7">
         <v>3</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H14" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="H14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="4">
         <v>13.9</v>
       </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="4">
+      <c r="C15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="6">
         <v>16.9</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="7">
         <v>3</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H15" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="H15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="4">
         <v>4.9</v>
       </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="4">
+      <c r="C16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="6">
         <v>7.9</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="7">
         <v>3</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="H16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="4">
         <v>7.9</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="6">
         <v>9.9</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="7">
         <v>2</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H17" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="H17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="4">
         <v>8.9</v>
       </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="4">
+      <c r="C18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="6">
         <v>16.9</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="7">
         <v>8</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H18" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="H18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="4">
         <v>18.9</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="6">
         <v>22.9</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="7">
         <v>4</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H19" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>59</v>
       </c>
@@ -1354,297 +1378,297 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="21" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>10.9</v>
       </c>
-      <c r="C21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="4">
+      <c r="C21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="6">
         <v>13.9</v>
       </c>
-      <c r="E21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="5">
+      <c r="E21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="7">
         <v>3</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="H21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="H21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="4">
         <v>39.9</v>
       </c>
-      <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="4">
+      <c r="C22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="6">
         <v>43.9</v>
       </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="5">
+      <c r="E22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="7">
         <v>4</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="H22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="4">
         <v>15.9</v>
       </c>
-      <c r="C23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="4">
+      <c r="C23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="6">
         <v>17.9</v>
       </c>
-      <c r="E23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="5">
+      <c r="E23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="7">
         <v>2</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="H23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="4">
         <v>18.8</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="6">
         <v>19.9</v>
       </c>
-      <c r="E24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="5">
+      <c r="E24" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="7">
         <v>1.1</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="H24" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="H24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="4">
         <v>14.8</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="6">
         <v>18.9</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="7">
         <v>4.1</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H25" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="H25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="4">
         <v>19.7</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="6">
+        <v>24.9</v>
+      </c>
+      <c r="E26" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D26" s="4">
-        <v>24.9</v>
-      </c>
-      <c r="E26" s="7" t="s">
+      <c r="F26" s="7">
+        <v>5.2</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F26" s="5">
-        <v>5.2</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="H26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H26" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B27" s="4">
+        <v>21.9</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" s="6">
+        <v>26.9</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="3">
-        <v>21.9</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="4">
-        <v>26.9</v>
-      </c>
-      <c r="E27" s="7" t="s">
+      <c r="F27" s="7">
+        <v>5</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F27" s="5">
-        <v>5</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="H27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B28" s="4">
+        <v>14.94</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="6">
+        <v>22.9</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="7">
+        <v>7.96</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B28" s="3">
-        <v>14.94</v>
-      </c>
-      <c r="C28" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="4">
-        <v>22.9</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F28" s="5">
-        <v>7.96</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="H28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H28" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B29" s="4">
+        <v>41.5</v>
+      </c>
+      <c r="C29" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="3">
-        <v>41.5</v>
-      </c>
-      <c r="C29" s="7" t="s">
+      <c r="D29" s="6">
+        <v>48.9</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D29" s="4">
-        <v>48.9</v>
-      </c>
-      <c r="E29" s="7" t="s">
+      <c r="F29" s="7">
+        <v>7.4</v>
+      </c>
+      <c r="G29" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F29" s="5">
-        <v>7.4</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="H29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="H29" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1656,211 +1680,211 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="31" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="4">
+        <v>15.9</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="6">
+        <v>19.9</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="7">
+        <v>4</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B31" s="3">
-        <v>15.9</v>
-      </c>
-      <c r="C31" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" s="4">
-        <v>19.9</v>
-      </c>
-      <c r="E31" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="5">
-        <v>4</v>
-      </c>
-      <c r="G31" t="s">
-        <v>34</v>
-      </c>
-      <c r="H31" t="s">
-        <v>14</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B32" s="4">
+        <v>5.9</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="6">
+        <v>8.9</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="7">
+        <v>3</v>
+      </c>
+      <c r="G32" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B32" s="3">
+      <c r="H32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" s="4">
         <v>5.9</v>
       </c>
-      <c r="C32" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="4">
+      <c r="C33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="6">
         <v>8.9</v>
       </c>
-      <c r="E32" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="5">
+      <c r="E33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="7">
         <v>3</v>
       </c>
-      <c r="G32" t="s">
-        <v>89</v>
-      </c>
-      <c r="H32" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" s="8" t="s">
+      <c r="G33" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="J32" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B34" s="4">
+        <v>9.9</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="6">
+        <v>12.9</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="7">
+        <v>3</v>
+      </c>
+      <c r="G34" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="3">
+      <c r="H34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" s="4">
+        <v>4.9</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="6">
         <v>5.9</v>
       </c>
-      <c r="C33" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="4">
-        <v>8.9</v>
-      </c>
-      <c r="E33" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="5">
-        <v>3</v>
-      </c>
-      <c r="G33" t="s">
-        <v>89</v>
-      </c>
-      <c r="H33" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>92</v>
-      </c>
-      <c r="B34" s="3">
-        <v>9.9</v>
-      </c>
-      <c r="C34" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="4">
-        <v>12.9</v>
-      </c>
-      <c r="E34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="5">
-        <v>3</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="E35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="7">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="H34" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="H35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B35" s="3">
-        <v>4.9</v>
-      </c>
-      <c r="C35" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="4">
-        <v>5.9</v>
-      </c>
-      <c r="E35" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="5">
-        <v>1</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="B36" s="11">
+        <v>490.61</v>
+      </c>
+      <c r="C36" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="H35" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
+      <c r="D36" s="11">
+        <v>593.89</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F36" s="11">
+        <v>103.28</v>
+      </c>
+      <c r="G36" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B36" s="10">
-        <v>490.61</v>
-      </c>
-      <c r="C36" s="9" t="s">
+      <c r="H36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="10">
-        <v>593.89</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="F36" s="9">
-        <v>103.28</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="98">
+  <si>
+    <t>מעקב מחירים יומי — 2026-09-18</t>
+  </si>
   <si>
     <t>מוצר</t>
   </si>
@@ -223,9 +226,6 @@
     <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
   </si>
   <si>
-    <t>9.90</t>
-  </si>
-  <si>
     <t>16.90</t>
   </si>
   <si>
@@ -259,9 +259,6 @@
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
-    <t>31.90</t>
-  </si>
-  <si>
     <t>33.33 (3 ב-100)</t>
   </si>
   <si>
@@ -274,6 +271,9 @@
     <t>תפוח עץ פינק ליידי 1 ק"ג</t>
   </si>
   <si>
+    <t>⬆ +1.00 ₪</t>
+  </si>
+  <si>
     <t>עגבניה (ק"ג)</t>
   </si>
   <si>
@@ -301,23 +301,28 @@
     <t/>
   </si>
   <si>
-    <t>17.4%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-17 מול 2026-09-16 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>17.2%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-18 מול 2026-09-17 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
     </font>
     <font>
       <b/>
@@ -331,7 +336,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -370,6 +375,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -401,24 +411,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -427,17 +440,22 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -779,1120 +797,1134 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="8" width="12" customWidth="1"/>
     <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" ht="32" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="5">
         <v>7.2</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="C4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="7">
         <v>7.35</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="E4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="8">
         <v>0.15</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="H4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="5">
         <v>5.9</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="C5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="7">
         <v>6.4</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="E5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="8">
         <v>0.5</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="G5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="4">
+      <c r="H5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5">
         <v>19.5</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="7">
         <v>20.9</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="E6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="8">
         <v>1.4</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="G6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
         <v>20.9</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="7">
         <v>26.9</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="E8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="8">
         <v>6</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="G8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="4">
+      <c r="H8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="5">
         <v>35.9</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="7">
         <v>39.9</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="E9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="8">
         <v>4</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="G9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="4">
+      <c r="H9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="5">
         <v>13.07</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="7">
         <v>14.24</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="E10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="8">
         <v>1.17</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="G10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="4">
+      <c r="H10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5">
         <v>8.2</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="7">
         <v>9.5</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="E11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="8">
         <v>1.3</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="G11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="4">
+      <c r="H11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="5">
         <v>9.9</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="7">
         <v>13.9</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="E12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="8">
         <v>4</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="G12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="4">
+      <c r="H12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="5">
         <v>19.9</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="7">
         <v>24.9</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="E13" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="8">
         <v>5</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="G13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="4">
+      <c r="H13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="5">
         <v>42.9</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="7">
         <v>45.9</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="E14" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="8">
         <v>3</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="G14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="4">
+      <c r="H14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="5">
         <v>11.9</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C15" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="7">
         <v>14.9</v>
       </c>
-      <c r="E14" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="7">
+      <c r="E15" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="8">
         <v>3</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="4">
+      <c r="G15" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="5">
         <v>13.9</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="7">
         <v>16.9</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="7">
+      <c r="E16" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="8">
         <v>3</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="G16" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="4">
+      <c r="H16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="5">
         <v>4.9</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="7">
         <v>7.9</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="7">
+      <c r="E17" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="8">
         <v>3</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="G17" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="4">
+      <c r="H17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="5">
         <v>7.9</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C18" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="7">
         <v>9.9</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" s="7">
+      <c r="E18" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="8">
         <v>2</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="G18" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="4">
+      <c r="H18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="5">
         <v>8.9</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="7">
         <v>16.9</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="7">
+      <c r="E19" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="8">
         <v>8</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="G19" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="4">
+      <c r="H19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="5">
         <v>18.9</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C20" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="7">
         <v>22.9</v>
       </c>
-      <c r="E19" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="7">
+      <c r="E20" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="8">
         <v>4</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="G20" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="5">
         <v>10.9</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="7">
         <v>13.9</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="7">
+      <c r="E22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="8">
         <v>3</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="G22" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="4">
+      <c r="H22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="5">
         <v>39.9</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C23" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="7">
         <v>43.9</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="7">
+      <c r="E23" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="8">
         <v>4</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="G23" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="4">
+      <c r="H23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="5">
         <v>15.9</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="7">
         <v>17.9</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="7">
+      <c r="E24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="8">
         <v>2</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="G24" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="4">
+      <c r="H24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="5">
         <v>18.8</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C25" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="7">
         <v>19.9</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="7">
+      <c r="E25" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="8">
         <v>1.1</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="G25" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B25" s="4">
+      <c r="H25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="5">
         <v>14.8</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="7">
         <v>18.9</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E26" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F26" s="8">
         <v>4.1</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="G26" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="H25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="H26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B27" s="5">
         <v>19.7</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C27" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="7">
         <v>24.9</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E27" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F27" s="8">
         <v>5.2</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G27" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="H26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="H27" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B28" s="5">
         <v>21.9</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C28" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="7">
         <v>26.9</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E28" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F28" s="8">
         <v>5</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="G28" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="H27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="H28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B29" s="5">
         <v>14.94</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="7">
         <v>22.9</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F28" s="7">
+      <c r="E29" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="8">
         <v>7.96</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G29" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="H29" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B30" s="5">
         <v>41.5</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="7">
+        <v>48.9</v>
+      </c>
+      <c r="E30" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="6">
-        <v>48.9</v>
-      </c>
-      <c r="E29" s="9" t="s">
+      <c r="F30" s="8">
+        <v>7.4</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="F29" s="7">
-        <v>7.4</v>
-      </c>
-      <c r="G29" s="5" t="s">
+      <c r="H30" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-    </row>
-    <row r="31" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="B32" s="5">
+        <v>16.9</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="7">
+        <v>19.9</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="8">
+        <v>3</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="B31" s="4">
-        <v>15.9</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" s="6">
-        <v>19.9</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="7">
-        <v>4</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="J32" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B33" s="5">
         <v>5.9</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="7">
         <v>8.9</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="7">
+      <c r="E33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="8">
         <v>3</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G33" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="H32" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="H33" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B34" s="5">
         <v>5.9</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="6">
+      <c r="C34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="7">
         <v>8.9</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="7">
+      <c r="E34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="8">
         <v>3</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G34" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="H33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+      <c r="H34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B35" s="5">
         <v>9.9</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="6">
+      <c r="C35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="7">
         <v>12.9</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="7">
+      <c r="E35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="8">
         <v>3</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G35" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="H34" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="H35" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B36" s="5">
         <v>4.9</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="6">
+      <c r="C36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="7">
         <v>5.9</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="7">
+      <c r="E36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="8">
         <v>1</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="G36" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="H35" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
+      <c r="H36" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B36" s="11">
-        <v>490.61</v>
-      </c>
-      <c r="C36" s="12" t="s">
+      <c r="B37" s="13">
+        <v>491.61</v>
+      </c>
+      <c r="C37" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D37" s="13">
         <v>593.89</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E37" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="F36" s="11">
-        <v>103.28</v>
-      </c>
-      <c r="G36" s="12" t="s">
+      <c r="F37" s="13">
+        <v>102.28</v>
+      </c>
+      <c r="G37" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="H36" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="12" t="s">
+      <c r="H37" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="J36" s="12" t="s">
+      <c r="J37" s="14" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="37" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
+    <row r="38" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A37:J37"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A38:J38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="69">
   <si>
     <t>מוצר</t>
   </si>
@@ -175,9 +175,6 @@
     <t>מגבוני האגיס ללא בישום 4X56</t>
   </si>
   <si>
-    <t>16.67 (3 ב-50)</t>
-  </si>
-  <si>
     <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
   </si>
   <si>
@@ -193,7 +190,7 @@
     <t>31.90</t>
   </si>
   <si>
-    <t>33.33 (3 ב-100)</t>
+    <t>36.67 (3 ב-110)</t>
   </si>
   <si>
     <t>פירות וירקות</t>
@@ -205,9 +202,6 @@
     <t>עגבניה (ק"ג)</t>
   </si>
   <si>
-    <t>⬆ +1.00 ₪</t>
-  </si>
-  <si>
     <t>מלפפון (ק"ג)</t>
   </si>
   <si>
@@ -223,7 +217,7 @@
     <t/>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-20 מול 2026-09-19 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-21 מול 2026-09-20 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -253,7 +247,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -292,11 +286,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -313,7 +302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -321,17 +310,31 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -731,98 +734,98 @@
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>7.2</v>
       </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="C3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="6">
         <v>7.35</v>
       </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="5">
+      <c r="E3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="7">
         <v>0.15</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="8">
         <v>0.02</v>
       </c>
       <c r="H3" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="7" t="s">
+      <c r="I3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>5.9</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="C4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6">
         <v>6.4</v>
       </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="E4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="7">
         <v>0.5</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="8">
         <v>0.078</v>
       </c>
       <c r="H4" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="7" t="s">
+      <c r="I4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>19.5</v>
       </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="C5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="6">
         <v>20.9</v>
       </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="E5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="7">
         <v>1.4</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="8">
         <v>0.067</v>
       </c>
       <c r="H5" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="7" t="s">
+      <c r="I5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>14</v>
       </c>
     </row>
@@ -841,418 +844,418 @@
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>20.9</v>
       </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="C7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="6">
         <v>26.9</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="7">
         <v>6</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="8">
         <v>0.223</v>
       </c>
       <c r="H7" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" s="7" t="s">
+      <c r="I7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>35.9</v>
       </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="C8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="6">
         <v>39.9</v>
       </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="E8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="7">
         <v>4</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="8">
         <v>0.1</v>
       </c>
       <c r="H8" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="7" t="s">
+      <c r="I8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>13.07</v>
       </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="4">
+      <c r="C9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="6">
         <v>14.24</v>
       </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="E9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="7">
         <v>1.17</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="8">
         <v>0.08199999999999999</v>
       </c>
       <c r="H9" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="7" t="s">
+      <c r="I9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>8.2</v>
       </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="C10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="6">
         <v>9.5</v>
       </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="5">
+      <c r="E10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="7">
         <v>1.3</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="8">
         <v>0.13699999999999998</v>
       </c>
       <c r="H10" t="s">
         <v>13</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="7" t="s">
+      <c r="I10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="4">
         <v>9.9</v>
       </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="4">
+      <c r="C11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="6">
         <v>13.9</v>
       </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="5">
+      <c r="E11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="7">
         <v>4</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="8">
         <v>0.28800000000000003</v>
       </c>
       <c r="H11" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="7" t="s">
+      <c r="I11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>19.9</v>
       </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="C12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="6">
         <v>24.9</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="7">
         <v>5</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="8">
         <v>0.201</v>
       </c>
       <c r="H12" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J12" s="7" t="s">
+      <c r="I12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="4">
         <v>42.9</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="6">
         <v>45.9</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="7">
         <v>3</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="8">
         <v>0.065</v>
       </c>
       <c r="H13" t="s">
         <v>13</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="7" t="s">
+      <c r="I13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="4">
         <v>11.9</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="6">
         <v>14.9</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="7">
         <v>3</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="8">
         <v>0.201</v>
       </c>
       <c r="H14" t="s">
         <v>13</v>
       </c>
-      <c r="I14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J14" s="7" t="s">
+      <c r="I14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="4">
         <v>13.9</v>
       </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="4">
+      <c r="C15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="6">
         <v>16.9</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="7">
         <v>3</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="8">
         <v>0.17800000000000002</v>
       </c>
       <c r="H15" t="s">
         <v>13</v>
       </c>
-      <c r="I15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J15" s="7" t="s">
+      <c r="I15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="4">
         <v>4.9</v>
       </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="4">
+      <c r="C16" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="6">
         <v>7.9</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="7">
         <v>3</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="8">
         <v>0.38</v>
       </c>
       <c r="H16" t="s">
         <v>13</v>
       </c>
-      <c r="I16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J16" s="7" t="s">
+      <c r="I16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J16" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="4">
         <v>7.9</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="6">
         <v>9.9</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="7">
         <v>2</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="8">
         <v>0.20199999999999999</v>
       </c>
       <c r="H17" t="s">
         <v>13</v>
       </c>
-      <c r="I17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17" s="7" t="s">
+      <c r="I17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="4">
         <v>8.9</v>
       </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="4">
+      <c r="C18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="6">
         <v>16.9</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="7">
         <v>8</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="8">
         <v>0.473</v>
       </c>
       <c r="H18" t="s">
         <v>13</v>
       </c>
-      <c r="I18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J18" s="7" t="s">
+      <c r="I18" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="4">
         <v>18.9</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="6">
         <v>22.9</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="7">
         <v>4</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="8">
         <v>0.175</v>
       </c>
       <c r="H19" t="s">
         <v>13</v>
       </c>
-      <c r="I19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J19" s="7" t="s">
+      <c r="I19" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1271,296 +1274,296 @@
       <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>10.9</v>
       </c>
-      <c r="C21" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="4">
+      <c r="C21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="6">
         <v>13.9</v>
       </c>
-      <c r="E21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="5">
+      <c r="E21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="7">
         <v>3</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="8">
         <v>0.21600000000000003</v>
       </c>
       <c r="H21" t="s">
         <v>13</v>
       </c>
-      <c r="I21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J21" s="7" t="s">
+      <c r="I21" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J21" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="4">
         <v>39.9</v>
       </c>
-      <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="4">
+      <c r="C22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="6">
         <v>43.9</v>
       </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="5">
+      <c r="E22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="7">
         <v>4</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="8">
         <v>0.091</v>
       </c>
       <c r="H22" t="s">
         <v>13</v>
       </c>
-      <c r="I22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="7" t="s">
+      <c r="I22" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="4">
         <v>15.9</v>
       </c>
-      <c r="C23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="4">
+      <c r="C23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="6">
         <v>17.9</v>
       </c>
-      <c r="E23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="5">
+      <c r="E23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="7">
         <v>2</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="8">
         <v>0.11199999999999999</v>
       </c>
       <c r="H23" t="s">
         <v>13</v>
       </c>
-      <c r="I23" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J23" s="7" t="s">
+      <c r="I23" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="4">
         <v>18.8</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="6">
         <v>19.9</v>
       </c>
-      <c r="E24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="5">
+      <c r="E24" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="7">
         <v>1.1</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="8">
         <v>0.055</v>
       </c>
       <c r="H24" t="s">
         <v>13</v>
       </c>
-      <c r="I24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" s="7" t="s">
+      <c r="I24" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="4">
         <v>14.8</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="6">
         <v>18.9</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="7">
         <v>4.1</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="8">
         <v>0.217</v>
       </c>
       <c r="H25" t="s">
         <v>13</v>
       </c>
-      <c r="I25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25" s="7" t="s">
+      <c r="I25" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J25" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="4">
         <v>19.7</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="6">
         <v>24.9</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="7">
+        <v>5.2</v>
+      </c>
+      <c r="G26" s="8">
+        <v>0.209</v>
+      </c>
+      <c r="H26" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="5">
-        <v>5.2</v>
-      </c>
-      <c r="G26" s="6">
-        <v>0.209</v>
-      </c>
-      <c r="H26" t="s">
-        <v>13</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B27" s="4">
+        <v>21.9</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="6">
+        <v>26.9</v>
+      </c>
+      <c r="E27" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="3">
-        <v>21.9</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="4">
-        <v>26.9</v>
-      </c>
-      <c r="E27" s="8" t="s">
+      <c r="F27" s="7">
+        <v>5</v>
+      </c>
+      <c r="G27" s="8">
+        <v>0.18600000000000003</v>
+      </c>
+      <c r="H27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F27" s="5">
-        <v>5</v>
-      </c>
-      <c r="G27" s="6">
-        <v>0.18600000000000003</v>
-      </c>
-      <c r="H27" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B28" s="4">
+        <v>14.94</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="6">
+        <v>22.9</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="7">
+        <v>7.96</v>
+      </c>
+      <c r="G28" s="8">
+        <v>0.348</v>
+      </c>
+      <c r="H28" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="3">
-        <v>14.94</v>
-      </c>
-      <c r="C28" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="4">
-        <v>22.9</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="5">
-        <v>7.96</v>
-      </c>
-      <c r="G28" s="6">
-        <v>0.348</v>
-      </c>
-      <c r="H28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B29" s="4">
+        <v>41.5</v>
+      </c>
+      <c r="C29" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="3">
-        <v>41.5</v>
-      </c>
-      <c r="C29" s="8" t="s">
+      <c r="D29" s="6">
+        <v>48.9</v>
+      </c>
+      <c r="E29" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D29" s="4">
-        <v>48.9</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F29" s="5">
+      <c r="F29" s="7">
         <v>7.4</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="8">
         <v>0.151</v>
       </c>
       <c r="H29" t="s">
         <v>13</v>
       </c>
-      <c r="I29" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J29" s="7" t="s">
+      <c r="I29" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1573,206 +1576,206 @@
       <c r="J30" s="2"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="A31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="4">
+        <v>16.9</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="6">
+        <v>19.9</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="7">
+        <v>3</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0.151</v>
+      </c>
+      <c r="H31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="3">
-        <v>16.9</v>
-      </c>
-      <c r="C31" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" s="4">
-        <v>19.9</v>
-      </c>
-      <c r="E31" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="5">
+      <c r="B32" s="4">
+        <v>6.9</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="6">
+        <v>8.9</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="7">
+        <v>2</v>
+      </c>
+      <c r="G32" s="8">
+        <v>0.225</v>
+      </c>
+      <c r="H32" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="4">
+        <v>6.9</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="6">
+        <v>8.9</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="7">
+        <v>2</v>
+      </c>
+      <c r="G33" s="8">
+        <v>0.225</v>
+      </c>
+      <c r="H33" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" s="4">
+        <v>9.9</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="6">
+        <v>12.9</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="7">
         <v>3</v>
       </c>
-      <c r="G31" s="6">
-        <v>0.151</v>
-      </c>
-      <c r="H31" t="s">
-        <v>13</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="3">
-        <v>6.9</v>
-      </c>
-      <c r="C32" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="4">
-        <v>8.9</v>
-      </c>
-      <c r="E32" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="5">
-        <v>2</v>
-      </c>
-      <c r="G32" s="6">
-        <v>0.225</v>
-      </c>
-      <c r="H32" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="G34" s="8">
+        <v>0.233</v>
+      </c>
+      <c r="H34" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B33" s="3">
-        <v>6.9</v>
-      </c>
-      <c r="C33" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="4">
-        <v>8.9</v>
-      </c>
-      <c r="E33" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="5">
-        <v>2</v>
-      </c>
-      <c r="G33" s="6">
-        <v>0.225</v>
-      </c>
-      <c r="H33" t="s">
-        <v>13</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="B35" s="4">
+        <v>4.9</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="6">
+        <v>5.9</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="7">
+        <v>1</v>
+      </c>
+      <c r="G35" s="8">
+        <v>0.16899999999999998</v>
+      </c>
+      <c r="H35" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="3">
-        <v>9.9</v>
-      </c>
-      <c r="C34" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="4">
-        <v>12.9</v>
-      </c>
-      <c r="E34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="5">
-        <v>3</v>
-      </c>
-      <c r="G34" s="6">
-        <v>0.233</v>
-      </c>
-      <c r="H34" t="s">
-        <v>13</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="B36" s="12">
+        <v>493.61</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="3">
-        <v>4.9</v>
-      </c>
-      <c r="C35" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="4">
-        <v>5.9</v>
-      </c>
-      <c r="E35" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="5">
-        <v>1</v>
-      </c>
-      <c r="G35" s="6">
+      <c r="D36" s="12">
+        <v>593.89</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="F36" s="12">
+        <v>100.28</v>
+      </c>
+      <c r="G36" s="14">
         <v>0.16899999999999998</v>
       </c>
-      <c r="H35" t="s">
-        <v>13</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
+      <c r="H36" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="11">
-        <v>493.61</v>
-      </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="11">
-        <v>593.89</v>
-      </c>
-      <c r="E36" s="10"/>
-      <c r="F36" s="11">
-        <v>100.28</v>
-      </c>
-      <c r="G36" s="12">
-        <v>0.16899999999999998</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="69">
   <si>
     <t>מוצר</t>
   </si>
@@ -217,7 +217,7 @@
     <t/>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-21 מול 2026-09-20 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-22 מול 2026-09-21 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -311,29 +311,43 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -687,7 +701,7 @@
     <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -755,7 +769,7 @@
       <c r="G3" s="8">
         <v>0.02</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I3" s="9" t="s">
@@ -787,7 +801,7 @@
       <c r="G4" s="8">
         <v>0.078</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I4" s="9" t="s">
@@ -819,7 +833,7 @@
       <c r="G5" s="8">
         <v>0.067</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I5" s="9" t="s">
@@ -865,7 +879,7 @@
       <c r="G7" s="8">
         <v>0.223</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I7" s="9" t="s">
@@ -897,7 +911,7 @@
       <c r="G8" s="8">
         <v>0.1</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I8" s="9" t="s">
@@ -927,9 +941,9 @@
         <v>1.17</v>
       </c>
       <c r="G9" s="8">
-        <v>0.08199999999999999</v>
-      </c>
-      <c r="H9" t="s">
+        <v>0.082</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I9" s="9" t="s">
@@ -959,9 +973,9 @@
         <v>1.3</v>
       </c>
       <c r="G10" s="8">
-        <v>0.13699999999999998</v>
-      </c>
-      <c r="H10" t="s">
+        <v>0.137</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I10" s="9" t="s">
@@ -991,9 +1005,9 @@
         <v>4</v>
       </c>
       <c r="G11" s="8">
-        <v>0.28800000000000003</v>
-      </c>
-      <c r="H11" t="s">
+        <v>0.288</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I11" s="9" t="s">
@@ -1025,7 +1039,7 @@
       <c r="G12" s="8">
         <v>0.201</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I12" s="9" t="s">
@@ -1057,7 +1071,7 @@
       <c r="G13" s="8">
         <v>0.065</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I13" s="9" t="s">
@@ -1089,7 +1103,7 @@
       <c r="G14" s="8">
         <v>0.201</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I14" s="9" t="s">
@@ -1119,9 +1133,9 @@
         <v>3</v>
       </c>
       <c r="G15" s="8">
-        <v>0.17800000000000002</v>
-      </c>
-      <c r="H15" t="s">
+        <v>0.178</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I15" s="9" t="s">
@@ -1153,7 +1167,7 @@
       <c r="G16" s="8">
         <v>0.38</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I16" s="9" t="s">
@@ -1183,9 +1197,9 @@
         <v>2</v>
       </c>
       <c r="G17" s="8">
-        <v>0.20199999999999999</v>
-      </c>
-      <c r="H17" t="s">
+        <v>0.202</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I17" s="9" t="s">
@@ -1217,7 +1231,7 @@
       <c r="G18" s="8">
         <v>0.473</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I18" s="9" t="s">
@@ -1249,7 +1263,7 @@
       <c r="G19" s="8">
         <v>0.175</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I19" s="9" t="s">
@@ -1293,9 +1307,9 @@
         <v>3</v>
       </c>
       <c r="G21" s="8">
-        <v>0.21600000000000003</v>
-      </c>
-      <c r="H21" t="s">
+        <v>0.216</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="9" t="s">
@@ -1327,7 +1341,7 @@
       <c r="G22" s="8">
         <v>0.091</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I22" s="9" t="s">
@@ -1357,9 +1371,9 @@
         <v>2</v>
       </c>
       <c r="G23" s="8">
-        <v>0.11199999999999999</v>
-      </c>
-      <c r="H23" t="s">
+        <v>0.112</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I23" s="9" t="s">
@@ -1391,7 +1405,7 @@
       <c r="G24" s="8">
         <v>0.055</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I24" s="9" t="s">
@@ -1423,7 +1437,7 @@
       <c r="G25" s="8">
         <v>0.217</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I25" s="9" t="s">
@@ -1455,7 +1469,7 @@
       <c r="G26" s="8">
         <v>0.209</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I26" s="9" t="s">
@@ -1485,9 +1499,9 @@
         <v>5</v>
       </c>
       <c r="G27" s="8">
-        <v>0.18600000000000003</v>
-      </c>
-      <c r="H27" t="s">
+        <v>0.186</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I27" s="9" t="s">
@@ -1519,7 +1533,7 @@
       <c r="G28" s="8">
         <v>0.348</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I28" s="9" t="s">
@@ -1551,7 +1565,7 @@
       <c r="G29" s="8">
         <v>0.151</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I29" s="9" t="s">
@@ -1597,7 +1611,7 @@
       <c r="G31" s="8">
         <v>0.151</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I31" s="9" t="s">
@@ -1629,7 +1643,7 @@
       <c r="G32" s="8">
         <v>0.225</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I32" s="9" t="s">
@@ -1661,7 +1675,7 @@
       <c r="G33" s="8">
         <v>0.225</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I33" s="9" t="s">
@@ -1693,7 +1707,7 @@
       <c r="G34" s="8">
         <v>0.233</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I34" s="9" t="s">
@@ -1723,9 +1737,9 @@
         <v>1</v>
       </c>
       <c r="G35" s="8">
-        <v>0.16899999999999998</v>
-      </c>
-      <c r="H35" t="s">
+        <v>0.169</v>
+      </c>
+      <c r="H35" s="5" t="s">
         <v>13</v>
       </c>
       <c r="I35" s="9" t="s">
@@ -1755,13 +1769,17 @@
         <v>100.28</v>
       </c>
       <c r="G36" s="14">
-        <v>0.16899999999999998</v>
+        <v>0.169</v>
       </c>
       <c r="H36" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
+      <c r="I36" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -217,12 +217,12 @@
     <t>50.3%</t>
   </si>
   <si>
-    <t>⬇ -8.90 ₪</t>
-  </si>
-  <si>
     <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
   </si>
   <si>
+    <t>9.90</t>
+  </si>
+  <si>
     <t>16.90</t>
   </si>
   <si>
@@ -256,6 +256,9 @@
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
+    <t>31.90</t>
+  </si>
+  <si>
     <t>36.67 (3 ב-110)</t>
   </si>
   <si>
@@ -283,9 +286,6 @@
     <t>23.3%</t>
   </si>
   <si>
-    <t>⬆ +5.00 ₪</t>
-  </si>
-  <si>
     <t>בצל יבש (ק"ג)</t>
   </si>
   <si>
@@ -301,7 +301,7 @@
     <t>18.4%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-24 מול 2026-09-23 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-25 מול 2026-09-24 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -328,7 +328,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -367,16 +367,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -393,7 +383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -404,11 +394,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -419,18 +413,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -778,13 +766,13 @@
   <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
@@ -820,7 +808,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -930,7 +918,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -1360,7 +1348,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>59</v>
       </c>
@@ -1495,8 +1483,8 @@
       <c r="H24" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I24" s="10" t="s">
-        <v>68</v>
+      <c r="I24" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>15</v>
@@ -1504,13 +1492,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B25" s="4">
         <v>14.8</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>12</v>
+      <c r="C25" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="D25" s="6">
         <v>18.9</v>
@@ -1573,8 +1561,8 @@
       <c r="B27" s="4">
         <v>21.9</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>12</v>
+      <c r="C27" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="D27" s="6">
         <v>26.9</v>
@@ -1637,20 +1625,20 @@
       <c r="B29" s="4">
         <v>41.5</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>12</v>
+      <c r="C29" s="9" t="s">
+        <v>81</v>
       </c>
       <c r="D29" s="6">
         <v>48.9</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F29" s="7">
         <v>7.4</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>14</v>
@@ -1662,9 +1650,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1678,7 +1666,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B31" s="4">
         <v>16.9</v>
@@ -1696,7 +1684,7 @@
         <v>3</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>14</v>
@@ -1710,7 +1698,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B32" s="4">
         <v>6.9</v>
@@ -1728,7 +1716,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>14</v>
@@ -1742,7 +1730,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B33" s="4">
         <v>6.9</v>
@@ -1760,7 +1748,7 @@
         <v>2</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>14</v>
@@ -1774,7 +1762,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B34" s="4">
         <v>9.9</v>
@@ -1792,13 +1780,13 @@
         <v>3</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I34" s="11" t="s">
-        <v>90</v>
+      <c r="I34" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="J34" s="8" t="s">
         <v>15</v>
@@ -1836,51 +1824,51 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="11">
         <v>484.71</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="D36" s="13">
+      <c r="D36" s="11">
         <v>593.89</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="11">
         <v>109.18</v>
       </c>
-      <c r="G36" s="14" t="s">
+      <c r="G36" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="H36" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="14" t="s">
+      <c r="H36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="J36" s="14" t="s">
+      <c r="J36" s="12" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="98">
+  <si>
+    <t>מעקב מחירי מכולת יומי — 2026-09-26</t>
+  </si>
   <si>
     <t>מוצר</t>
   </si>
@@ -301,20 +304,25 @@
     <t>18.4%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-25 מול 2026-09-24 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-26 מול 2026-09-25 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
     </font>
     <font>
       <b/>
@@ -383,24 +391,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -409,19 +420,19 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -763,1120 +774,1135 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="5">
         <v>7.2</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="C4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="7">
         <v>7.35</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="E4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="8">
         <v>0.15</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="H4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="5">
         <v>5.9</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="C5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="7">
         <v>6.4</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="E5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="8">
         <v>0.5</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="G5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="4">
+      <c r="H5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5">
         <v>19.5</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="7">
         <v>20.9</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="E6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="8">
         <v>1.4</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="G6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
         <v>20.9</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="7">
         <v>26.9</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="E8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="8">
         <v>6</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="G8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="4">
+      <c r="H8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="5">
         <v>35.9</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="7">
         <v>39.9</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="E9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="8">
         <v>4</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="G9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="4">
+      <c r="H9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="5">
         <v>13.07</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="7">
         <v>14.24</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="E10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="8">
         <v>1.17</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="G10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="4">
+      <c r="H10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5">
         <v>8.2</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="7">
         <v>9.5</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="E11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="8">
         <v>1.3</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="G11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="4">
+      <c r="H11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="5">
         <v>9.9</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="7">
         <v>13.9</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="E12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="8">
         <v>4</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="G12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="4">
+      <c r="H12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="5">
         <v>19.9</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="7">
         <v>24.9</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="E13" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="8">
         <v>5</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="G13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="4">
+      <c r="H13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="5">
         <v>42.9</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="7">
         <v>45.9</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="E14" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="8">
         <v>3</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="G14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="4">
+      <c r="H14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="5">
         <v>11.9</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C15" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="7">
         <v>14.9</v>
       </c>
-      <c r="E14" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="7">
+      <c r="E15" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="8">
         <v>3</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="4">
+      <c r="G15" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="5">
         <v>13.9</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="7">
         <v>16.9</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="7">
+      <c r="E16" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="8">
         <v>3</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="G16" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="4">
+      <c r="H16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="5">
         <v>4.9</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="7">
         <v>7.9</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="7">
+      <c r="E17" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="8">
         <v>3</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="G17" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="4">
+      <c r="H17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="5">
         <v>7.9</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C18" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="7">
         <v>9.9</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" s="7">
+      <c r="E18" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="8">
         <v>2</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="G18" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="4">
+      <c r="H18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="5">
         <v>8.9</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="7">
         <v>16.9</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="7">
+      <c r="E19" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="8">
         <v>8</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="G19" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="4">
+      <c r="H19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="5">
         <v>18.9</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C20" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="7">
         <v>22.9</v>
       </c>
-      <c r="E19" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="7">
+      <c r="E20" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="8">
         <v>4</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="G20" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="5">
         <v>10.9</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="7">
         <v>13.9</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="7">
+      <c r="E22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="8">
         <v>3</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="G22" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="4">
+      <c r="H22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="5">
         <v>39.9</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C23" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="7">
         <v>43.9</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="7">
+      <c r="E23" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="8">
         <v>4</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="G23" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="4">
+      <c r="H23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="5">
         <v>15.9</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="7">
         <v>17.9</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="7">
+      <c r="E24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="8">
         <v>2</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="G24" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="4">
+      <c r="H24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="5">
         <v>9.9</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C25" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="7">
         <v>19.9</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="7">
+      <c r="E25" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="8">
         <v>10</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="G25" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="4">
+      <c r="H25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="5">
         <v>14.8</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C26" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="7">
         <v>18.9</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F25" s="7">
+      <c r="E26" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26" s="8">
         <v>4.1</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="G26" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B26" s="4">
+      <c r="H26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="5">
         <v>19.7</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C27" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="7">
         <v>24.9</v>
       </c>
-      <c r="E26" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F26" s="7">
+      <c r="E27" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" s="8">
         <v>5.2</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="G27" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="4">
+      <c r="H27" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="5">
         <v>21.9</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C28" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="7">
         <v>26.9</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="F27" s="7">
+      <c r="E28" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F28" s="8">
         <v>5</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="G28" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="4">
+      <c r="H28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="5">
         <v>14.94</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="7">
         <v>22.9</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F28" s="7">
+      <c r="E29" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="8">
         <v>7.96</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="G29" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="4">
+      <c r="H29" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="5">
         <v>41.5</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C30" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" s="7">
         <v>48.9</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="F29" s="7">
+      <c r="E30" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F30" s="8">
         <v>7.4</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="G30" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H30" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" s="5">
         <v>16.9</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="7">
         <v>19.9</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="7">
+      <c r="E32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="8">
         <v>3</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B32" s="4">
+      <c r="G32" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="5">
         <v>6.9</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="7">
         <v>8.9</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="7">
+      <c r="E33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="8">
         <v>2</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="G33" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B33" s="4">
+      <c r="H33" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="5">
         <v>6.9</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="6">
+      <c r="C34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="7">
         <v>8.9</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="7">
+      <c r="E34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="8">
         <v>2</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B34" s="4">
+      <c r="G34" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="5">
         <v>9.9</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="6">
+      <c r="C35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="7">
         <v>12.9</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="7">
+      <c r="E35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="8">
         <v>3</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="G35" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B35" s="4">
+      <c r="H35" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="5">
         <v>4.9</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="6">
+      <c r="C36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="7">
         <v>5.9</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="7">
+      <c r="E36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="8">
         <v>1</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
+      <c r="G36" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B36" s="11">
+      <c r="H36" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="12">
         <v>484.71</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" s="11">
+      <c r="C37" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D37" s="12">
         <v>593.89</v>
       </c>
-      <c r="E36" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="F36" s="11">
+      <c r="E37" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="F37" s="12">
         <v>109.18</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G37" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="H36" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
+      <c r="J37" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A37:J37"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A38:J38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="98">
   <si>
-    <t>מעקב מחירי מכולת יומי — 2026-09-26</t>
+    <t>מעקב מחירי מכולת יומי — 2026-09-27</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -304,7 +304,7 @@
     <t>18.4%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-26 מול 2026-09-25 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-27 מול 2026-09-26 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -411,7 +411,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -778,9 +778,9 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
@@ -801,7 +801,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -833,7 +833,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -943,7 +943,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>60</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>85</v>
       </c>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="98">
   <si>
-    <t>מעקב מחירי מכולת יומי — 2026-09-27</t>
+    <t>מעקב מחירי מכולת יומי — 2026-09-28</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -262,7 +262,7 @@
     <t>31.90</t>
   </si>
   <si>
-    <t>36.67 (3 ב-110)</t>
+    <t>30.00 (4 ב-120)</t>
   </si>
   <si>
     <t>15.1%</t>
@@ -304,7 +304,7 @@
     <t>18.4%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-27 מול 2026-09-26 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-28 מול 2026-09-27 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="98">
   <si>
-    <t>מעקב מחירי מכולת יומי — 2026-09-28</t>
+    <t>מעקב מחירים יומי — 2026-09-29</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -304,7 +304,7 @@
     <t>18.4%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-28 מול 2026-09-27 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-29 מול 2026-09-28 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -397,7 +397,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -777,17 +777,17 @@
   <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -801,7 +801,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -833,7 +833,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -943,7 +943,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>60</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>85</v>
       </c>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="98">
   <si>
-    <t>מעקב מחירים יומי — 2026-09-29</t>
+    <t>מעקב מחירים יומי — 2026-09-30</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -304,7 +304,7 @@
     <t>18.4%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-29 מול 2026-09-28 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-30 מול 2026-09-29 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -391,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -429,6 +429,7 @@
     <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1868,10 +1869,10 @@
       <c r="F37" s="12">
         <v>109.18</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="G37" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="H37" s="13" t="s">
+      <c r="H37" s="14" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="13" t="s">
@@ -1882,18 +1883,18 @@
       </c>
     </row>
     <row r="38" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="98">
-  <si>
-    <t>מעקב מחירים יומי — 2026-09-30</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="113">
+  <si>
+    <t>מעקב מחירים יומי — 2026-10-01</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -58,7 +58,7 @@
     <t>2.0%</t>
   </si>
   <si>
-    <t>אושר עד</t>
+    <t>אושר עד (0.15 ₪)</t>
   </si>
   <si>
     <t>ללא שינוי</t>
@@ -70,12 +70,18 @@
     <t>7.8%</t>
   </si>
   <si>
+    <t>אושר עד (0.50 ₪)</t>
+  </si>
+  <si>
     <t>גבינה צהובה 9% פרוסות 200 גרם</t>
   </si>
   <si>
     <t>6.7%</t>
   </si>
   <si>
+    <t>אושר עד (1.40 ₪)</t>
+  </si>
+  <si>
     <t>מאכל ושתיה סגורים</t>
   </si>
   <si>
@@ -88,24 +94,36 @@
     <t>22.3%</t>
   </si>
   <si>
+    <t>אושר עד (6.00 ₪)</t>
+  </si>
+  <si>
     <t>קפה נמס טסטרס צויס 200 גרם</t>
   </si>
   <si>
     <t>10.0%</t>
   </si>
   <si>
+    <t>אושר עד (4.00 ₪)</t>
+  </si>
+  <si>
     <t>ביצים L (מנורמל ל-12 יח')</t>
   </si>
   <si>
     <t>8.2%</t>
   </si>
   <si>
+    <t>אושר עד (1.17 ₪)</t>
+  </si>
+  <si>
     <t>קוקה קולה זירו 1.5 ליטר</t>
   </si>
   <si>
     <t>13.7%</t>
   </si>
   <si>
+    <t>אושר עד (1.30 ₪)</t>
+  </si>
+  <si>
     <t>סירופ יכין פטל דיאט 1 ליטר</t>
   </si>
   <si>
@@ -121,6 +139,9 @@
     <t>20.1%</t>
   </si>
   <si>
+    <t>אושר עד (5.00 ₪)</t>
+  </si>
+  <si>
     <t>יין טפרברג מוסקטו לבן 750 מ"ל</t>
   </si>
   <si>
@@ -133,6 +154,9 @@
     <t>6.5%</t>
   </si>
   <si>
+    <t>אושר עד (3.00 ₪)</t>
+  </si>
+  <si>
     <t>שיבולת שועל קוואקר 500 גרם</t>
   </si>
   <si>
@@ -172,6 +196,9 @@
     <t>20.2%</t>
   </si>
   <si>
+    <t>אושר עד (2.00 ₪)</t>
+  </si>
+  <si>
     <t>דבש טבעי עמק חפר 350 גרם</t>
   </si>
   <si>
@@ -181,6 +208,9 @@
     <t>47.3%</t>
   </si>
   <si>
+    <t>אושר עד (8.00 ₪)</t>
+  </si>
+  <si>
     <t>רביולי גבינה קלאסי שטראוס 400 גרם</t>
   </si>
   <si>
@@ -220,18 +250,21 @@
     <t>50.3%</t>
   </si>
   <si>
+    <t>אושר עד (10.00 ₪)</t>
+  </si>
+  <si>
     <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
   </si>
   <si>
-    <t>9.90</t>
-  </si>
-  <si>
     <t>16.90</t>
   </si>
   <si>
     <t>21.7%</t>
   </si>
   <si>
+    <t>אושר עד (4.10 ₪)</t>
+  </si>
+  <si>
     <t>מגבוני האגיס ללא בישום 4X56</t>
   </si>
   <si>
@@ -241,6 +274,9 @@
     <t>20.9%</t>
   </si>
   <si>
+    <t>אושר עד (5.20 ₪)</t>
+  </si>
+  <si>
     <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
   </si>
   <si>
@@ -256,18 +292,21 @@
     <t>34.8%</t>
   </si>
   <si>
+    <t>אושר עד (7.96 ₪)</t>
+  </si>
+  <si>
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
-    <t>31.90</t>
-  </si>
-  <si>
     <t>30.00 (4 ב-120)</t>
   </si>
   <si>
     <t>15.1%</t>
   </si>
   <si>
+    <t>אושר עד (7.40 ₪)</t>
+  </si>
+  <si>
     <t>פירות וירקות</t>
   </si>
   <si>
@@ -295,6 +334,9 @@
     <t>16.9%</t>
   </si>
   <si>
+    <t>אושר עד (1.00 ₪)</t>
+  </si>
+  <si>
     <t>סה"כ</t>
   </si>
   <si>
@@ -304,7 +346,10 @@
     <t>18.4%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-09-30 מול 2026-09-29 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>אושר עד (109.18 ₪)</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-01 מול 2026-09-30 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -397,7 +442,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -778,7 +823,7 @@
   <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -788,7 +833,7 @@
     <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -802,7 +847,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -903,7 +948,7 @@
         <v>18</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>16</v>
@@ -914,7 +959,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" s="5">
         <v>19.5</v>
@@ -932,10 +977,10 @@
         <v>1.4</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>16</v>
@@ -946,7 +991,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -960,7 +1005,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B8" s="5">
         <v>20.9</v>
@@ -972,16 +1017,16 @@
         <v>26.9</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F8" s="8">
         <v>6</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>16</v>
@@ -992,7 +1037,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B9" s="5">
         <v>35.9</v>
@@ -1010,10 +1055,10 @@
         <v>4</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>16</v>
@@ -1024,7 +1069,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B10" s="5">
         <v>13.07</v>
@@ -1042,10 +1087,10 @@
         <v>1.17</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>16</v>
@@ -1056,7 +1101,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B11" s="5">
         <v>8.2</v>
@@ -1074,10 +1119,10 @@
         <v>1.3</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>16</v>
@@ -1088,7 +1133,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B12" s="5">
         <v>9.9</v>
@@ -1106,10 +1151,10 @@
         <v>4</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>16</v>
@@ -1120,7 +1165,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B13" s="5">
         <v>19.9</v>
@@ -1132,16 +1177,16 @@
         <v>24.9</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F13" s="8">
         <v>5</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>16</v>
@@ -1152,28 +1197,28 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5">
         <v>42.9</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D14" s="7">
         <v>45.9</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F14" s="8">
         <v>3</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>16</v>
@@ -1184,28 +1229,28 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B15" s="5">
         <v>11.9</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D15" s="7">
         <v>14.9</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="F15" s="8">
         <v>3</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="I15" s="9" t="s">
         <v>16</v>
@@ -1216,7 +1261,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B16" s="5">
         <v>13.9</v>
@@ -1228,16 +1273,16 @@
         <v>16.9</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F16" s="8">
         <v>3</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="I16" s="9" t="s">
         <v>16</v>
@@ -1248,7 +1293,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B17" s="5">
         <v>4.9</v>
@@ -1260,16 +1305,16 @@
         <v>7.9</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F17" s="8">
         <v>3</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>16</v>
@@ -1280,28 +1325,28 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B18" s="5">
         <v>7.9</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D18" s="7">
         <v>9.9</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F18" s="8">
         <v>2</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="I18" s="9" t="s">
         <v>16</v>
@@ -1312,7 +1357,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B19" s="5">
         <v>8.9</v>
@@ -1324,16 +1369,16 @@
         <v>16.9</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F19" s="8">
         <v>8</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="I19" s="9" t="s">
         <v>16</v>
@@ -1344,28 +1389,28 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B20" s="5">
         <v>18.9</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D20" s="7">
         <v>22.9</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F20" s="8">
         <v>4</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I20" s="9" t="s">
         <v>16</v>
@@ -1376,7 +1421,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1390,7 +1435,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B22" s="5">
         <v>10.9</v>
@@ -1408,10 +1453,10 @@
         <v>3</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="I22" s="9" t="s">
         <v>16</v>
@@ -1422,7 +1467,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B23" s="5">
         <v>39.9</v>
@@ -1440,10 +1485,10 @@
         <v>4</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>16</v>
@@ -1454,7 +1499,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B24" s="5">
         <v>15.9</v>
@@ -1472,10 +1517,10 @@
         <v>2</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="I24" s="9" t="s">
         <v>16</v>
@@ -1486,7 +1531,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B25" s="5">
         <v>9.9</v>
@@ -1504,10 +1549,10 @@
         <v>10</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="I25" s="9" t="s">
         <v>16</v>
@@ -1518,28 +1563,28 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B26" s="5">
         <v>14.8</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>70</v>
+      <c r="C26" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="D26" s="7">
         <v>18.9</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F26" s="8">
         <v>4.1</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="I26" s="9" t="s">
         <v>16</v>
@@ -1550,28 +1595,28 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B27" s="5">
         <v>19.7</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D27" s="7">
         <v>24.9</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="F27" s="8">
         <v>5.2</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="I27" s="9" t="s">
         <v>16</v>
@@ -1582,28 +1627,28 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B28" s="5">
         <v>21.9</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>54</v>
+      <c r="C28" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="D28" s="7">
         <v>26.9</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F28" s="8">
         <v>5</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="I28" s="9" t="s">
         <v>16</v>
@@ -1614,7 +1659,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B29" s="5">
         <v>14.94</v>
@@ -1626,16 +1671,16 @@
         <v>22.9</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F29" s="8">
         <v>7.96</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="I29" s="9" t="s">
         <v>16</v>
@@ -1646,28 +1691,28 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="B30" s="5">
         <v>41.5</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>82</v>
+      <c r="C30" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="D30" s="7">
         <v>48.9</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F30" s="8">
         <v>7.4</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="I30" s="9" t="s">
         <v>16</v>
@@ -1678,7 +1723,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1692,7 +1737,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B32" s="5">
         <v>16.9</v>
@@ -1710,10 +1755,10 @@
         <v>3</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="I32" s="9" t="s">
         <v>16</v>
@@ -1724,7 +1769,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B33" s="5">
         <v>6.9</v>
@@ -1742,10 +1787,10 @@
         <v>2</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="I33" s="9" t="s">
         <v>16</v>
@@ -1756,7 +1801,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="B34" s="5">
         <v>6.9</v>
@@ -1774,10 +1819,10 @@
         <v>2</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>16</v>
@@ -1788,7 +1833,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B35" s="5">
         <v>9.9</v>
@@ -1806,10 +1851,10 @@
         <v>3</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>16</v>
@@ -1820,7 +1865,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B36" s="5">
         <v>4.9</v>
@@ -1838,10 +1883,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>16</v>
@@ -1852,39 +1897,39 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B37" s="12">
         <v>484.71</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D37" s="12">
         <v>593.89</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="F37" s="12">
         <v>109.18</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="113">
   <si>
-    <t>מעקב מחירים יומי — 2026-10-01</t>
+    <t>מעקב מחירים יומי — 2026-10-02</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -349,7 +349,7 @@
     <t>אושר עד (109.18 ₪)</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-01 מול 2026-09-30 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-02 מול 2026-10-01 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="113">
-  <si>
-    <t>מעקב מחירים יומי — 2026-10-02</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="145">
+  <si>
+    <t>מעקב מחירי סופרמרקט יומי — 2026-10-03</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -52,13 +52,22 @@
     <t>חלב 3% תנובה 1 ליטר</t>
   </si>
   <si>
+    <t>7.20</t>
+  </si>
+  <si>
     <t>—</t>
   </si>
   <si>
+    <t>7.35</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
     <t>2.0%</t>
   </si>
   <si>
-    <t>אושר עד (0.15 ₪)</t>
+    <t>אושר עד</t>
   </si>
   <si>
     <t>ללא שינוי</t>
@@ -67,178 +76,241 @@
     <t>קוטג' תנובה 5% 250 גרם</t>
   </si>
   <si>
+    <t>5.90</t>
+  </si>
+  <si>
+    <t>6.40</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
     <t>7.8%</t>
   </si>
   <si>
-    <t>אושר עד (0.50 ₪)</t>
-  </si>
-  <si>
     <t>גבינה צהובה 9% פרוסות 200 גרם</t>
   </si>
   <si>
+    <t>19.50</t>
+  </si>
+  <si>
+    <t>20.90</t>
+  </si>
+  <si>
+    <t>1.40</t>
+  </si>
+  <si>
     <t>6.7%</t>
   </si>
   <si>
-    <t>אושר עד (1.40 ₪)</t>
-  </si>
-  <si>
     <t>מאכל ושתיה סגורים</t>
   </si>
   <si>
     <t>טונה סטארקיסט בשמן 4X160 גרם</t>
   </si>
   <si>
+    <t>26.90</t>
+  </si>
+  <si>
     <t>23.00 (2 ב-46)</t>
   </si>
   <si>
+    <t>6.00</t>
+  </si>
+  <si>
     <t>22.3%</t>
   </si>
   <si>
-    <t>אושר עד (6.00 ₪)</t>
-  </si>
-  <si>
     <t>קפה נמס טסטרס צויס 200 גרם</t>
   </si>
   <si>
+    <t>35.90</t>
+  </si>
+  <si>
+    <t>39.90</t>
+  </si>
+  <si>
+    <t>4.00</t>
+  </si>
+  <si>
     <t>10.0%</t>
   </si>
   <si>
-    <t>אושר עד (4.00 ₪)</t>
-  </si>
-  <si>
     <t>ביצים L (מנורמל ל-12 יח')</t>
   </si>
   <si>
+    <t>13.07</t>
+  </si>
+  <si>
+    <t>14.24</t>
+  </si>
+  <si>
+    <t>1.17</t>
+  </si>
+  <si>
     <t>8.2%</t>
   </si>
   <si>
-    <t>אושר עד (1.17 ₪)</t>
-  </si>
-  <si>
     <t>קוקה קולה זירו 1.5 ליטר</t>
   </si>
   <si>
+    <t>8.20</t>
+  </si>
+  <si>
+    <t>9.50</t>
+  </si>
+  <si>
+    <t>1.30</t>
+  </si>
+  <si>
     <t>13.7%</t>
   </si>
   <si>
-    <t>אושר עד (1.30 ₪)</t>
-  </si>
-  <si>
     <t>סירופ יכין פטל דיאט 1 ליטר</t>
   </si>
   <si>
+    <t>9.90</t>
+  </si>
+  <si>
+    <t>13.90</t>
+  </si>
+  <si>
     <t>28.8%</t>
   </si>
   <si>
     <t>יין סגל אדום יבש 750 מ"ל</t>
   </si>
   <si>
-    <t>22.50 (2 ב-45)</t>
+    <t>19.90</t>
+  </si>
+  <si>
+    <t>24.90</t>
+  </si>
+  <si>
+    <t>5.00</t>
   </si>
   <si>
     <t>20.1%</t>
   </si>
   <si>
-    <t>אושר עד (5.00 ₪)</t>
-  </si>
-  <si>
     <t>יין טפרברג מוסקטו לבן 750 מ"ל</t>
   </si>
   <si>
+    <t>42.90</t>
+  </si>
+  <si>
     <t>37.50 (2 ב-75)</t>
   </si>
   <si>
-    <t>40.00 (2 ב-80)</t>
+    <t>45.90</t>
+  </si>
+  <si>
+    <t>3.00</t>
   </si>
   <si>
     <t>6.5%</t>
   </si>
   <si>
-    <t>אושר עד (3.00 ₪)</t>
-  </si>
-  <si>
     <t>שיבולת שועל קוואקר 500 גרם</t>
   </si>
   <si>
+    <t>11.90</t>
+  </si>
+  <si>
     <t>9.00 (2 ב-18)</t>
   </si>
   <si>
-    <t>11.00 (2 ב-22)</t>
+    <t>14.90</t>
   </si>
   <si>
     <t>חמאת בוטנים טבעית בטר אנד דיפרנט 350 גרם</t>
   </si>
   <si>
+    <t>16.90</t>
+  </si>
+  <si>
+    <t>17.8%</t>
+  </si>
+  <si>
+    <t>ספגטי אסם 500 גרם</t>
+  </si>
+  <si>
+    <t>4.90</t>
+  </si>
+  <si>
+    <t>7.90</t>
+  </si>
+  <si>
+    <t>38.0%</t>
+  </si>
+  <si>
+    <t>פסטה פנה ריגטה ברילה 500 גרם</t>
+  </si>
+  <si>
+    <t>6.50 (2 ב-13)</t>
+  </si>
+  <si>
+    <t>2.00</t>
+  </si>
+  <si>
+    <t>20.2%</t>
+  </si>
+  <si>
+    <t>דבש טבעי עמק חפר 350 גרם</t>
+  </si>
+  <si>
+    <t>8.90</t>
+  </si>
+  <si>
+    <t>8.00</t>
+  </si>
+  <si>
+    <t>47.3%</t>
+  </si>
+  <si>
+    <t>רביולי גבינה קלאסי שטראוס 400 גרם</t>
+  </si>
+  <si>
+    <t>18.90</t>
+  </si>
+  <si>
+    <t>15.00 (2 ב-30)</t>
+  </si>
+  <si>
+    <t>22.90</t>
+  </si>
+  <si>
+    <t>17.5%</t>
+  </si>
+  <si>
+    <t>ניקיון וטואלטיקה</t>
+  </si>
+  <si>
+    <t>מגבות נייר ניקול 6 גלילים</t>
+  </si>
+  <si>
+    <t>10.90</t>
+  </si>
+  <si>
+    <t>21.6%</t>
+  </si>
+  <si>
+    <t>נייר טואלט לילי פסטל 32 גלילים</t>
+  </si>
+  <si>
+    <t>43.90</t>
+  </si>
+  <si>
+    <t>9.1%</t>
+  </si>
+  <si>
+    <t>אקונומיקה סנו גאוול 4 ליטר</t>
+  </si>
+  <si>
     <t>15.90</t>
   </si>
   <si>
-    <t>17.8%</t>
-  </si>
-  <si>
-    <t>ספגטי אסם 500 גרם</t>
-  </si>
-  <si>
-    <t>6.00 (4 ב-24)</t>
-  </si>
-  <si>
-    <t>38.0%</t>
-  </si>
-  <si>
-    <t>פסטה פנה ריגטה ברילה 500 גרם</t>
-  </si>
-  <si>
-    <t>6.50 (2 ב-13)</t>
-  </si>
-  <si>
-    <t>7.50 (2 ב-15)</t>
-  </si>
-  <si>
-    <t>20.2%</t>
-  </si>
-  <si>
-    <t>אושר עד (2.00 ₪)</t>
-  </si>
-  <si>
-    <t>דבש טבעי עמק חפר 350 גרם</t>
-  </si>
-  <si>
-    <t>14.90</t>
-  </si>
-  <si>
-    <t>47.3%</t>
-  </si>
-  <si>
-    <t>אושר עד (8.00 ₪)</t>
-  </si>
-  <si>
-    <t>רביולי גבינה קלאסי שטראוס 400 גרם</t>
-  </si>
-  <si>
-    <t>15.00 (2 ב-30)</t>
-  </si>
-  <si>
-    <t>18.00 (2 ב-36)</t>
-  </si>
-  <si>
-    <t>17.5%</t>
-  </si>
-  <si>
-    <t>ניקיון וטואלטיקה</t>
-  </si>
-  <si>
-    <t>מגבות נייר ניקול 6 גלילים</t>
-  </si>
-  <si>
-    <t>21.6%</t>
-  </si>
-  <si>
-    <t>נייר טואלט לילי פסטל 32 גלילים</t>
-  </si>
-  <si>
-    <t>9.1%</t>
-  </si>
-  <si>
-    <t>אקונומיקה סנו גאוול 4 ליטר</t>
+    <t>17.90</t>
   </si>
   <si>
     <t>11.2%</t>
@@ -247,40 +319,40 @@
     <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
   </si>
   <si>
+    <t>10.00</t>
+  </si>
+  <si>
     <t>50.3%</t>
   </si>
   <si>
-    <t>אושר עד (10.00 ₪)</t>
-  </si>
-  <si>
     <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
   </si>
   <si>
-    <t>16.90</t>
+    <t>14.80</t>
+  </si>
+  <si>
+    <t>4.10</t>
   </si>
   <si>
     <t>21.7%</t>
   </si>
   <si>
-    <t>אושר עד (4.10 ₪)</t>
-  </si>
-  <si>
     <t>מגבוני האגיס ללא בישום 4X56</t>
   </si>
   <si>
-    <t>20.00 (2 ב-40)</t>
+    <t>19.70</t>
+  </si>
+  <si>
+    <t>5.20</t>
   </si>
   <si>
     <t>20.9%</t>
   </si>
   <si>
-    <t>אושר עד (5.20 ₪)</t>
-  </si>
-  <si>
     <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
   </si>
   <si>
-    <t>22.00 (2 ב-44)</t>
+    <t>21.90</t>
   </si>
   <si>
     <t>18.6%</t>
@@ -289,24 +361,36 @@
     <t>שמפו פנטן משקם 600 מ"ל</t>
   </si>
   <si>
+    <t>14.94</t>
+  </si>
+  <si>
+    <t>7.96</t>
+  </si>
+  <si>
     <t>34.8%</t>
   </si>
   <si>
-    <t>אושר עד (7.96 ₪)</t>
-  </si>
-  <si>
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
+    <t>41.50</t>
+  </si>
+  <si>
+    <t>31.90</t>
+  </si>
+  <si>
+    <t>48.90</t>
+  </si>
+  <si>
     <t>30.00 (4 ב-120)</t>
   </si>
   <si>
+    <t>7.40</t>
+  </si>
+  <si>
     <t>15.1%</t>
   </si>
   <si>
-    <t>אושר עד (7.40 ₪)</t>
-  </si>
-  <si>
     <t>פירות וירקות</t>
   </si>
   <si>
@@ -316,6 +400,9 @@
     <t>עגבניה (ק"ג)</t>
   </si>
   <si>
+    <t>6.90</t>
+  </si>
+  <si>
     <t>22.5%</t>
   </si>
   <si>
@@ -325,31 +412,40 @@
     <t>בננות (ק"ג)</t>
   </si>
   <si>
+    <t>12.90</t>
+  </si>
+  <si>
     <t>23.3%</t>
   </si>
   <si>
     <t>בצל יבש (ק"ג)</t>
   </si>
   <si>
+    <t>1.00</t>
+  </si>
+  <si>
     <t>16.9%</t>
   </si>
   <si>
-    <t>אושר עד (1.00 ₪)</t>
-  </si>
-  <si>
     <t>סה"כ</t>
   </si>
   <si>
+    <t>484.71</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
+    <t>593.89</t>
+  </si>
+  <si>
+    <t>109.18</t>
+  </si>
+  <si>
     <t>18.4%</t>
   </si>
   <si>
-    <t>אושר עד (109.18 ₪)</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-02 מול 2026-10-01 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-03 מול 2026-10-02 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -436,13 +532,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -450,16 +546,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -471,13 +564,10 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -823,7 +913,7 @@
   <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -847,7 +937,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -879,7 +969,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -897,101 +987,101 @@
       <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5">
-        <v>7.2</v>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="7">
-        <v>7.35</v>
+        <v>14</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="8">
-        <v>0.15</v>
+        <v>14</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="5">
-        <v>5.9</v>
+        <v>20</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="7">
-        <v>6.4</v>
+        <v>14</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="8">
-        <v>0.5</v>
+        <v>14</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="5">
-        <v>19.5</v>
+        <v>25</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="7">
-        <v>20.9</v>
+        <v>14</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="8">
-        <v>1.4</v>
+        <v>14</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1005,423 +1095,423 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="5">
-        <v>20.9</v>
+        <v>31</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="7">
-        <v>26.9</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="8">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="5">
-        <v>35.9</v>
+        <v>36</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="7">
-        <v>39.9</v>
+        <v>14</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="8">
-        <v>4</v>
+        <v>14</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="5">
-        <v>13.07</v>
+        <v>41</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="7">
-        <v>14.24</v>
+        <v>14</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="8">
-        <v>1.17</v>
+        <v>14</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="5">
-        <v>8.2</v>
+        <v>46</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="7">
-        <v>9.5</v>
+        <v>14</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="8">
-        <v>1.3</v>
+        <v>14</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="5">
-        <v>9.9</v>
+        <v>51</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="7">
-        <v>13.9</v>
+        <v>14</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="8">
-        <v>4</v>
+        <v>14</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="5">
-        <v>19.9</v>
+        <v>55</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="7">
-        <v>24.9</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="8">
-        <v>5</v>
+        <v>14</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="5">
-        <v>42.9</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="7">
-        <v>45.9</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="8">
-        <v>3</v>
+        <v>60</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="5">
-        <v>11.9</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="7">
-        <v>14.9</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="8">
-        <v>3</v>
+        <v>66</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="5">
-        <v>13.9</v>
+        <v>70</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="7">
-        <v>16.9</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" s="8">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="5">
-        <v>4.9</v>
+        <v>73</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="7">
-        <v>7.9</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="8">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="5">
-        <v>7.9</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="7">
-        <v>9.9</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F18" s="8">
-        <v>2</v>
+        <v>77</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" s="5">
-        <v>8.9</v>
+        <v>81</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="7">
-        <v>16.9</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="F19" s="8">
-        <v>8</v>
+        <v>14</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B20" s="5">
-        <v>18.9</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" s="7">
-        <v>22.9</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" s="8">
-        <v>4</v>
+        <v>85</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1435,295 +1525,295 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B22" s="5">
-        <v>10.9</v>
+        <v>91</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="7">
-        <v>13.9</v>
+        <v>14</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="8">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="5">
-        <v>39.9</v>
+        <v>94</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="7">
-        <v>43.9</v>
+        <v>14</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="8">
-        <v>4</v>
+        <v>14</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B24" s="5">
-        <v>15.9</v>
+        <v>97</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="7">
-        <v>17.9</v>
+        <v>14</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="8">
-        <v>2</v>
+        <v>14</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B25" s="5">
-        <v>9.9</v>
+        <v>101</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="7">
-        <v>19.9</v>
+        <v>14</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="8">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B26" s="5">
-        <v>14.8</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="7">
-        <v>18.9</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F26" s="8">
-        <v>4.1</v>
+        <v>104</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>106</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" s="5">
-        <v>19.7</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="7">
-        <v>24.9</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="F27" s="8">
-        <v>5.2</v>
+        <v>108</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B28" s="5">
-        <v>21.9</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="7">
-        <v>26.9</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="F28" s="8">
-        <v>5</v>
+        <v>112</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B29" s="5">
-        <v>14.94</v>
+        <v>115</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="7">
-        <v>22.9</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F29" s="8">
-        <v>7.96</v>
+        <v>14</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B30" s="5">
-        <v>41.5</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="7">
-        <v>48.9</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F30" s="8">
-        <v>7.4</v>
+        <v>119</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1737,209 +1827,209 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B32" s="5">
-        <v>16.9</v>
+        <v>127</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="7">
-        <v>19.9</v>
+        <v>14</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="8">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B33" s="5">
-        <v>6.9</v>
+        <v>128</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="7">
-        <v>8.9</v>
+        <v>14</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="8">
-        <v>2</v>
+        <v>14</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B34" s="5">
-        <v>6.9</v>
+        <v>131</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="7">
-        <v>8.9</v>
+        <v>14</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="8">
-        <v>2</v>
+        <v>14</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B35" s="5">
-        <v>9.9</v>
+        <v>132</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="7">
-        <v>12.9</v>
+        <v>14</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="8">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B36" s="5">
-        <v>4.9</v>
+        <v>135</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="7">
-        <v>5.9</v>
+        <v>14</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="8">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>136</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="B37" s="12">
-        <v>484.71</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D37" s="12">
-        <v>593.89</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="F37" s="12">
-        <v>109.18</v>
-      </c>
-      <c r="G37" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H37" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="J37" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
+      <c r="A37" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="145">
-  <si>
-    <t>מעקב מחירי סופרמרקט יומי — 2026-10-03</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="90">
+  <si>
+    <t>מחירון יומי - 2026-10-04</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -52,19 +52,10 @@
     <t>חלב 3% תנובה 1 ליטר</t>
   </si>
   <si>
-    <t>7.20</t>
-  </si>
-  <si>
     <t>—</t>
   </si>
   <si>
-    <t>7.35</t>
-  </si>
-  <si>
-    <t>0.15</t>
-  </si>
-  <si>
-    <t>2.0%</t>
+    <t>2%</t>
   </si>
   <si>
     <t>אושר עד</t>
@@ -76,30 +67,12 @@
     <t>קוטג' תנובה 5% 250 גרם</t>
   </si>
   <si>
-    <t>5.90</t>
-  </si>
-  <si>
-    <t>6.40</t>
-  </si>
-  <si>
-    <t>0.50</t>
-  </si>
-  <si>
     <t>7.8%</t>
   </si>
   <si>
     <t>גבינה צהובה 9% פרוסות 200 גרם</t>
   </si>
   <si>
-    <t>19.50</t>
-  </si>
-  <si>
-    <t>20.90</t>
-  </si>
-  <si>
-    <t>1.40</t>
-  </si>
-  <si>
     <t>6.7%</t>
   </si>
   <si>
@@ -109,103 +82,46 @@
     <t>טונה סטארקיסט בשמן 4X160 גרם</t>
   </si>
   <si>
-    <t>26.90</t>
-  </si>
-  <si>
-    <t>23.00 (2 ב-46)</t>
-  </si>
-  <si>
-    <t>6.00</t>
-  </si>
-  <si>
     <t>22.3%</t>
   </si>
   <si>
     <t>קפה נמס טסטרס צויס 200 גרם</t>
   </si>
   <si>
-    <t>35.90</t>
-  </si>
-  <si>
-    <t>39.90</t>
-  </si>
-  <si>
-    <t>4.00</t>
-  </si>
-  <si>
-    <t>10.0%</t>
+    <t>10%</t>
   </si>
   <si>
     <t>ביצים L (מנורמל ל-12 יח')</t>
   </si>
   <si>
-    <t>13.07</t>
-  </si>
-  <si>
-    <t>14.24</t>
-  </si>
-  <si>
-    <t>1.17</t>
-  </si>
-  <si>
     <t>8.2%</t>
   </si>
   <si>
     <t>קוקה קולה זירו 1.5 ליטר</t>
   </si>
   <si>
-    <t>8.20</t>
-  </si>
-  <si>
-    <t>9.50</t>
-  </si>
-  <si>
-    <t>1.30</t>
-  </si>
-  <si>
     <t>13.7%</t>
   </si>
   <si>
     <t>סירופ יכין פטל דיאט 1 ליטר</t>
   </si>
   <si>
-    <t>9.90</t>
-  </si>
-  <si>
-    <t>13.90</t>
-  </si>
-  <si>
     <t>28.8%</t>
   </si>
   <si>
     <t>יין סגל אדום יבש 750 מ"ל</t>
   </si>
   <si>
-    <t>19.90</t>
-  </si>
-  <si>
-    <t>24.90</t>
-  </si>
-  <si>
-    <t>5.00</t>
-  </si>
-  <si>
     <t>20.1%</t>
   </si>
   <si>
     <t>יין טפרברג מוסקטו לבן 750 מ"ל</t>
   </si>
   <si>
-    <t>42.90</t>
-  </si>
-  <si>
-    <t>37.50 (2 ב-75)</t>
-  </si>
-  <si>
-    <t>45.90</t>
-  </si>
-  <si>
-    <t>3.00</t>
+    <t>40.00 (2 ב-80)</t>
+  </si>
+  <si>
+    <t>42.50 (2 ב-85)</t>
   </si>
   <si>
     <t>6.5%</t>
@@ -214,72 +130,48 @@
     <t>שיבולת שועל קוואקר 500 גרם</t>
   </si>
   <si>
-    <t>11.90</t>
-  </si>
-  <si>
-    <t>9.00 (2 ב-18)</t>
+    <t>11.00 (2 ב-22)</t>
+  </si>
+  <si>
+    <t>חמאת בוטנים טבעית בטר אנד דיפרנט 350 גרם</t>
+  </si>
+  <si>
+    <t>17.8%</t>
+  </si>
+  <si>
+    <t>ספגטי אסם 500 גרם</t>
+  </si>
+  <si>
+    <t>4.50 (4 ב-18)</t>
+  </si>
+  <si>
+    <t>6.00 (3 ב-18)</t>
+  </si>
+  <si>
+    <t>38%</t>
+  </si>
+  <si>
+    <t>פסטה פנה ריגטה ברילה 500 גרם</t>
+  </si>
+  <si>
+    <t>6.67 (3 ב-20)</t>
+  </si>
+  <si>
+    <t>20.2%</t>
+  </si>
+  <si>
+    <t>דבש טבעי עמק חפר 350 גרם</t>
   </si>
   <si>
     <t>14.90</t>
   </si>
   <si>
-    <t>חמאת בוטנים טבעית בטר אנד דיפרנט 350 גרם</t>
-  </si>
-  <si>
-    <t>16.90</t>
-  </si>
-  <si>
-    <t>17.8%</t>
-  </si>
-  <si>
-    <t>ספגטי אסם 500 גרם</t>
-  </si>
-  <si>
-    <t>4.90</t>
-  </si>
-  <si>
-    <t>7.90</t>
-  </si>
-  <si>
-    <t>38.0%</t>
-  </si>
-  <si>
-    <t>פסטה פנה ריגטה ברילה 500 גרם</t>
-  </si>
-  <si>
-    <t>6.50 (2 ב-13)</t>
-  </si>
-  <si>
-    <t>2.00</t>
-  </si>
-  <si>
-    <t>20.2%</t>
-  </si>
-  <si>
-    <t>דבש טבעי עמק חפר 350 גרם</t>
-  </si>
-  <si>
-    <t>8.90</t>
-  </si>
-  <si>
-    <t>8.00</t>
-  </si>
-  <si>
     <t>47.3%</t>
   </si>
   <si>
     <t>רביולי גבינה קלאסי שטראוס 400 גרם</t>
   </si>
   <si>
-    <t>18.90</t>
-  </si>
-  <si>
-    <t>15.00 (2 ב-30)</t>
-  </si>
-  <si>
-    <t>22.90</t>
-  </si>
-  <si>
     <t>17.5%</t>
   </si>
   <si>
@@ -289,49 +181,31 @@
     <t>מגבות נייר ניקול 6 גלילים</t>
   </si>
   <si>
-    <t>10.90</t>
-  </si>
-  <si>
     <t>21.6%</t>
   </si>
   <si>
     <t>נייר טואלט לילי פסטל 32 גלילים</t>
   </si>
   <si>
-    <t>43.90</t>
-  </si>
-  <si>
     <t>9.1%</t>
   </si>
   <si>
     <t>אקונומיקה סנו גאוול 4 ליטר</t>
   </si>
   <si>
-    <t>15.90</t>
-  </si>
-  <si>
-    <t>17.90</t>
-  </si>
-  <si>
     <t>11.2%</t>
   </si>
   <si>
     <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
   </si>
   <si>
-    <t>10.00</t>
-  </si>
-  <si>
     <t>50.3%</t>
   </si>
   <si>
     <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
   </si>
   <si>
-    <t>14.80</t>
-  </si>
-  <si>
-    <t>4.10</t>
+    <t>16.00 (2 ב-32)</t>
   </si>
   <si>
     <t>21.7%</t>
@@ -340,19 +214,13 @@
     <t>מגבוני האגיס ללא בישום 4X56</t>
   </si>
   <si>
-    <t>19.70</t>
-  </si>
-  <si>
-    <t>5.20</t>
-  </si>
-  <si>
     <t>20.9%</t>
   </si>
   <si>
     <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
   </si>
   <si>
-    <t>21.90</t>
+    <t>21.00 (2 ב-42)</t>
   </si>
   <si>
     <t>18.6%</t>
@@ -361,10 +229,7 @@
     <t>שמפו פנטן משקם 600 מ"ל</t>
   </si>
   <si>
-    <t>14.94</t>
-  </si>
-  <si>
-    <t>7.96</t>
+    <t>19.00 (2 ב-38)</t>
   </si>
   <si>
     <t>34.8%</t>
@@ -373,21 +238,9 @@
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
-    <t>41.50</t>
-  </si>
-  <si>
-    <t>31.90</t>
-  </si>
-  <si>
-    <t>48.90</t>
-  </si>
-  <si>
     <t>30.00 (4 ב-120)</t>
   </si>
   <si>
-    <t>7.40</t>
-  </si>
-  <si>
     <t>15.1%</t>
   </si>
   <si>
@@ -400,9 +253,6 @@
     <t>עגבניה (ק"ג)</t>
   </si>
   <si>
-    <t>6.90</t>
-  </si>
-  <si>
     <t>22.5%</t>
   </si>
   <si>
@@ -412,40 +262,25 @@
     <t>בננות (ק"ג)</t>
   </si>
   <si>
-    <t>12.90</t>
-  </si>
-  <si>
     <t>23.3%</t>
   </si>
   <si>
     <t>בצל יבש (ק"ג)</t>
   </si>
   <si>
-    <t>1.00</t>
-  </si>
-  <si>
     <t>16.9%</t>
   </si>
   <si>
     <t>סה"כ</t>
   </si>
   <si>
-    <t>484.71</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>593.89</t>
-  </si>
-  <si>
-    <t>109.18</t>
-  </si>
-  <si>
     <t>18.4%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-03 מול 2026-10-02 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-04 מול 2026-10-03 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -532,7 +367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -546,15 +381,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -564,9 +396,7 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -913,7 +743,7 @@
   <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -937,7 +767,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -969,7 +799,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -987,101 +817,101 @@
       <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>13</v>
+      <c r="B4" s="5">
+        <v>7.2</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="7">
+        <v>7.35</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>17</v>
-      </c>
       <c r="H4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="B5" s="5">
+        <v>5.9</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>22</v>
+        <v>13</v>
+      </c>
+      <c r="D5" s="7">
+        <v>6.4</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0.5</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>26</v>
+        <v>19</v>
+      </c>
+      <c r="B6" s="5">
+        <v>19.5</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="D6" s="7">
+        <v>20.9</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>28</v>
+        <v>13</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1.4</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1095,423 +925,423 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>20.9</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>34</v>
+        <v>13</v>
+      </c>
+      <c r="D8" s="7">
+        <v>26.9</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="8">
+        <v>6</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>37</v>
+        <v>24</v>
+      </c>
+      <c r="B9" s="5">
+        <v>35.9</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>38</v>
+        <v>13</v>
+      </c>
+      <c r="D9" s="7">
+        <v>39.9</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>39</v>
+        <v>13</v>
+      </c>
+      <c r="F9" s="8">
+        <v>4</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>42</v>
+        <v>26</v>
+      </c>
+      <c r="B10" s="5">
+        <v>13.07</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>43</v>
+        <v>13</v>
+      </c>
+      <c r="D10" s="7">
+        <v>14.24</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>44</v>
+        <v>13</v>
+      </c>
+      <c r="F10" s="8">
+        <v>1.17</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>47</v>
+        <v>28</v>
+      </c>
+      <c r="B11" s="5">
+        <v>8.2</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>48</v>
+        <v>13</v>
+      </c>
+      <c r="D11" s="7">
+        <v>9.5</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>49</v>
+        <v>13</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1.3</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>52</v>
+        <v>30</v>
+      </c>
+      <c r="B12" s="5">
+        <v>9.9</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>53</v>
+        <v>13</v>
+      </c>
+      <c r="D12" s="7">
+        <v>13.9</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>39</v>
+        <v>13</v>
+      </c>
+      <c r="F12" s="8">
+        <v>4</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>56</v>
+        <v>32</v>
+      </c>
+      <c r="B13" s="5">
+        <v>19.9</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>57</v>
+        <v>13</v>
+      </c>
+      <c r="D13" s="7">
+        <v>24.9</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>58</v>
+        <v>13</v>
+      </c>
+      <c r="F13" s="8">
+        <v>5</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>64</v>
+        <v>34</v>
+      </c>
+      <c r="B14" s="5">
+        <v>42.9</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="7">
+        <v>45.9</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="8">
+        <v>3</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>64</v>
+        <v>38</v>
+      </c>
+      <c r="B15" s="5">
+        <v>11.9</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="7">
+        <v>14.9</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="8">
+        <v>3</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>53</v>
+        <v>40</v>
+      </c>
+      <c r="B16" s="5">
+        <v>13.9</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>71</v>
+        <v>13</v>
+      </c>
+      <c r="D16" s="7">
+        <v>16.9</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>64</v>
+        <v>13</v>
+      </c>
+      <c r="F16" s="8">
+        <v>3</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>64</v>
+        <v>42</v>
+      </c>
+      <c r="B17" s="5">
+        <v>4.9</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="7">
+        <v>7.9</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="8">
+        <v>3</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B18" s="5">
+        <v>7.9</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="7">
+        <v>9.9</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>79</v>
+        <v>13</v>
+      </c>
+      <c r="F18" s="8">
+        <v>2</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>82</v>
+        <v>49</v>
+      </c>
+      <c r="B19" s="5">
+        <v>8.9</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>83</v>
+        <v>13</v>
+      </c>
+      <c r="D19" s="7">
+        <v>16.9</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="8">
+        <v>8</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>88</v>
+        <v>52</v>
+      </c>
+      <c r="B20" s="5">
+        <v>18.9</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="7">
+        <v>22.9</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>39</v>
+        <v>13</v>
+      </c>
+      <c r="F20" s="8">
+        <v>4</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1525,295 +1355,295 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>92</v>
+        <v>55</v>
+      </c>
+      <c r="B22" s="5">
+        <v>10.9</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>53</v>
+        <v>13</v>
+      </c>
+      <c r="D22" s="7">
+        <v>13.9</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>64</v>
+        <v>13</v>
+      </c>
+      <c r="F22" s="8">
+        <v>3</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>38</v>
+        <v>57</v>
+      </c>
+      <c r="B23" s="5">
+        <v>39.9</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>95</v>
+        <v>13</v>
+      </c>
+      <c r="D23" s="7">
+        <v>43.9</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>39</v>
+        <v>13</v>
+      </c>
+      <c r="F23" s="8">
+        <v>4</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>98</v>
+        <v>59</v>
+      </c>
+      <c r="B24" s="5">
+        <v>15.9</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>99</v>
+        <v>13</v>
+      </c>
+      <c r="D24" s="7">
+        <v>17.9</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>79</v>
+        <v>13</v>
+      </c>
+      <c r="F24" s="8">
+        <v>2</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>52</v>
+        <v>61</v>
+      </c>
+      <c r="B25" s="5">
+        <v>9.9</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>56</v>
+        <v>13</v>
+      </c>
+      <c r="D25" s="7">
+        <v>19.9</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>102</v>
+        <v>13</v>
+      </c>
+      <c r="F25" s="8">
+        <v>10</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>106</v>
+        <v>63</v>
+      </c>
+      <c r="B26" s="5">
+        <v>14.8</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="7">
+        <v>18.9</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="8">
+        <v>4.1</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>57</v>
+        <v>66</v>
+      </c>
+      <c r="B27" s="5">
+        <v>19.7</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="7">
+        <v>24.9</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>110</v>
+        <v>13</v>
+      </c>
+      <c r="F27" s="8">
+        <v>5.2</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C28" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="5">
+        <v>21.9</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="7">
+        <v>26.9</v>
+      </c>
+      <c r="E28" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>58</v>
+      <c r="F28" s="8">
+        <v>5</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>116</v>
+        <v>71</v>
+      </c>
+      <c r="B29" s="5">
+        <v>14.94</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>117</v>
+        <v>13</v>
+      </c>
+      <c r="D29" s="7">
+        <v>22.9</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29" s="8">
+        <v>7.96</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>124</v>
+        <v>74</v>
+      </c>
+      <c r="B30" s="5">
+        <v>41.5</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="7">
+        <v>48.9</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F30" s="8">
+        <v>7.4</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1827,209 +1657,209 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>71</v>
+        <v>78</v>
+      </c>
+      <c r="B32" s="5">
+        <v>16.9</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>56</v>
+        <v>13</v>
+      </c>
+      <c r="D32" s="7">
+        <v>19.9</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>64</v>
+        <v>13</v>
+      </c>
+      <c r="F32" s="8">
+        <v>3</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>129</v>
+        <v>79</v>
+      </c>
+      <c r="B33" s="5">
+        <v>6.9</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>82</v>
+        <v>13</v>
+      </c>
+      <c r="D33" s="7">
+        <v>8.9</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>79</v>
+        <v>13</v>
+      </c>
+      <c r="F33" s="8">
+        <v>2</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>129</v>
+        <v>81</v>
+      </c>
+      <c r="B34" s="5">
+        <v>6.9</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>82</v>
+        <v>13</v>
+      </c>
+      <c r="D34" s="7">
+        <v>8.9</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>79</v>
+        <v>13</v>
+      </c>
+      <c r="F34" s="8">
+        <v>2</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>52</v>
+        <v>82</v>
+      </c>
+      <c r="B35" s="5">
+        <v>9.9</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>133</v>
+        <v>13</v>
+      </c>
+      <c r="D35" s="7">
+        <v>12.9</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>64</v>
+        <v>13</v>
+      </c>
+      <c r="F35" s="8">
+        <v>3</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>74</v>
+        <v>84</v>
+      </c>
+      <c r="B36" s="5">
+        <v>4.9</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="D36" s="7">
+        <v>5.9</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>136</v>
+        <v>13</v>
+      </c>
+      <c r="F36" s="8">
+        <v>1</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="H37" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
+      <c r="A37" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="12">
+        <v>484.71</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D37" s="12">
+        <v>593.89</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F37" s="12">
+        <v>109.18</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="94">
-  <si>
-    <t>מעקב מחירים יומי - 2026-10-06</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="97">
+  <si>
+    <t>מעקב מחירים יומי - 2026-10-07</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -100,7 +100,13 @@
     <t>קוקה קולה זירו 1.5 ליטר</t>
   </si>
   <si>
-    <t>13.7%</t>
+    <t>2.7%</t>
+  </si>
+  <si>
+    <t>שופרסל</t>
+  </si>
+  <si>
+    <t>⬇ -1.52 ₪</t>
   </si>
   <si>
     <t>סירופ יכין פטל דיאט 1 ליטר</t>
@@ -151,7 +157,7 @@
     <t>6.00 (3 ב-18)</t>
   </si>
   <si>
-    <t>27.9%</t>
+    <t>27.8%</t>
   </si>
   <si>
     <t>פסטה פנה ריגטה ברילה 500 גרם</t>
@@ -262,7 +268,10 @@
     <t>5.90</t>
   </si>
   <si>
-    <t>⬆ +1.00 ₪</t>
+    <t>40.4%</t>
+  </si>
+  <si>
+    <t>⬇ -2.00 ₪</t>
   </si>
   <si>
     <t>מלפפון (ק"ג)</t>
@@ -289,10 +298,10 @@
     <t/>
   </si>
   <si>
-    <t>16.6%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-06 מול 2026-10-05 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>16.7%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-07 מול 2026-10-06 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -358,12 +367,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1051,37 +1060,37 @@
       <c r="A11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="7">
         <v>8.2</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="7">
-        <v>9.5</v>
+      <c r="D11" s="5">
+        <v>7.98</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="8">
-        <v>1.3</v>
+        <v>0.22</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>29</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="9" t="s">
-        <v>16</v>
+      <c r="J11" s="10" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="5">
         <v>9.9</v>
@@ -1099,7 +1108,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>15</v>
@@ -1113,7 +1122,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="5">
         <v>19.9</v>
@@ -1131,7 +1140,7 @@
         <v>5</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>15</v>
@@ -1145,25 +1154,25 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="5">
         <v>42.9</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>35</v>
+      <c r="C14" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="D14" s="7">
         <v>45.9</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>36</v>
+      <c r="E14" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="F14" s="8">
         <v>3</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>15</v>
@@ -1177,25 +1186,25 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B15" s="5">
         <v>11.9</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>39</v>
+      <c r="C15" s="11" t="s">
+        <v>41</v>
       </c>
       <c r="D15" s="7">
         <v>14.9</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>40</v>
+      <c r="E15" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="F15" s="8">
         <v>3</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>15</v>
@@ -1209,7 +1218,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B16" s="5">
         <v>13.9</v>
@@ -1227,7 +1236,7 @@
         <v>3</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>15</v>
@@ -1241,25 +1250,25 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5">
         <v>5.7</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>44</v>
+      <c r="C17" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="D17" s="7">
         <v>7.9</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>45</v>
+      <c r="E17" s="11" t="s">
+        <v>47</v>
       </c>
       <c r="F17" s="8">
         <v>2.2</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>15</v>
@@ -1273,13 +1282,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B18" s="5">
         <v>7.9</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>48</v>
+      <c r="C18" s="11" t="s">
+        <v>50</v>
       </c>
       <c r="D18" s="7">
         <v>9.9</v>
@@ -1291,7 +1300,7 @@
         <v>2</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>15</v>
@@ -1305,7 +1314,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B19" s="5">
         <v>8.9</v>
@@ -1316,14 +1325,14 @@
       <c r="D19" s="7">
         <v>16.9</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>51</v>
+      <c r="E19" s="11" t="s">
+        <v>53</v>
       </c>
       <c r="F19" s="8">
         <v>8</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>15</v>
@@ -1337,7 +1346,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B20" s="5">
         <v>18.9</v>
@@ -1355,7 +1364,7 @@
         <v>4</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>15</v>
@@ -1369,7 +1378,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1383,7 +1392,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B22" s="5">
         <v>10.9</v>
@@ -1401,7 +1410,7 @@
         <v>3</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>15</v>
@@ -1415,7 +1424,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B23" s="5">
         <v>39.9</v>
@@ -1433,7 +1442,7 @@
         <v>4</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>15</v>
@@ -1447,7 +1456,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B24" s="5">
         <v>15.9</v>
@@ -1465,7 +1474,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>15</v>
@@ -1479,13 +1488,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B25" s="5">
         <v>18.8</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>63</v>
+      <c r="C25" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="D25" s="7">
         <v>19.9</v>
@@ -1497,7 +1506,7 @@
         <v>1.1</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>15</v>
@@ -1511,7 +1520,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B26" s="5">
         <v>14.8</v>
@@ -1522,14 +1531,14 @@
       <c r="D26" s="7">
         <v>18.9</v>
       </c>
-      <c r="E26" s="10" t="s">
-        <v>66</v>
+      <c r="E26" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="F26" s="8">
         <v>4.1</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>15</v>
@@ -1543,13 +1552,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B27" s="5">
         <v>19.7</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>69</v>
+      <c r="C27" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="D27" s="7">
         <v>24.9</v>
@@ -1561,7 +1570,7 @@
         <v>5.2</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>15</v>
@@ -1575,7 +1584,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B28" s="5">
         <v>21.9</v>
@@ -1586,8 +1595,8 @@
       <c r="D28" s="7">
         <v>26.9</v>
       </c>
-      <c r="E28" s="10" t="s">
-        <v>72</v>
+      <c r="E28" s="11" t="s">
+        <v>74</v>
       </c>
       <c r="F28" s="8">
         <v>5</v>
@@ -1607,7 +1616,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B29" s="5">
         <v>14.94</v>
@@ -1618,14 +1627,14 @@
       <c r="D29" s="7">
         <v>22.9</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>74</v>
+      <c r="E29" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="F29" s="8">
         <v>7.96</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>15</v>
@@ -1639,13 +1648,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B30" s="5">
         <v>41.5</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>77</v>
+      <c r="C30" s="11" t="s">
+        <v>79</v>
       </c>
       <c r="D30" s="7">
         <v>48.9</v>
@@ -1657,7 +1666,7 @@
         <v>7.4</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>15</v>
@@ -1671,7 +1680,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1685,7 +1694,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B32" s="5">
         <v>16.9</v>
@@ -1703,7 +1712,7 @@
         <v>3</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>15</v>
@@ -1717,13 +1726,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B33" s="5">
-        <v>7.9</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>82</v>
+        <v>5.9</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>84</v>
       </c>
       <c r="D33" s="7">
         <v>9.9</v>
@@ -1732,24 +1741,24 @@
         <v>13</v>
       </c>
       <c r="F33" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>83</v>
+      <c r="I33" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B34" s="5">
         <v>6.9</v>
@@ -1767,7 +1776,7 @@
         <v>2</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>15</v>
@@ -1781,7 +1790,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B35" s="5">
         <v>9.9</v>
@@ -1799,7 +1808,7 @@
         <v>3</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>15</v>
@@ -1813,7 +1822,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B36" s="5">
         <v>4.9</v>
@@ -1831,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>15</v>
@@ -1845,35 +1854,33 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B37" s="13">
-        <v>496.41</v>
+        <v>494.41</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D37" s="13">
-        <v>594.89</v>
+        <v>593.37</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F37" s="13">
-        <v>98.48</v>
+        <v>98.96</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H37" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-    </row>
-    <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="97">
-  <si>
-    <t>מעקב מחירים יומי - 2026-10-07</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="94">
+  <si>
+    <t>מעקב מחירים יומי - 2026-10-08</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -106,9 +106,6 @@
     <t>שופרסל</t>
   </si>
   <si>
-    <t>⬇ -1.52 ₪</t>
-  </si>
-  <si>
     <t>סירופ יכין פטל דיאט 1 ליטר</t>
   </si>
   <si>
@@ -271,9 +268,6 @@
     <t>40.4%</t>
   </si>
   <si>
-    <t>⬇ -2.00 ₪</t>
-  </si>
-  <si>
     <t>מלפפון (ק"ג)</t>
   </si>
   <si>
@@ -295,13 +289,10 @@
     <t>סה"כ</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>16.7%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-07 מול 2026-10-06 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-08 מול 2026-10-07 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -333,7 +324,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -367,11 +358,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
@@ -396,29 +382,23 @@
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -426,13 +406,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1084,13 +1062,13 @@
       <c r="I11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="10" t="s">
-        <v>31</v>
+      <c r="J11" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="5">
         <v>9.9</v>
@@ -1108,7 +1086,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>15</v>
@@ -1122,7 +1100,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="5">
         <v>19.9</v>
@@ -1140,7 +1118,7 @@
         <v>5</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>15</v>
@@ -1154,25 +1132,25 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="5">
         <v>42.9</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>37</v>
+      <c r="C14" s="10" t="s">
+        <v>36</v>
       </c>
       <c r="D14" s="7">
         <v>45.9</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>38</v>
+      <c r="E14" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="F14" s="8">
         <v>3</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>15</v>
@@ -1186,25 +1164,25 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="5">
         <v>11.9</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>41</v>
+      <c r="C15" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="D15" s="7">
         <v>14.9</v>
       </c>
-      <c r="E15" s="11" t="s">
-        <v>42</v>
+      <c r="E15" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="F15" s="8">
         <v>3</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>15</v>
@@ -1218,7 +1196,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="5">
         <v>13.9</v>
@@ -1236,7 +1214,7 @@
         <v>3</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>15</v>
@@ -1250,25 +1228,25 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="5">
         <v>5.7</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>46</v>
+      <c r="C17" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="D17" s="7">
         <v>7.9</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>47</v>
+      <c r="E17" s="10" t="s">
+        <v>46</v>
       </c>
       <c r="F17" s="8">
         <v>2.2</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>15</v>
@@ -1282,13 +1260,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18" s="5">
         <v>7.9</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>50</v>
+      <c r="C18" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="D18" s="7">
         <v>9.9</v>
@@ -1300,7 +1278,7 @@
         <v>2</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>15</v>
@@ -1314,7 +1292,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" s="5">
         <v>8.9</v>
@@ -1325,14 +1303,14 @@
       <c r="D19" s="7">
         <v>16.9</v>
       </c>
-      <c r="E19" s="11" t="s">
-        <v>53</v>
+      <c r="E19" s="10" t="s">
+        <v>52</v>
       </c>
       <c r="F19" s="8">
         <v>8</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>15</v>
@@ -1346,7 +1324,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B20" s="5">
         <v>18.9</v>
@@ -1364,7 +1342,7 @@
         <v>4</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>15</v>
@@ -1378,7 +1356,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1392,7 +1370,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B22" s="5">
         <v>10.9</v>
@@ -1410,7 +1388,7 @@
         <v>3</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>15</v>
@@ -1424,7 +1402,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" s="5">
         <v>39.9</v>
@@ -1442,7 +1420,7 @@
         <v>4</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>15</v>
@@ -1456,7 +1434,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B24" s="5">
         <v>15.9</v>
@@ -1474,7 +1452,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>15</v>
@@ -1488,13 +1466,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B25" s="5">
         <v>18.8</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>65</v>
+      <c r="C25" s="10" t="s">
+        <v>64</v>
       </c>
       <c r="D25" s="7">
         <v>19.9</v>
@@ -1506,7 +1484,7 @@
         <v>1.1</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>15</v>
@@ -1520,7 +1498,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B26" s="5">
         <v>14.8</v>
@@ -1531,14 +1509,14 @@
       <c r="D26" s="7">
         <v>18.9</v>
       </c>
-      <c r="E26" s="11" t="s">
-        <v>68</v>
+      <c r="E26" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="F26" s="8">
         <v>4.1</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>15</v>
@@ -1552,13 +1530,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B27" s="5">
         <v>19.7</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>71</v>
+      <c r="C27" s="10" t="s">
+        <v>70</v>
       </c>
       <c r="D27" s="7">
         <v>24.9</v>
@@ -1570,7 +1548,7 @@
         <v>5.2</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>15</v>
@@ -1584,7 +1562,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B28" s="5">
         <v>21.9</v>
@@ -1595,8 +1573,8 @@
       <c r="D28" s="7">
         <v>26.9</v>
       </c>
-      <c r="E28" s="11" t="s">
-        <v>74</v>
+      <c r="E28" s="10" t="s">
+        <v>73</v>
       </c>
       <c r="F28" s="8">
         <v>5</v>
@@ -1616,7 +1594,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B29" s="5">
         <v>14.94</v>
@@ -1627,14 +1605,14 @@
       <c r="D29" s="7">
         <v>22.9</v>
       </c>
-      <c r="E29" s="11" t="s">
-        <v>76</v>
+      <c r="E29" s="10" t="s">
+        <v>75</v>
       </c>
       <c r="F29" s="8">
         <v>7.96</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>15</v>
@@ -1648,13 +1626,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B30" s="5">
         <v>41.5</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>79</v>
+      <c r="C30" s="10" t="s">
+        <v>78</v>
       </c>
       <c r="D30" s="7">
         <v>48.9</v>
@@ -1666,7 +1644,7 @@
         <v>7.4</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>15</v>
@@ -1680,7 +1658,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1694,7 +1672,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B32" s="5">
         <v>16.9</v>
@@ -1712,7 +1690,7 @@
         <v>3</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>15</v>
@@ -1726,13 +1704,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B33" s="5">
         <v>5.9</v>
       </c>
-      <c r="C33" s="11" t="s">
-        <v>84</v>
+      <c r="C33" s="10" t="s">
+        <v>83</v>
       </c>
       <c r="D33" s="7">
         <v>9.9</v>
@@ -1744,13 +1722,13 @@
         <v>4</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="10" t="s">
-        <v>86</v>
+      <c r="I33" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>16</v>
@@ -1758,7 +1736,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B34" s="5">
         <v>6.9</v>
@@ -1776,7 +1754,7 @@
         <v>2</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>15</v>
@@ -1790,7 +1768,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B35" s="5">
         <v>9.9</v>
@@ -1808,7 +1786,7 @@
         <v>3</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>15</v>
@@ -1822,7 +1800,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B36" s="5">
         <v>4.9</v>
@@ -1840,47 +1818,43 @@
         <v>1</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" s="12">
+        <v>494.41</v>
+      </c>
+      <c r="C37" s="13"/>
+      <c r="D37" s="12">
+        <v>593.37</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="12">
+        <v>98.96</v>
+      </c>
+      <c r="G37" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="H36" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B37" s="13">
-        <v>494.41</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D37" s="13">
-        <v>593.37</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F37" s="13">
-        <v>98.96</v>
-      </c>
-      <c r="G37" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="H37" s="14" t="s">
-        <v>15</v>
-      </c>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="94">
-  <si>
-    <t>מעקב מחירים יומי - 2026-10-08</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="98">
+  <si>
+    <t>מחירי מוצרים - 2026-10-09</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -82,6 +82,9 @@
     <t>טונה סטארקיסט בשמן 4X160 גרם</t>
   </si>
   <si>
+    <t>23.00 (2 ב-46)</t>
+  </si>
+  <si>
     <t>18.6%</t>
   </si>
   <si>
@@ -226,6 +229,9 @@
     <t>17.50 (2 ב-35)</t>
   </si>
   <si>
+    <t>20.00 (2 ב-40)</t>
+  </si>
+  <si>
     <t>20.9%</t>
   </si>
   <si>
@@ -250,6 +256,9 @@
     <t>31.90</t>
   </si>
   <si>
+    <t>33.33 (3 ב-100)</t>
+  </si>
+  <si>
     <t>15.1%</t>
   </si>
   <si>
@@ -289,10 +298,13 @@
     <t>סה"כ</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>16.7%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-08 מול 2026-10-07 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-09 מול 2026-10-08 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -379,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -398,7 +410,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -410,9 +421,6 @@
     </xf>
     <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -765,7 +773,7 @@
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="10" width="20" customWidth="1"/>
+    <col min="9" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -782,7 +790,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -844,19 +852,19 @@
       <c r="E4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="G4" s="6" t="s">
+      <c r="F4">
+        <v>0.14999999999999947</v>
+      </c>
+      <c r="G4" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="9" t="s">
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -876,19 +884,19 @@
       <c r="E5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5">
         <v>0.5</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="9" t="s">
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -908,19 +916,19 @@
       <c r="E6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="8">
-        <v>1.4</v>
-      </c>
-      <c r="G6" s="6" t="s">
+      <c r="F6">
+        <v>1.3999999999999986</v>
+      </c>
+      <c r="G6" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="9" t="s">
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -951,28 +959,28 @@
       <c r="D8" s="7">
         <v>26.9</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="8">
+      <c r="E8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8">
         <v>5</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="9" t="s">
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="5">
         <v>35.9</v>
@@ -986,25 +994,25 @@
       <c r="E9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9">
         <v>4</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="9" t="s">
+      <c r="G9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="5">
         <v>13.07</v>
@@ -1018,25 +1026,25 @@
       <c r="E10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10">
         <v>1.17</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="9" t="s">
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="7">
         <v>8.2</v>
@@ -1050,25 +1058,25 @@
       <c r="E11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="8">
-        <v>0.22</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="6" t="s">
+      <c r="F11">
+        <v>0.21999999999999886</v>
+      </c>
+      <c r="G11" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="9" t="s">
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="5">
         <v>9.9</v>
@@ -1082,25 +1090,25 @@
       <c r="E12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12">
         <v>4</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="9" t="s">
+      <c r="G12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="5">
         <v>19.9</v>
@@ -1114,89 +1122,89 @@
       <c r="E13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13">
         <v>5</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="9" t="s">
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="5">
         <v>42.9</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>36</v>
+      <c r="C14" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="D14" s="7">
         <v>45.9</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="8">
+      <c r="E14" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14">
         <v>3</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="9" t="s">
+      <c r="G14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="5">
         <v>11.9</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>40</v>
+      <c r="C15" s="9" t="s">
+        <v>41</v>
       </c>
       <c r="D15" s="7">
         <v>14.9</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="8">
+      <c r="E15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15">
         <v>3</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="9" t="s">
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="5">
         <v>13.9</v>
@@ -1210,63 +1218,63 @@
       <c r="E16" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="8">
-        <v>3</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="9" t="s">
+      <c r="F16">
+        <v>2.9999999999999982</v>
+      </c>
+      <c r="G16" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5">
         <v>5.7</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>45</v>
+      <c r="C17" s="9" t="s">
+        <v>46</v>
       </c>
       <c r="D17" s="7">
         <v>7.9</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="8">
+      <c r="E17" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17">
         <v>2.2</v>
       </c>
-      <c r="G17" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="9" t="s">
+      <c r="G17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" s="5">
         <v>7.9</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>49</v>
+      <c r="C18" s="9" t="s">
+        <v>50</v>
       </c>
       <c r="D18" s="7">
         <v>9.9</v>
@@ -1274,25 +1282,25 @@
       <c r="E18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18">
         <v>2</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="9" t="s">
+      <c r="G18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B19" s="5">
         <v>8.9</v>
@@ -1303,28 +1311,28 @@
       <c r="D19" s="7">
         <v>16.9</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F19" s="8">
-        <v>8</v>
-      </c>
-      <c r="G19" s="6" t="s">
+      <c r="E19" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="9" t="s">
+      <c r="F19">
+        <v>7.999999999999998</v>
+      </c>
+      <c r="G19" t="s">
+        <v>54</v>
+      </c>
+      <c r="H19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B20" s="5">
         <v>18.9</v>
@@ -1338,25 +1346,25 @@
       <c r="E20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20">
         <v>4</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="9" t="s">
+      <c r="G20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1370,7 +1378,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B22" s="5">
         <v>10.9</v>
@@ -1384,25 +1392,25 @@
       <c r="E22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22">
         <v>3</v>
       </c>
-      <c r="G22" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="9" t="s">
+      <c r="G22" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23" s="5">
         <v>39.9</v>
@@ -1416,25 +1424,25 @@
       <c r="E23" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23">
         <v>4</v>
       </c>
-      <c r="G23" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="9" t="s">
+      <c r="G23" t="s">
+        <v>61</v>
+      </c>
+      <c r="H23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="5">
         <v>15.9</v>
@@ -1448,31 +1456,31 @@
       <c r="E24" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="8">
-        <v>2</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="9" t="s">
+      <c r="F24">
+        <v>1.9999999999999982</v>
+      </c>
+      <c r="G24" t="s">
+        <v>63</v>
+      </c>
+      <c r="H24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B25" s="5">
         <v>18.8</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>64</v>
+      <c r="C25" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="D25" s="7">
         <v>19.9</v>
@@ -1480,25 +1488,25 @@
       <c r="E25" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F25" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="9" t="s">
+      <c r="F25">
+        <v>1.0999999999999979</v>
+      </c>
+      <c r="G25" t="s">
+        <v>66</v>
+      </c>
+      <c r="H25" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B26" s="5">
         <v>14.8</v>
@@ -1509,60 +1517,60 @@
       <c r="D26" s="7">
         <v>18.9</v>
       </c>
-      <c r="E26" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="F26" s="8">
-        <v>4.1</v>
-      </c>
-      <c r="G26" s="6" t="s">
+      <c r="E26" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="H26" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="9" t="s">
+      <c r="F26">
+        <v>4.099999999999998</v>
+      </c>
+      <c r="G26" t="s">
+        <v>69</v>
+      </c>
+      <c r="H26" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B27" s="5">
         <v>19.7</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>70</v>
+      <c r="C27" s="9" t="s">
+        <v>71</v>
       </c>
       <c r="D27" s="7">
         <v>24.9</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="8">
-        <v>5.2</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="9" t="s">
+      <c r="E27" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27">
+        <v>5.199999999999999</v>
+      </c>
+      <c r="G27" t="s">
+        <v>73</v>
+      </c>
+      <c r="H27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B28" s="5">
         <v>21.9</v>
@@ -1573,28 +1581,28 @@
       <c r="D28" s="7">
         <v>26.9</v>
       </c>
-      <c r="E28" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F28" s="8">
+      <c r="E28" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28">
         <v>5</v>
       </c>
-      <c r="G28" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="9" t="s">
+      <c r="G28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B29" s="5">
         <v>14.94</v>
@@ -1605,60 +1613,60 @@
       <c r="D29" s="7">
         <v>22.9</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F29" s="8">
-        <v>7.96</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="9" t="s">
+      <c r="E29" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F29">
+        <v>7.959999999999999</v>
+      </c>
+      <c r="G29" t="s">
+        <v>78</v>
+      </c>
+      <c r="H29" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B30" s="5">
         <v>41.5</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>78</v>
+      <c r="C30" s="9" t="s">
+        <v>80</v>
       </c>
       <c r="D30" s="7">
         <v>48.9</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="8">
-        <v>7.4</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="9" t="s">
+      <c r="E30" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F30">
+        <v>7.399999999999999</v>
+      </c>
+      <c r="G30" t="s">
+        <v>82</v>
+      </c>
+      <c r="H30" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1672,7 +1680,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B32" s="5">
         <v>16.9</v>
@@ -1686,31 +1694,31 @@
       <c r="E32" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32">
         <v>3</v>
       </c>
-      <c r="G32" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="9" t="s">
+      <c r="G32" t="s">
+        <v>82</v>
+      </c>
+      <c r="H32" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B33" s="5">
         <v>5.9</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>83</v>
+      <c r="C33" s="9" t="s">
+        <v>86</v>
       </c>
       <c r="D33" s="7">
         <v>9.9</v>
@@ -1718,25 +1726,25 @@
       <c r="E33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33">
         <v>4</v>
       </c>
-      <c r="G33" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="9" t="s">
+      <c r="G33" t="s">
+        <v>87</v>
+      </c>
+      <c r="H33" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B34" s="5">
         <v>6.9</v>
@@ -1750,25 +1758,25 @@
       <c r="E34" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34">
         <v>2</v>
       </c>
-      <c r="G34" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="9" t="s">
+      <c r="G34" t="s">
+        <v>89</v>
+      </c>
+      <c r="H34" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B35" s="5">
         <v>9.9</v>
@@ -1782,25 +1790,25 @@
       <c r="E35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35">
         <v>3</v>
       </c>
-      <c r="G35" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="9" t="s">
+      <c r="G35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B36" s="5">
         <v>4.9</v>
@@ -1814,57 +1822,67 @@
       <c r="E36" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36">
         <v>1</v>
       </c>
-      <c r="G36" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="9" t="s">
+      <c r="G36" t="s">
+        <v>93</v>
+      </c>
+      <c r="H36" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B37" s="12">
-        <v>494.41</v>
-      </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="12">
-        <v>593.37</v>
-      </c>
-      <c r="E37" s="13"/>
+      <c r="A37" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="11">
+        <v>494.40999999999985</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D37" s="11">
+        <v>593.3699999999997</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>95</v>
+      </c>
       <c r="F37" s="12">
-        <v>98.96</v>
-      </c>
-      <c r="G37" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
+        <v>98.95999999999981</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="98">
-  <si>
-    <t>מחירי מוצרים - 2026-10-09</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="97">
+  <si>
+    <t>מחירי מוצרים - 2026-10-10</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -298,13 +298,10 @@
     <t>סה"כ</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>16.7%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-09 מול 2026-10-08 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-10 מול 2026-10-09 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -391,7 +388,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -410,6 +407,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -419,8 +419,12 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -766,14 +770,14 @@
   <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="10" width="22" customWidth="1"/>
+    <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -852,19 +856,19 @@
       <c r="E4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F4">
-        <v>0.14999999999999947</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="F4" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="8" t="s">
+      <c r="H4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -884,19 +888,19 @@
       <c r="E5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="8">
         <v>0.5</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="8" t="s">
+      <c r="H5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -916,19 +920,19 @@
       <c r="E6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F6">
-        <v>1.3999999999999986</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="F6" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="8" t="s">
+      <c r="H6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -959,22 +963,22 @@
       <c r="D8" s="7">
         <v>26.9</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="8">
         <v>5</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="8" t="s">
+      <c r="H8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -994,19 +998,19 @@
       <c r="E9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="8">
         <v>4</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="8" t="s">
+      <c r="H9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1026,19 +1030,19 @@
       <c r="E10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="8">
         <v>1.17</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="8" t="s">
+      <c r="H10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1058,19 +1062,19 @@
       <c r="E11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F11">
-        <v>0.21999999999999886</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="F11" s="8">
+        <v>0.22</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="8" t="s">
+      <c r="I11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1090,19 +1094,19 @@
       <c r="E12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="8">
         <v>4</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="8" t="s">
+      <c r="H12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1122,19 +1126,19 @@
       <c r="E13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="8">
         <v>5</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H13" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="8" t="s">
+      <c r="H13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1145,28 +1149,28 @@
       <c r="B14" s="5">
         <v>42.9</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="10" t="s">
         <v>37</v>
       </c>
       <c r="D14" s="7">
         <v>45.9</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="8">
         <v>3</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="8" t="s">
+      <c r="H14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1177,28 +1181,28 @@
       <c r="B15" s="5">
         <v>11.9</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="10" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="7">
         <v>14.9</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="8">
         <v>3</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H15" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="8" t="s">
+      <c r="H15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1218,19 +1222,19 @@
       <c r="E16" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F16">
-        <v>2.9999999999999982</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="F16" s="8">
+        <v>3</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="8" t="s">
+      <c r="H16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1241,28 +1245,28 @@
       <c r="B17" s="5">
         <v>5.7</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="10" t="s">
         <v>46</v>
       </c>
       <c r="D17" s="7">
         <v>7.9</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="8">
         <v>2.2</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="H17" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="8" t="s">
+      <c r="H17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1273,7 +1277,7 @@
       <c r="B18" s="5">
         <v>7.9</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D18" s="7">
@@ -1282,19 +1286,19 @@
       <c r="E18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="8">
         <v>2</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H18" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="8" t="s">
+      <c r="H18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1311,22 +1315,22 @@
       <c r="D19" s="7">
         <v>16.9</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="F19">
-        <v>7.999999999999998</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="F19" s="8">
+        <v>8</v>
+      </c>
+      <c r="G19" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="H19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="8" t="s">
+      <c r="H19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1346,19 +1350,19 @@
       <c r="E20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="8">
         <v>4</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="H20" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="8" t="s">
+      <c r="H20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1392,19 +1396,19 @@
       <c r="E22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="8">
         <v>3</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="H22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="8" t="s">
+      <c r="H22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1424,19 +1428,19 @@
       <c r="E23" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="8">
         <v>4</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="8" t="s">
+      <c r="H23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1456,19 +1460,19 @@
       <c r="E24" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F24">
-        <v>1.9999999999999982</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="F24" s="8">
+        <v>2</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="H24" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="8" t="s">
+      <c r="H24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1479,7 +1483,7 @@
       <c r="B25" s="5">
         <v>18.8</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="10" t="s">
         <v>65</v>
       </c>
       <c r="D25" s="7">
@@ -1488,19 +1492,19 @@
       <c r="E25" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F25">
-        <v>1.0999999999999979</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="F25" s="8">
+        <v>1.1</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="H25" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="8" t="s">
+      <c r="H25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1517,22 +1521,22 @@
       <c r="D26" s="7">
         <v>18.9</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F26">
-        <v>4.099999999999998</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="F26" s="8">
+        <v>4.1</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="H26" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="8" t="s">
+      <c r="H26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1543,28 +1547,28 @@
       <c r="B27" s="5">
         <v>19.7</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="10" t="s">
         <v>71</v>
       </c>
       <c r="D27" s="7">
         <v>24.9</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F27">
-        <v>5.199999999999999</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="F27" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="G27" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="H27" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="8" t="s">
+      <c r="H27" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1581,22 +1585,22 @@
       <c r="D28" s="7">
         <v>26.9</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="8">
         <v>5</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="8" t="s">
+      <c r="H28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1613,22 +1617,22 @@
       <c r="D29" s="7">
         <v>22.9</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F29">
-        <v>7.959999999999999</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="F29" s="8">
+        <v>7.96</v>
+      </c>
+      <c r="G29" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="H29" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="8" t="s">
+      <c r="H29" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1639,28 +1643,28 @@
       <c r="B30" s="5">
         <v>41.5</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="10" t="s">
         <v>80</v>
       </c>
       <c r="D30" s="7">
         <v>48.9</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F30">
-        <v>7.399999999999999</v>
-      </c>
-      <c r="G30" t="s">
+      <c r="F30" s="8">
+        <v>7.4</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="H30" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="8" t="s">
+      <c r="H30" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1694,19 +1698,19 @@
       <c r="E32" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="8">
         <v>3</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="H32" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="8" t="s">
+      <c r="H32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1717,7 +1721,7 @@
       <c r="B33" s="5">
         <v>5.9</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="10" t="s">
         <v>86</v>
       </c>
       <c r="D33" s="7">
@@ -1726,19 +1730,19 @@
       <c r="E33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="8">
         <v>4</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="H33" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="8" t="s">
+      <c r="H33" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1758,19 +1762,19 @@
       <c r="E34" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="8">
         <v>2</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G34" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="H34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="8" t="s">
+      <c r="H34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1790,19 +1794,19 @@
       <c r="E35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="8">
         <v>3</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="H35" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="8" t="s">
+      <c r="H35" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1822,67 +1826,57 @@
       <c r="E36" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="8">
         <v>1</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="H36" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="8" t="s">
+      <c r="H36" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="B37" s="11">
-        <v>494.40999999999985</v>
-      </c>
-      <c r="C37" s="12" t="s">
+      <c r="B37" s="12">
+        <v>494.41</v>
+      </c>
+      <c r="C37" s="13"/>
+      <c r="D37" s="12">
+        <v>593.37</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="12">
+        <v>98.96</v>
+      </c>
+      <c r="G37" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D37" s="11">
-        <v>593.3699999999997</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F37" s="12">
-        <v>98.95999999999981</v>
-      </c>
-      <c r="G37" s="12" t="s">
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+    </row>
+    <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="H37" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="97">
-  <si>
-    <t>מחירי מוצרים - 2026-10-10</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="98">
+  <si>
+    <t>מעקב מחירים יומי — 2026-10-11</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -271,10 +271,10 @@
     <t>עגבניה (ק"ג)</t>
   </si>
   <si>
-    <t>5.90</t>
-  </si>
-  <si>
-    <t>40.4%</t>
+    <t>30.3%</t>
+  </si>
+  <si>
+    <t>⬆ +1.00 ₪</t>
   </si>
   <si>
     <t>מלפפון (ק"ג)</t>
@@ -298,10 +298,13 @@
     <t>סה"כ</t>
   </si>
   <si>
-    <t>16.7%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-10 מול 2026-10-09 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t/>
+  </si>
+  <si>
+    <t>16.5%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-11 מול 2026-10-10 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -333,7 +336,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -368,6 +371,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -407,9 +415,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -417,14 +423,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -770,14 +772,14 @@
   <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="10" width="20" customWidth="1"/>
+    <col min="9" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -859,10 +861,10 @@
       <c r="F4" s="8">
         <v>0.15</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" t="s">
         <v>15</v>
       </c>
       <c r="I4" s="9" t="s">
@@ -891,10 +893,10 @@
       <c r="F5" s="8">
         <v>0.5</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" t="s">
         <v>15</v>
       </c>
       <c r="I5" s="9" t="s">
@@ -923,10 +925,10 @@
       <c r="F6" s="8">
         <v>1.4</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="9" t="s">
@@ -969,10 +971,10 @@
       <c r="F8" s="8">
         <v>5</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" t="s">
         <v>15</v>
       </c>
       <c r="I8" s="9" t="s">
@@ -1001,10 +1003,10 @@
       <c r="F9" s="8">
         <v>4</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" t="s">
         <v>15</v>
       </c>
       <c r="I9" s="9" t="s">
@@ -1033,10 +1035,10 @@
       <c r="F10" s="8">
         <v>1.17</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" t="s">
         <v>15</v>
       </c>
       <c r="I10" s="9" t="s">
@@ -1065,10 +1067,10 @@
       <c r="F11" s="8">
         <v>0.22</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="9" t="s">
@@ -1097,10 +1099,10 @@
       <c r="F12" s="8">
         <v>4</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" t="s">
         <v>15</v>
       </c>
       <c r="I12" s="9" t="s">
@@ -1129,10 +1131,10 @@
       <c r="F13" s="8">
         <v>5</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" t="s">
         <v>15</v>
       </c>
       <c r="I13" s="9" t="s">
@@ -1161,10 +1163,10 @@
       <c r="F14" s="8">
         <v>3</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" t="s">
         <v>39</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" t="s">
         <v>15</v>
       </c>
       <c r="I14" s="9" t="s">
@@ -1193,10 +1195,10 @@
       <c r="F15" s="8">
         <v>3</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" t="s">
         <v>15</v>
       </c>
       <c r="I15" s="9" t="s">
@@ -1225,10 +1227,10 @@
       <c r="F16" s="8">
         <v>3</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="9" t="s">
@@ -1257,10 +1259,10 @@
       <c r="F17" s="8">
         <v>2.2</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="9" t="s">
@@ -1289,10 +1291,10 @@
       <c r="F18" s="8">
         <v>2</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" t="s">
         <v>51</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="9" t="s">
@@ -1321,10 +1323,10 @@
       <c r="F19" s="8">
         <v>8</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" t="s">
         <v>54</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="9" t="s">
@@ -1353,10 +1355,10 @@
       <c r="F20" s="8">
         <v>4</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" t="s">
         <v>56</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="9" t="s">
@@ -1399,10 +1401,10 @@
       <c r="F22" s="8">
         <v>3</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" t="s">
         <v>59</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="9" t="s">
@@ -1431,10 +1433,10 @@
       <c r="F23" s="8">
         <v>4</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" t="s">
         <v>61</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="9" t="s">
@@ -1463,10 +1465,10 @@
       <c r="F24" s="8">
         <v>2</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" t="s">
         <v>63</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="9" t="s">
@@ -1495,10 +1497,10 @@
       <c r="F25" s="8">
         <v>1.1</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" t="s">
         <v>66</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="9" t="s">
@@ -1527,10 +1529,10 @@
       <c r="F26" s="8">
         <v>4.1</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" t="s">
         <v>69</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="9" t="s">
@@ -1559,10 +1561,10 @@
       <c r="F27" s="8">
         <v>5.2</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" t="s">
         <v>73</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="9" t="s">
@@ -1591,10 +1593,10 @@
       <c r="F28" s="8">
         <v>5</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" t="s">
         <v>24</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="H28" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="9" t="s">
@@ -1623,10 +1625,10 @@
       <c r="F29" s="8">
         <v>7.96</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" t="s">
         <v>78</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="H29" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="9" t="s">
@@ -1655,10 +1657,10 @@
       <c r="F30" s="8">
         <v>7.4</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" t="s">
         <v>82</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H30" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="9" t="s">
@@ -1701,10 +1703,10 @@
       <c r="F32" s="8">
         <v>3</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" t="s">
         <v>82</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="H32" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="9" t="s">
@@ -1719,10 +1721,10 @@
         <v>85</v>
       </c>
       <c r="B33" s="5">
-        <v>5.9</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>86</v>
+        <v>6.9</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="D33" s="7">
         <v>9.9</v>
@@ -1731,16 +1733,16 @@
         <v>13</v>
       </c>
       <c r="F33" s="8">
-        <v>4</v>
-      </c>
-      <c r="G33" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" t="s">
+        <v>86</v>
+      </c>
+      <c r="H33" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="11" t="s">
         <v>87</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>16</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>16</v>
@@ -1765,10 +1767,10 @@
       <c r="F34" s="8">
         <v>2</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" t="s">
         <v>89</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="H34" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="9" t="s">
@@ -1797,10 +1799,10 @@
       <c r="F35" s="8">
         <v>3</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" t="s">
         <v>91</v>
       </c>
-      <c r="H35" s="6" t="s">
+      <c r="H35" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="9" t="s">
@@ -1829,10 +1831,10 @@
       <c r="F36" s="8">
         <v>1</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" t="s">
         <v>93</v>
       </c>
-      <c r="H36" s="6" t="s">
+      <c r="H36" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="9" t="s">
@@ -1843,30 +1845,40 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B37" s="12">
-        <v>494.41</v>
-      </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="12">
+      <c r="B37" s="13">
+        <v>495.41</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D37" s="13">
         <v>593.37</v>
       </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="12">
-        <v>98.96</v>
-      </c>
-      <c r="G37" s="13" t="s">
+      <c r="E37" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-    </row>
-    <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F37" s="13">
+        <v>97.96</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="98">
-  <si>
-    <t>מעקב מחירים יומי — 2026-10-11</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="99">
+  <si>
+    <t>מחירי מוצרים - 2026-10-12</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -229,7 +229,7 @@
     <t>17.50 (2 ב-35)</t>
   </si>
   <si>
-    <t>20.00 (2 ב-40)</t>
+    <t>16.67 (3 ב-50)</t>
   </si>
   <si>
     <t>20.9%</t>
@@ -271,10 +271,13 @@
     <t>עגבניה (ק"ג)</t>
   </si>
   <si>
-    <t>30.3%</t>
-  </si>
-  <si>
-    <t>⬆ +1.00 ₪</t>
+    <t>7.90</t>
+  </si>
+  <si>
+    <t>10.1%</t>
+  </si>
+  <si>
+    <t>⬆ +2.00 ₪</t>
   </si>
   <si>
     <t>מלפפון (ק"ג)</t>
@@ -301,10 +304,10 @@
     <t/>
   </si>
   <si>
-    <t>16.5%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-11 מול 2026-10-10 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>16.2%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-12 מול 2026-10-11 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -396,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -410,12 +413,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -425,8 +434,16 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -772,13 +789,13 @@
   <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -861,10 +878,10 @@
       <c r="F4" s="8">
         <v>0.15</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I4" s="9" t="s">
@@ -893,10 +910,10 @@
       <c r="F5" s="8">
         <v>0.5</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I5" s="9" t="s">
@@ -925,10 +942,10 @@
       <c r="F6" s="8">
         <v>1.4</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="9" t="s">
@@ -971,10 +988,10 @@
       <c r="F8" s="8">
         <v>5</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I8" s="9" t="s">
@@ -1003,10 +1020,10 @@
       <c r="F9" s="8">
         <v>4</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I9" s="9" t="s">
@@ -1035,10 +1052,10 @@
       <c r="F10" s="8">
         <v>1.17</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I10" s="9" t="s">
@@ -1067,10 +1084,10 @@
       <c r="F11" s="8">
         <v>0.22</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="9" t="s">
@@ -1099,10 +1116,10 @@
       <c r="F12" s="8">
         <v>4</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I12" s="9" t="s">
@@ -1131,10 +1148,10 @@
       <c r="F13" s="8">
         <v>5</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I13" s="9" t="s">
@@ -1163,10 +1180,10 @@
       <c r="F14" s="8">
         <v>3</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I14" s="9" t="s">
@@ -1195,10 +1212,10 @@
       <c r="F15" s="8">
         <v>3</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I15" s="9" t="s">
@@ -1227,10 +1244,10 @@
       <c r="F16" s="8">
         <v>3</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="9" t="s">
@@ -1259,10 +1276,10 @@
       <c r="F17" s="8">
         <v>2.2</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="9" t="s">
@@ -1291,10 +1308,10 @@
       <c r="F18" s="8">
         <v>2</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="9" t="s">
@@ -1323,10 +1340,10 @@
       <c r="F19" s="8">
         <v>8</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="9" t="s">
@@ -1355,10 +1372,10 @@
       <c r="F20" s="8">
         <v>4</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="9" t="s">
@@ -1401,10 +1418,10 @@
       <c r="F22" s="8">
         <v>3</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="9" t="s">
@@ -1433,10 +1450,10 @@
       <c r="F23" s="8">
         <v>4</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="9" t="s">
@@ -1465,10 +1482,10 @@
       <c r="F24" s="8">
         <v>2</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="9" t="s">
@@ -1497,10 +1514,10 @@
       <c r="F25" s="8">
         <v>1.1</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="9" t="s">
@@ -1529,10 +1546,10 @@
       <c r="F26" s="8">
         <v>4.1</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="9" t="s">
@@ -1561,10 +1578,10 @@
       <c r="F27" s="8">
         <v>5.2</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="9" t="s">
@@ -1593,10 +1610,10 @@
       <c r="F28" s="8">
         <v>5</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="9" t="s">
@@ -1625,10 +1642,10 @@
       <c r="F29" s="8">
         <v>7.96</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="9" t="s">
@@ -1657,10 +1674,10 @@
       <c r="F30" s="8">
         <v>7.4</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="9" t="s">
@@ -1703,10 +1720,10 @@
       <c r="F32" s="8">
         <v>3</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="9" t="s">
@@ -1721,10 +1738,10 @@
         <v>85</v>
       </c>
       <c r="B33" s="5">
-        <v>6.9</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>13</v>
+        <v>8.9</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="D33" s="7">
         <v>9.9</v>
@@ -1733,16 +1750,16 @@
         <v>13</v>
       </c>
       <c r="F33" s="8">
-        <v>3</v>
-      </c>
-      <c r="G33" t="s">
-        <v>86</v>
-      </c>
-      <c r="H33" t="s">
+        <v>1</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>16</v>
@@ -1750,7 +1767,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B34" s="5">
         <v>6.9</v>
@@ -1767,10 +1784,10 @@
       <c r="F34" s="8">
         <v>2</v>
       </c>
-      <c r="G34" t="s">
-        <v>89</v>
-      </c>
-      <c r="H34" t="s">
+      <c r="G34" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="9" t="s">
@@ -1782,7 +1799,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B35" s="5">
         <v>9.9</v>
@@ -1799,10 +1816,10 @@
       <c r="F35" s="8">
         <v>3</v>
       </c>
-      <c r="G35" t="s">
-        <v>91</v>
-      </c>
-      <c r="H35" t="s">
+      <c r="G35" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H35" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="9" t="s">
@@ -1814,7 +1831,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B36" s="5">
         <v>4.9</v>
@@ -1831,10 +1848,10 @@
       <c r="F36" s="8">
         <v>1</v>
       </c>
-      <c r="G36" t="s">
-        <v>93</v>
-      </c>
-      <c r="H36" t="s">
+      <c r="G36" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="9" t="s">
@@ -1846,49 +1863,49 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B37" s="13">
-        <v>495.41</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>95</v>
+        <v>497.41</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="D37" s="13">
         <v>593.37</v>
       </c>
-      <c r="E37" s="12" t="s">
-        <v>95</v>
+      <c r="E37" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="F37" s="13">
-        <v>97.96</v>
-      </c>
-      <c r="G37" s="12" t="s">
+        <v>95.96</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="H37" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
+      <c r="J37" s="14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="99">
-  <si>
-    <t>מחירי מוצרים - 2026-10-12</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="99">
+  <si>
+    <t>מעקב מחירים יומי — 2026-10-13</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -268,22 +268,22 @@
     <t>תפוח עץ פינק ליידי 1 ק"ג</t>
   </si>
   <si>
+    <t>⬇ -1.00 ₪</t>
+  </si>
+  <si>
     <t>עגבניה (ק"ג)</t>
   </si>
   <si>
-    <t>7.90</t>
+    <t>6.90</t>
   </si>
   <si>
     <t>10.1%</t>
   </si>
   <si>
-    <t>⬆ +2.00 ₪</t>
-  </si>
-  <si>
     <t>מלפפון (ק"ג)</t>
   </si>
   <si>
-    <t>22.5%</t>
+    <t>33.7%</t>
   </si>
   <si>
     <t>בננות (ק"ג)</t>
@@ -304,10 +304,10 @@
     <t/>
   </si>
   <si>
-    <t>16.2%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-12 מול 2026-10-11 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>16.5%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-13 מול 2026-10-12 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -378,7 +378,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -399,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -413,16 +413,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -437,10 +434,6 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -789,17 +782,18 @@
   <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -875,7 +869,7 @@
       <c r="E4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="6">
         <v>0.15</v>
       </c>
       <c r="G4" s="6" t="s">
@@ -884,10 +878,10 @@
       <c r="H4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="9" t="s">
+      <c r="I4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -907,7 +901,7 @@
       <c r="E5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="6">
         <v>0.5</v>
       </c>
       <c r="G5" s="6" t="s">
@@ -916,10 +910,10 @@
       <c r="H5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="9" t="s">
+      <c r="I5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -939,7 +933,7 @@
       <c r="E6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="6">
         <v>1.4</v>
       </c>
       <c r="G6" s="6" t="s">
@@ -948,10 +942,10 @@
       <c r="H6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="9" t="s">
+      <c r="I6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -982,10 +976,10 @@
       <c r="D8" s="7">
         <v>26.9</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="6">
         <v>5</v>
       </c>
       <c r="G8" s="6" t="s">
@@ -994,10 +988,10 @@
       <c r="H8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="9" t="s">
+      <c r="I8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1017,7 +1011,7 @@
       <c r="E9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="6">
         <v>4</v>
       </c>
       <c r="G9" s="6" t="s">
@@ -1026,10 +1020,10 @@
       <c r="H9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="9" t="s">
+      <c r="I9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1049,7 +1043,7 @@
       <c r="E10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="6">
         <v>1.17</v>
       </c>
       <c r="G10" s="6" t="s">
@@ -1058,10 +1052,10 @@
       <c r="H10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="9" t="s">
+      <c r="I10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1081,7 +1075,7 @@
       <c r="E11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="6">
         <v>0.22</v>
       </c>
       <c r="G11" s="6" t="s">
@@ -1090,10 +1084,10 @@
       <c r="H11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="9" t="s">
+      <c r="I11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1113,7 +1107,7 @@
       <c r="E12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="6">
         <v>4</v>
       </c>
       <c r="G12" s="6" t="s">
@@ -1122,10 +1116,10 @@
       <c r="H12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="9" t="s">
+      <c r="I12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1145,7 +1139,7 @@
       <c r="E13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="6">
         <v>5</v>
       </c>
       <c r="G13" s="6" t="s">
@@ -1154,10 +1148,10 @@
       <c r="H13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="9" t="s">
+      <c r="I13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1168,16 +1162,16 @@
       <c r="B14" s="5">
         <v>42.9</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D14" s="7">
         <v>45.9</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="6">
         <v>3</v>
       </c>
       <c r="G14" s="6" t="s">
@@ -1186,10 +1180,10 @@
       <c r="H14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="9" t="s">
+      <c r="I14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1200,16 +1194,16 @@
       <c r="B15" s="5">
         <v>11.9</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="7">
         <v>14.9</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="6">
         <v>3</v>
       </c>
       <c r="G15" s="6" t="s">
@@ -1218,10 +1212,10 @@
       <c r="H15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="9" t="s">
+      <c r="I15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1241,7 +1235,7 @@
       <c r="E16" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="6">
         <v>3</v>
       </c>
       <c r="G16" s="6" t="s">
@@ -1250,10 +1244,10 @@
       <c r="H16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="9" t="s">
+      <c r="I16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1264,16 +1258,16 @@
       <c r="B17" s="5">
         <v>5.7</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="9" t="s">
         <v>46</v>
       </c>
       <c r="D17" s="7">
         <v>7.9</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="6">
         <v>2.2</v>
       </c>
       <c r="G17" s="6" t="s">
@@ -1282,10 +1276,10 @@
       <c r="H17" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="9" t="s">
+      <c r="I17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1296,7 +1290,7 @@
       <c r="B18" s="5">
         <v>7.9</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>50</v>
       </c>
       <c r="D18" s="7">
@@ -1305,7 +1299,7 @@
       <c r="E18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="6">
         <v>2</v>
       </c>
       <c r="G18" s="6" t="s">
@@ -1314,10 +1308,10 @@
       <c r="H18" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I18" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="9" t="s">
+      <c r="I18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1334,10 +1328,10 @@
       <c r="D19" s="7">
         <v>16.9</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="6">
         <v>8</v>
       </c>
       <c r="G19" s="6" t="s">
@@ -1346,10 +1340,10 @@
       <c r="H19" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="9" t="s">
+      <c r="I19" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1369,7 +1363,7 @@
       <c r="E20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="6">
         <v>4</v>
       </c>
       <c r="G20" s="6" t="s">
@@ -1378,10 +1372,10 @@
       <c r="H20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="9" t="s">
+      <c r="I20" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1415,7 +1409,7 @@
       <c r="E22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="6">
         <v>3</v>
       </c>
       <c r="G22" s="6" t="s">
@@ -1424,10 +1418,10 @@
       <c r="H22" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="9" t="s">
+      <c r="I22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1447,7 +1441,7 @@
       <c r="E23" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="6">
         <v>4</v>
       </c>
       <c r="G23" s="6" t="s">
@@ -1456,10 +1450,10 @@
       <c r="H23" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I23" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="9" t="s">
+      <c r="I23" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1479,7 +1473,7 @@
       <c r="E24" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="6">
         <v>2</v>
       </c>
       <c r="G24" s="6" t="s">
@@ -1488,10 +1482,10 @@
       <c r="H24" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I24" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="9" t="s">
+      <c r="I24" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1502,7 +1496,7 @@
       <c r="B25" s="5">
         <v>18.8</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D25" s="7">
@@ -1511,7 +1505,7 @@
       <c r="E25" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="6">
         <v>1.1</v>
       </c>
       <c r="G25" s="6" t="s">
@@ -1520,10 +1514,10 @@
       <c r="H25" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="9" t="s">
+      <c r="I25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1540,10 +1534,10 @@
       <c r="D26" s="7">
         <v>18.9</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="6">
         <v>4.1</v>
       </c>
       <c r="G26" s="6" t="s">
@@ -1552,10 +1546,10 @@
       <c r="H26" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I26" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="9" t="s">
+      <c r="I26" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1566,16 +1560,16 @@
       <c r="B27" s="5">
         <v>19.7</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="9" t="s">
         <v>71</v>
       </c>
       <c r="D27" s="7">
         <v>24.9</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="6">
         <v>5.2</v>
       </c>
       <c r="G27" s="6" t="s">
@@ -1584,10 +1578,10 @@
       <c r="H27" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I27" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="9" t="s">
+      <c r="I27" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1604,10 +1598,10 @@
       <c r="D28" s="7">
         <v>26.9</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="6">
         <v>5</v>
       </c>
       <c r="G28" s="6" t="s">
@@ -1616,10 +1610,10 @@
       <c r="H28" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I28" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="9" t="s">
+      <c r="I28" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1636,10 +1630,10 @@
       <c r="D29" s="7">
         <v>22.9</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="6">
         <v>7.96</v>
       </c>
       <c r="G29" s="6" t="s">
@@ -1648,10 +1642,10 @@
       <c r="H29" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="9" t="s">
+      <c r="I29" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1662,16 +1656,16 @@
       <c r="B30" s="5">
         <v>41.5</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="9" t="s">
         <v>80</v>
       </c>
       <c r="D30" s="7">
         <v>48.9</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="6">
         <v>7.4</v>
       </c>
       <c r="G30" s="6" t="s">
@@ -1680,10 +1674,10 @@
       <c r="H30" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="9" t="s">
+      <c r="I30" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1706,7 +1700,7 @@
         <v>84</v>
       </c>
       <c r="B32" s="5">
-        <v>16.9</v>
+        <v>15.9</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>13</v>
@@ -1717,31 +1711,31 @@
       <c r="E32" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="8">
-        <v>3</v>
+      <c r="F32" s="6">
+        <v>4</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I32" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="9" t="s">
+      <c r="I32" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="J32" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B33" s="5">
         <v>8.9</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>86</v>
+      <c r="C33" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="D33" s="7">
         <v>9.9</v>
@@ -1749,19 +1743,19 @@
       <c r="E33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="6">
         <v>1</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="J33" s="9" t="s">
+      <c r="I33" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1770,7 +1764,7 @@
         <v>89</v>
       </c>
       <c r="B34" s="5">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>13</v>
@@ -1781,8 +1775,8 @@
       <c r="E34" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F34" s="8">
-        <v>2</v>
+      <c r="F34" s="6">
+        <v>3</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>90</v>
@@ -1790,10 +1784,10 @@
       <c r="H34" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I34" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="9" t="s">
+      <c r="I34" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="J34" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1813,7 +1807,7 @@
       <c r="E35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="6">
         <v>3</v>
       </c>
       <c r="G35" s="6" t="s">
@@ -1822,10 +1816,10 @@
       <c r="H35" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I35" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="9" t="s">
+      <c r="I35" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1845,7 +1839,7 @@
       <c r="E36" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="6">
         <v>1</v>
       </c>
       <c r="G36" s="6" t="s">
@@ -1854,58 +1848,54 @@
       <c r="H36" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I36" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="9" t="s">
+      <c r="I36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="B37" s="13">
-        <v>497.41</v>
-      </c>
-      <c r="C37" s="14" t="s">
+      <c r="B37" s="12">
+        <v>495.41</v>
+      </c>
+      <c r="C37" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D37" s="13">
+      <c r="D37" s="12">
         <v>593.37</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F37" s="13">
-        <v>95.96</v>
-      </c>
-      <c r="G37" s="15" t="s">
+      <c r="F37" s="12">
+        <v>97.96</v>
+      </c>
+      <c r="G37" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="H37" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>96</v>
-      </c>
+      <c r="H37" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
     </row>
     <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="99">
-  <si>
-    <t>מעקב מחירים יומי — 2026-10-13</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="97">
+  <si>
+    <t>מחירי מוצרים - 2026-10-14</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -268,9 +268,6 @@
     <t>תפוח עץ פינק ליידי 1 ק"ג</t>
   </si>
   <si>
-    <t>⬇ -1.00 ₪</t>
-  </si>
-  <si>
     <t>עגבניה (ק"ג)</t>
   </si>
   <si>
@@ -301,13 +298,10 @@
     <t>סה"כ</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>16.5%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-13 מול 2026-10-12 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-14 מול 2026-10-13 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -339,7 +333,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -378,11 +372,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -399,7 +388,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -413,13 +402,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -429,12 +417,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -787,10 +775,9 @@
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="10" width="22" customWidth="1"/>
+    <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -869,7 +856,7 @@
       <c r="E4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="8">
         <v>0.15</v>
       </c>
       <c r="G4" s="6" t="s">
@@ -878,10 +865,10 @@
       <c r="H4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="8" t="s">
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -901,7 +888,7 @@
       <c r="E5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="8">
         <v>0.5</v>
       </c>
       <c r="G5" s="6" t="s">
@@ -910,10 +897,10 @@
       <c r="H5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="8" t="s">
+      <c r="I5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -933,7 +920,7 @@
       <c r="E6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="8">
         <v>1.4</v>
       </c>
       <c r="G6" s="6" t="s">
@@ -942,10 +929,10 @@
       <c r="H6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="8" t="s">
+      <c r="I6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -976,10 +963,10 @@
       <c r="D8" s="7">
         <v>26.9</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="8">
         <v>5</v>
       </c>
       <c r="G8" s="6" t="s">
@@ -988,10 +975,10 @@
       <c r="H8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="8" t="s">
+      <c r="I8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1011,7 +998,7 @@
       <c r="E9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="8">
         <v>4</v>
       </c>
       <c r="G9" s="6" t="s">
@@ -1020,10 +1007,10 @@
       <c r="H9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="8" t="s">
+      <c r="I9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1043,7 +1030,7 @@
       <c r="E10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="8">
         <v>1.17</v>
       </c>
       <c r="G10" s="6" t="s">
@@ -1052,10 +1039,10 @@
       <c r="H10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="8" t="s">
+      <c r="I10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1075,7 +1062,7 @@
       <c r="E11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="8">
         <v>0.22</v>
       </c>
       <c r="G11" s="6" t="s">
@@ -1084,10 +1071,10 @@
       <c r="H11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="8" t="s">
+      <c r="I11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1107,7 +1094,7 @@
       <c r="E12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="8">
         <v>4</v>
       </c>
       <c r="G12" s="6" t="s">
@@ -1116,10 +1103,10 @@
       <c r="H12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="8" t="s">
+      <c r="I12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1139,7 +1126,7 @@
       <c r="E13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="8">
         <v>5</v>
       </c>
       <c r="G13" s="6" t="s">
@@ -1148,10 +1135,10 @@
       <c r="H13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="8" t="s">
+      <c r="I13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1162,16 +1149,16 @@
       <c r="B14" s="5">
         <v>42.9</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="10" t="s">
         <v>37</v>
       </c>
       <c r="D14" s="7">
         <v>45.9</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="8">
         <v>3</v>
       </c>
       <c r="G14" s="6" t="s">
@@ -1180,10 +1167,10 @@
       <c r="H14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="8" t="s">
+      <c r="I14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1194,16 +1181,16 @@
       <c r="B15" s="5">
         <v>11.9</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="10" t="s">
         <v>41</v>
       </c>
       <c r="D15" s="7">
         <v>14.9</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="8">
         <v>3</v>
       </c>
       <c r="G15" s="6" t="s">
@@ -1212,10 +1199,10 @@
       <c r="H15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="8" t="s">
+      <c r="I15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1235,7 +1222,7 @@
       <c r="E16" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="8">
         <v>3</v>
       </c>
       <c r="G16" s="6" t="s">
@@ -1244,10 +1231,10 @@
       <c r="H16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="8" t="s">
+      <c r="I16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1258,16 +1245,16 @@
       <c r="B17" s="5">
         <v>5.7</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="10" t="s">
         <v>46</v>
       </c>
       <c r="D17" s="7">
         <v>7.9</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="8">
         <v>2.2</v>
       </c>
       <c r="G17" s="6" t="s">
@@ -1276,10 +1263,10 @@
       <c r="H17" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="8" t="s">
+      <c r="I17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1290,7 +1277,7 @@
       <c r="B18" s="5">
         <v>7.9</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>50</v>
       </c>
       <c r="D18" s="7">
@@ -1299,7 +1286,7 @@
       <c r="E18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="8">
         <v>2</v>
       </c>
       <c r="G18" s="6" t="s">
@@ -1308,10 +1295,10 @@
       <c r="H18" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I18" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="8" t="s">
+      <c r="I18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1328,10 +1315,10 @@
       <c r="D19" s="7">
         <v>16.9</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="8">
         <v>8</v>
       </c>
       <c r="G19" s="6" t="s">
@@ -1340,10 +1327,10 @@
       <c r="H19" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="8" t="s">
+      <c r="I19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1363,7 +1350,7 @@
       <c r="E20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="8">
         <v>4</v>
       </c>
       <c r="G20" s="6" t="s">
@@ -1372,10 +1359,10 @@
       <c r="H20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="8" t="s">
+      <c r="I20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1409,7 +1396,7 @@
       <c r="E22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="8">
         <v>3</v>
       </c>
       <c r="G22" s="6" t="s">
@@ -1418,10 +1405,10 @@
       <c r="H22" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="8" t="s">
+      <c r="I22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1441,7 +1428,7 @@
       <c r="E23" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="8">
         <v>4</v>
       </c>
       <c r="G23" s="6" t="s">
@@ -1450,10 +1437,10 @@
       <c r="H23" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I23" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="8" t="s">
+      <c r="I23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1473,7 +1460,7 @@
       <c r="E24" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="8">
         <v>2</v>
       </c>
       <c r="G24" s="6" t="s">
@@ -1482,10 +1469,10 @@
       <c r="H24" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I24" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="8" t="s">
+      <c r="I24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1496,7 +1483,7 @@
       <c r="B25" s="5">
         <v>18.8</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="10" t="s">
         <v>65</v>
       </c>
       <c r="D25" s="7">
@@ -1505,7 +1492,7 @@
       <c r="E25" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="8">
         <v>1.1</v>
       </c>
       <c r="G25" s="6" t="s">
@@ -1514,10 +1501,10 @@
       <c r="H25" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="8" t="s">
+      <c r="I25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1534,10 +1521,10 @@
       <c r="D26" s="7">
         <v>18.9</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="8">
         <v>4.1</v>
       </c>
       <c r="G26" s="6" t="s">
@@ -1546,10 +1533,10 @@
       <c r="H26" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I26" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="8" t="s">
+      <c r="I26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1560,16 +1547,16 @@
       <c r="B27" s="5">
         <v>19.7</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="10" t="s">
         <v>71</v>
       </c>
       <c r="D27" s="7">
         <v>24.9</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="8">
         <v>5.2</v>
       </c>
       <c r="G27" s="6" t="s">
@@ -1578,10 +1565,10 @@
       <c r="H27" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I27" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="8" t="s">
+      <c r="I27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1598,10 +1585,10 @@
       <c r="D28" s="7">
         <v>26.9</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="8">
         <v>5</v>
       </c>
       <c r="G28" s="6" t="s">
@@ -1610,10 +1597,10 @@
       <c r="H28" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I28" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="8" t="s">
+      <c r="I28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1630,10 +1617,10 @@
       <c r="D29" s="7">
         <v>22.9</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="8">
         <v>7.96</v>
       </c>
       <c r="G29" s="6" t="s">
@@ -1642,10 +1629,10 @@
       <c r="H29" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I29" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="8" t="s">
+      <c r="I29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1656,16 +1643,16 @@
       <c r="B30" s="5">
         <v>41.5</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="10" t="s">
         <v>80</v>
       </c>
       <c r="D30" s="7">
         <v>48.9</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="8">
         <v>7.4</v>
       </c>
       <c r="G30" s="6" t="s">
@@ -1674,10 +1661,10 @@
       <c r="H30" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I30" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="8" t="s">
+      <c r="I30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1711,7 +1698,7 @@
       <c r="E32" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="8">
         <v>4</v>
       </c>
       <c r="G32" s="6" t="s">
@@ -1720,22 +1707,22 @@
       <c r="H32" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I32" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="J32" s="8" t="s">
+      <c r="I32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B33" s="5">
         <v>8.9</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>87</v>
+      <c r="C33" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="D33" s="7">
         <v>9.9</v>
@@ -1743,25 +1730,25 @@
       <c r="E33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="8">
         <v>1</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="8" t="s">
+      <c r="I33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B34" s="5">
         <v>5.9</v>
@@ -1775,25 +1762,25 @@
       <c r="E34" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="8">
         <v>3</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I34" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="J34" s="8" t="s">
+      <c r="I34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B35" s="5">
         <v>9.9</v>
@@ -1807,25 +1794,25 @@
       <c r="E35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="8">
         <v>3</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I35" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="8" t="s">
+      <c r="I35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B36" s="5">
         <v>4.9</v>
@@ -1839,63 +1826,59 @@
       <c r="E36" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="8">
         <v>1</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I36" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="8" t="s">
+      <c r="I36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B37" s="12">
         <v>495.41</v>
       </c>
-      <c r="C37" s="12" t="s">
-        <v>96</v>
-      </c>
+      <c r="C37" s="13"/>
       <c r="D37" s="12">
         <v>593.37</v>
       </c>
-      <c r="E37" s="12" t="s">
-        <v>96</v>
-      </c>
+      <c r="E37" s="13"/>
       <c r="F37" s="12">
         <v>97.96</v>
       </c>
-      <c r="G37" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-    </row>
-    <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
+      <c r="G37" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="97">
-  <si>
-    <t>מחירי מוצרים - 2026-10-14</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="97">
+  <si>
+    <t>מחירי מוצרים - 2026-10-15</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -151,7 +151,7 @@
     <t>ספגטי אסם 500 גרם</t>
   </si>
   <si>
-    <t>4.50 (4 ב-18)</t>
+    <t>4.00 (5 ב-20)</t>
   </si>
   <si>
     <t>6.00 (3 ב-18)</t>
@@ -181,6 +181,9 @@
     <t>רביולי גבינה קלאסי שטראוס 400 גרם</t>
   </si>
   <si>
+    <t>12.90</t>
+  </si>
+  <si>
     <t>17.5%</t>
   </si>
   <si>
@@ -190,9 +193,6 @@
     <t>מגבות נייר ניקול 6 גלילים</t>
   </si>
   <si>
-    <t>21.6%</t>
-  </si>
-  <si>
     <t>נייר טואלט לילי פסטל 32 גלילים</t>
   </si>
   <si>
@@ -226,9 +226,6 @@
     <t>מגבוני האגיס ללא בישום 4X56</t>
   </si>
   <si>
-    <t>17.50 (2 ב-35)</t>
-  </si>
-  <si>
     <t>16.67 (3 ב-50)</t>
   </si>
   <si>
@@ -298,10 +295,13 @@
     <t>סה"כ</t>
   </si>
   <si>
-    <t>16.5%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-14 מול 2026-10-13 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t/>
+  </si>
+  <si>
+    <t>18.3%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-15 מול 2026-10-14 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -333,7 +333,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -372,6 +372,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -388,13 +393,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -407,22 +412,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -770,17 +773,17 @@
   <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="10" width="20" customWidth="1"/>
+    <col min="9" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -794,7 +797,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1341,8 +1344,8 @@
       <c r="B20" s="5">
         <v>18.9</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>13</v>
+      <c r="C20" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="D20" s="7">
         <v>22.9</v>
@@ -1354,7 +1357,7 @@
         <v>4</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>15</v>
@@ -1368,7 +1371,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1382,32 +1385,20 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="5">
-        <v>10.9</v>
+        <v>59</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="11">
         <v>13.9</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="8">
-        <v>3</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
       <c r="J22" s="9" t="s">
         <v>16</v>
       </c>
@@ -1548,19 +1539,19 @@
         <v>19.7</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D27" s="7">
         <v>24.9</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F27" s="8">
         <v>5.2</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>15</v>
@@ -1574,7 +1565,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B28" s="5">
         <v>21.9</v>
@@ -1586,7 +1577,7 @@
         <v>26.9</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F28" s="8">
         <v>5</v>
@@ -1606,7 +1597,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" s="5">
         <v>14.94</v>
@@ -1618,13 +1609,13 @@
         <v>22.9</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F29" s="8">
         <v>7.96</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>15</v>
@@ -1638,25 +1629,25 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B30" s="5">
         <v>41.5</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D30" s="7">
         <v>48.9</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F30" s="8">
         <v>7.4</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>15</v>
@@ -1670,7 +1661,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1684,7 +1675,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B32" s="5">
         <v>15.9</v>
@@ -1716,13 +1707,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B33" s="5">
         <v>8.9</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D33" s="7">
         <v>9.9</v>
@@ -1734,7 +1725,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>15</v>
@@ -1748,7 +1739,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B34" s="5">
         <v>5.9</v>
@@ -1766,7 +1757,7 @@
         <v>3</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>15</v>
@@ -1780,7 +1771,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B35" s="5">
         <v>9.9</v>
@@ -1798,7 +1789,7 @@
         <v>3</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>15</v>
@@ -1812,7 +1803,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B36" s="5">
         <v>4.9</v>
@@ -1830,55 +1821,63 @@
         <v>1</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="H36" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
+      <c r="B37" s="13">
+        <v>484.51</v>
+      </c>
+      <c r="C37" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="B37" s="12">
-        <v>495.41</v>
-      </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="12">
+      <c r="D37" s="13">
         <v>593.37</v>
       </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="12">
-        <v>97.96</v>
-      </c>
-      <c r="G37" s="13" t="s">
+      <c r="E37" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F37" s="13">
+        <v>108.86</v>
+      </c>
+      <c r="G37" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="H37" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+      <c r="H37" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="97">
-  <si>
-    <t>מחירי מוצרים - 2026-10-15</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="97">
+  <si>
+    <t>מחירי מוצרים - 2026-10-16</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -301,7 +301,7 @@
     <t>18.3%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-15 מול 2026-10-14 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-16 מול 2026-10-15 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -393,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -404,30 +404,14 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -844,98 +828,98 @@
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>7.2</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="7">
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="5">
         <v>7.35</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="8">
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="6">
         <v>0.15</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="9" t="s">
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>5.9</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="7">
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="5">
         <v>6.4</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="8">
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="6">
         <v>0.5</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="9" t="s">
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>19.5</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="7">
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="5">
         <v>20.9</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="8">
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="6">
         <v>1.4</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="9" t="s">
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -954,418 +938,418 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>21.9</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="5">
         <v>26.9</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="6">
         <v>5</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="9" t="s">
+      <c r="H8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>35.9</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="5">
         <v>39.9</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="8">
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="6">
         <v>4</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="9" t="s">
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>13.07</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="5">
         <v>14.24</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="8">
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="6">
         <v>1.17</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="9" t="s">
+      <c r="H10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="5">
         <v>8.2</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4">
         <v>7.98</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="8">
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="6">
         <v>0.22</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="9" t="s">
+      <c r="I11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>9.9</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="5">
         <v>13.9</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="8">
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="6">
         <v>4</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="9" t="s">
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="4">
         <v>19.9</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="5">
         <v>24.9</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="8">
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="6">
         <v>5</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="9" t="s">
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>42.9</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="5">
         <v>45.9</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="6">
         <v>3</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" t="s">
         <v>39</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="9" t="s">
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="A15" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <v>11.9</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="5">
         <v>14.9</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="6">
         <v>3</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="9" t="s">
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>13.9</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="7">
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="5">
         <v>16.9</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="8">
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="6">
         <v>3</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="9" t="s">
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>5.7</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="5">
         <v>7.9</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="6">
         <v>2.2</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="9" t="s">
+      <c r="H17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="A18" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>7.9</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="5">
         <v>9.9</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="8">
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="6">
         <v>2</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" t="s">
         <v>51</v>
       </c>
-      <c r="H18" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="9" t="s">
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="A19" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>8.9</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="7">
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="5">
         <v>16.9</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="6">
         <v>8</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" t="s">
         <v>54</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="9" t="s">
+      <c r="H19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="A20" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>18.9</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="5">
         <v>22.9</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="8">
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="6">
         <v>4</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="9" t="s">
+      <c r="H20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1384,278 +1368,275 @@
       <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="A22" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="11">
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="9">
         <v>13.9</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="9" t="s">
+      <c r="E22" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="A23" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="4">
         <v>39.9</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="7">
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="5">
         <v>43.9</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="8">
+      <c r="E23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="6">
         <v>4</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" t="s">
         <v>61</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="9" t="s">
+      <c r="H23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="A24" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="4">
         <v>15.9</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="7">
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="5">
         <v>17.9</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="8">
+      <c r="E24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="6">
         <v>2</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" t="s">
         <v>63</v>
       </c>
-      <c r="H24" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="9" t="s">
+      <c r="H24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="4">
         <v>18.8</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="5">
         <v>19.9</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="8">
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="6">
         <v>1.1</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" t="s">
         <v>66</v>
       </c>
-      <c r="H25" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="9" t="s">
+      <c r="H25" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="A26" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="4">
         <v>14.8</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="7">
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="5">
         <v>18.9</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="6">
         <v>4.1</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" t="s">
         <v>69</v>
       </c>
-      <c r="H26" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="9" t="s">
+      <c r="H26" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="A27" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="4">
         <v>19.7</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="5">
         <v>24.9</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="6">
         <v>5.2</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" t="s">
         <v>72</v>
       </c>
-      <c r="H27" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="9" t="s">
+      <c r="H27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="A28" t="s">
         <v>73</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="4">
         <v>21.9</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="7">
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="5">
         <v>26.9</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="6">
         <v>5</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" t="s">
         <v>24</v>
       </c>
-      <c r="H28" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="9" t="s">
+      <c r="H28" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="A29" t="s">
         <v>75</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="4">
         <v>14.94</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="7">
+      <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="5">
         <v>22.9</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="6">
         <v>7.96</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" t="s">
         <v>77</v>
       </c>
-      <c r="H29" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="9" t="s">
+      <c r="H29" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="A30" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="4">
         <v>41.5</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="5">
         <v>48.9</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="6">
         <v>7.4</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" t="s">
         <v>81</v>
       </c>
-      <c r="H30" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="9" t="s">
+      <c r="H30" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1674,210 +1655,206 @@
       <c r="J31" s="3"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="A32" t="s">
         <v>83</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="4">
         <v>15.9</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="7">
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="5">
         <v>19.9</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="8">
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="6">
         <v>4</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" t="s">
         <v>35</v>
       </c>
-      <c r="H32" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="9" t="s">
+      <c r="H32" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+      <c r="A33" t="s">
         <v>84</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="4">
         <v>8.9</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="5">
         <v>9.9</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="8">
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="6">
         <v>1</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" t="s">
         <v>86</v>
       </c>
-      <c r="H33" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="9" t="s">
+      <c r="H33" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="A34" t="s">
         <v>87</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="4">
         <v>5.9</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="7">
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="5">
         <v>8.9</v>
       </c>
-      <c r="E34" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="8">
+      <c r="E34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="6">
         <v>3</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" t="s">
         <v>88</v>
       </c>
-      <c r="H34" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="9" t="s">
+      <c r="H34" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="A35" t="s">
         <v>89</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="4">
         <v>9.9</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="7">
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="5">
         <v>12.9</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="8">
+      <c r="E35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="6">
         <v>3</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" t="s">
         <v>90</v>
       </c>
-      <c r="H35" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="9" t="s">
+      <c r="H35" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="A36" t="s">
         <v>91</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="4">
         <v>4.9</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="7">
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="5">
         <v>5.9</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="8">
+      <c r="E36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="6">
         <v>1</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" t="s">
         <v>92</v>
       </c>
-      <c r="H36" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="9" t="s">
+      <c r="H36" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="11">
         <v>484.51</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="D37" s="13">
+      <c r="D37" s="11">
         <v>593.37</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="11">
         <v>108.86</v>
       </c>
-      <c r="G37" s="15" t="s">
+      <c r="G37" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="H37" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
+      <c r="H37" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="67">
-  <si>
-    <t>מעקב מחירי מוצרים - 2026-10-17</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="94">
+  <si>
+    <t>מעקב מחירים יומי — 2026-10-18</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -55,6 +55,9 @@
     <t>—</t>
   </si>
   <si>
+    <t>2.0%</t>
+  </si>
+  <si>
     <t>אושר עד</t>
   </si>
   <si>
@@ -64,9 +67,15 @@
     <t>קוטג' תנובה 5% 250 גרם</t>
   </si>
   <si>
+    <t>7.8%</t>
+  </si>
+  <si>
     <t>גבינה צהובה 9% פרוסות 200 גרם</t>
   </si>
   <si>
+    <t>6.7%</t>
+  </si>
+  <si>
     <t>מאכל ושתיה סגורים</t>
   </si>
   <si>
@@ -76,24 +85,42 @@
     <t>23.00 (2 ב-46)</t>
   </si>
   <si>
+    <t>18.6%</t>
+  </si>
+  <si>
     <t>קפה נמס טסטרס צויס 200 גרם</t>
   </si>
   <si>
+    <t>10.0%</t>
+  </si>
+  <si>
     <t>ביצים L (מנורמל ל-12 יח')</t>
   </si>
   <si>
+    <t>8.2%</t>
+  </si>
+  <si>
     <t>קוקה קולה זירו 1.5 ליטר</t>
   </si>
   <si>
+    <t>2.7%</t>
+  </si>
+  <si>
     <t>שופרסל</t>
   </si>
   <si>
     <t>סירופ יכין פטל דיאט 1 ליטר</t>
   </si>
   <si>
+    <t>28.8%</t>
+  </si>
+  <si>
     <t>יין סגל אדום יבש 750 מ"ל</t>
   </si>
   <si>
+    <t>20.1%</t>
+  </si>
+  <si>
     <t>יין טפרברג מוסקטו לבן 750 מ"ל</t>
   </si>
   <si>
@@ -103,6 +130,9 @@
     <t>42.50 (2 ב-85)</t>
   </si>
   <si>
+    <t>6.5%</t>
+  </si>
+  <si>
     <t>שיבולת שועל קוואקר 500 גרם</t>
   </si>
   <si>
@@ -112,6 +142,9 @@
     <t>חמאת בוטנים טבעית בטר אנד דיפרנט 350 גרם</t>
   </si>
   <si>
+    <t>17.8%</t>
+  </si>
+  <si>
     <t>ספגטי אסם 500 גרם</t>
   </si>
   <si>
@@ -121,54 +154,84 @@
     <t>6.00 (3 ב-18)</t>
   </si>
   <si>
+    <t>27.8%</t>
+  </si>
+  <si>
     <t>פסטה פנה ריגטה ברילה 500 גרם</t>
   </si>
   <si>
     <t>6.67 (3 ב-20)</t>
   </si>
   <si>
+    <t>20.2%</t>
+  </si>
+  <si>
     <t>דבש טבעי עמק חפר 350 גרם</t>
   </si>
   <si>
     <t>14.90</t>
   </si>
   <si>
+    <t>47.3%</t>
+  </si>
+  <si>
     <t>רביולי גבינה קלאסי שטראוס 400 גרם</t>
   </si>
   <si>
     <t>12.90</t>
   </si>
   <si>
+    <t>17.5%</t>
+  </si>
+  <si>
     <t>ניקיון וטואלטיקה</t>
   </si>
   <si>
     <t>מגבות נייר ניקול 6 גלילים</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>נייר טואלט לילי פסטל 32 גלילים</t>
   </si>
   <si>
+    <t>9.1%</t>
+  </si>
+  <si>
     <t>אקונומיקה סנו גאוול 4 ליטר</t>
   </si>
   <si>
+    <t>11.2%</t>
+  </si>
+  <si>
     <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
   </si>
   <si>
     <t>15.00 (2 ב-30)</t>
   </si>
   <si>
+    <t>5.5%</t>
+  </si>
+  <si>
     <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
   </si>
   <si>
     <t>16.00 (2 ב-32)</t>
   </si>
   <si>
+    <t>21.7%</t>
+  </si>
+  <si>
     <t>מגבוני האגיס ללא בישום 4X56</t>
   </si>
   <si>
     <t>16.67 (3 ב-50)</t>
   </si>
   <si>
+    <t>20.9%</t>
+  </si>
+  <si>
     <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
   </si>
   <si>
@@ -181,12 +244,18 @@
     <t>19.00 (2 ב-38)</t>
   </si>
   <si>
+    <t>34.8%</t>
+  </si>
+  <si>
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
     <t>33.33 (3 ב-100)</t>
   </si>
   <si>
+    <t>15.1%</t>
+  </si>
+  <si>
     <t>פירות וירקות</t>
   </si>
   <si>
@@ -196,31 +265,40 @@
     <t>עגבניה (ק"ג)</t>
   </si>
   <si>
-    <t>6.90</t>
+    <t>10.1%</t>
   </si>
   <si>
     <t>מלפפון (ק"ג)</t>
   </si>
   <si>
+    <t>33.7%</t>
+  </si>
+  <si>
     <t>בננות (ק"ג)</t>
   </si>
   <si>
+    <t>23.3%</t>
+  </si>
+  <si>
     <t>בצל יבש (ק"ג)</t>
   </si>
   <si>
+    <t>16.9%</t>
+  </si>
+  <si>
     <t>סה"כ</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-17 מול 2026-10-16 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>18.3%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-18 מול 2026-10-17 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
-  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
@@ -306,13 +384,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -320,36 +398,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -699,15 +766,15 @@
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="10" width="24" customWidth="1"/>
+    <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -721,7 +788,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -753,7 +820,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -786,22 +853,22 @@
       <c r="F4" s="8">
         <v>0.15</v>
       </c>
-      <c r="G4" s="9">
-        <v>2</v>
-      </c>
-      <c r="H4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>15</v>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" s="5">
         <v>5.9</v>
@@ -818,22 +885,22 @@
       <c r="F5" s="8">
         <v>0.5</v>
       </c>
-      <c r="G5" s="9">
-        <v>7.8</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>15</v>
+      <c r="G5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B6" s="5">
         <v>19.5</v>
@@ -850,22 +917,22 @@
       <c r="F6" s="8">
         <v>1.4</v>
       </c>
-      <c r="G6" s="9">
-        <v>6.7</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -879,7 +946,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B8" s="5">
         <v>21.9</v>
@@ -890,28 +957,28 @@
       <c r="D8" s="7">
         <v>26.9</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>20</v>
+      <c r="E8" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="F8" s="8">
         <v>5</v>
       </c>
-      <c r="G8" s="9">
-        <v>18.6</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>15</v>
+      <c r="G8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B9" s="5">
         <v>35.9</v>
@@ -928,22 +995,22 @@
       <c r="F9" s="8">
         <v>4</v>
       </c>
-      <c r="G9" s="9">
-        <v>10</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>15</v>
+      <c r="G9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B10" s="5">
         <v>13.07</v>
@@ -960,22 +1027,22 @@
       <c r="F10" s="8">
         <v>1.17</v>
       </c>
-      <c r="G10" s="9">
-        <v>8.2</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>15</v>
+      <c r="G10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B11" s="7">
         <v>8.2</v>
@@ -992,22 +1059,22 @@
       <c r="F11" s="8">
         <v>0.22</v>
       </c>
-      <c r="G11" s="9">
-        <v>2.7</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>15</v>
+      <c r="G11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B12" s="5">
         <v>9.9</v>
@@ -1024,22 +1091,22 @@
       <c r="F12" s="8">
         <v>4</v>
       </c>
-      <c r="G12" s="9">
-        <v>28.8</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>15</v>
+      <c r="G12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B13" s="5">
         <v>19.9</v>
@@ -1056,54 +1123,54 @@
       <c r="F13" s="8">
         <v>5</v>
       </c>
-      <c r="G13" s="9">
-        <v>20.1</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>15</v>
+      <c r="G13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B14" s="5">
         <v>42.9</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>28</v>
+      <c r="C14" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="D14" s="7">
         <v>45.9</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>29</v>
+      <c r="E14" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="F14" s="8">
         <v>3</v>
       </c>
-      <c r="G14" s="9">
-        <v>6.5</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>15</v>
+      <c r="G14" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B15" s="5">
         <v>11.9</v>
@@ -1114,28 +1181,28 @@
       <c r="D15" s="7">
         <v>14.9</v>
       </c>
-      <c r="E15" s="11" t="s">
-        <v>31</v>
+      <c r="E15" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="F15" s="8">
         <v>3</v>
       </c>
-      <c r="G15" s="9">
-        <v>20.1</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>15</v>
+      <c r="G15" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B16" s="5">
         <v>13.9</v>
@@ -1152,60 +1219,60 @@
       <c r="F16" s="8">
         <v>3</v>
       </c>
-      <c r="G16" s="9">
-        <v>17.8</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>15</v>
+      <c r="G16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B17" s="5">
         <v>5.7</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>34</v>
+      <c r="C17" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="D17" s="7">
         <v>7.9</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>35</v>
+      <c r="E17" s="10" t="s">
+        <v>46</v>
       </c>
       <c r="F17" s="8">
         <v>2.2</v>
       </c>
-      <c r="G17" s="9">
-        <v>27.8</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>15</v>
+      <c r="G17" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B18" s="5">
         <v>7.9</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>37</v>
+      <c r="C18" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="D18" s="7">
         <v>9.9</v>
@@ -1216,22 +1283,22 @@
       <c r="F18" s="8">
         <v>2</v>
       </c>
-      <c r="G18" s="9">
-        <v>20.2</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>15</v>
+      <c r="G18" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B19" s="5">
         <v>8.9</v>
@@ -1242,34 +1309,34 @@
       <c r="D19" s="7">
         <v>16.9</v>
       </c>
-      <c r="E19" s="11" t="s">
-        <v>39</v>
+      <c r="E19" s="10" t="s">
+        <v>52</v>
       </c>
       <c r="F19" s="8">
         <v>8</v>
       </c>
-      <c r="G19" s="9">
-        <v>47.3</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>15</v>
+      <c r="G19" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B20" s="5">
         <v>18.9</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>41</v>
+      <c r="C20" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="D20" s="7">
         <v>22.9</v>
@@ -1280,22 +1347,22 @@
       <c r="F20" s="8">
         <v>4</v>
       </c>
-      <c r="G20" s="9">
-        <v>17.5</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G20" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1309,24 +1376,30 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
+      </c>
+      <c r="B22" t="s">
+        <v>59</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="11">
         <v>13.9</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J22" s="10" t="s">
-        <v>15</v>
+      <c r="I22" t="s">
+        <v>59</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B23" s="5">
         <v>39.9</v>
@@ -1343,22 +1416,22 @@
       <c r="F23" s="8">
         <v>4</v>
       </c>
-      <c r="G23" s="9">
-        <v>9.1</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>15</v>
+      <c r="G23" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="B24" s="5">
         <v>15.9</v>
@@ -1375,28 +1448,28 @@
       <c r="F24" s="8">
         <v>2</v>
       </c>
-      <c r="G24" s="9">
-        <v>11.2</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>15</v>
+      <c r="G24" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="B25" s="5">
         <v>18.8</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>47</v>
+      <c r="C25" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="D25" s="7">
         <v>19.9</v>
@@ -1407,22 +1480,22 @@
       <c r="F25" s="8">
         <v>1.1</v>
       </c>
-      <c r="G25" s="9">
-        <v>5.5</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>15</v>
+      <c r="G25" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H25" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="B26" s="5">
         <v>14.8</v>
@@ -1433,60 +1506,60 @@
       <c r="D26" s="7">
         <v>18.9</v>
       </c>
-      <c r="E26" s="11" t="s">
-        <v>49</v>
+      <c r="E26" s="10" t="s">
+        <v>68</v>
       </c>
       <c r="F26" s="8">
         <v>4.1</v>
       </c>
-      <c r="G26" s="9">
-        <v>21.7</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>15</v>
+      <c r="G26" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H26" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="B27" s="5">
         <v>19.7</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>47</v>
+      <c r="C27" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="D27" s="7">
         <v>24.9</v>
       </c>
-      <c r="E27" s="11" t="s">
-        <v>51</v>
+      <c r="E27" s="10" t="s">
+        <v>71</v>
       </c>
       <c r="F27" s="8">
         <v>5.2</v>
       </c>
-      <c r="G27" s="9">
-        <v>20.9</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>15</v>
+      <c r="G27" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="B28" s="5">
         <v>21.9</v>
@@ -1497,28 +1570,28 @@
       <c r="D28" s="7">
         <v>26.9</v>
       </c>
-      <c r="E28" s="11" t="s">
-        <v>53</v>
+      <c r="E28" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="F28" s="8">
         <v>5</v>
       </c>
-      <c r="G28" s="9">
-        <v>18.6</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" s="10" t="s">
-        <v>15</v>
+      <c r="G28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="B29" s="5">
         <v>14.94</v>
@@ -1529,28 +1602,28 @@
       <c r="D29" s="7">
         <v>22.9</v>
       </c>
-      <c r="E29" s="11" t="s">
-        <v>55</v>
+      <c r="E29" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="F29" s="8">
         <v>7.96</v>
       </c>
-      <c r="G29" s="9">
-        <v>34.8</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>15</v>
+      <c r="G29" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H29" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="B30" s="5">
         <v>41.5</v>
@@ -1561,28 +1634,28 @@
       <c r="D30" s="7">
         <v>48.9</v>
       </c>
-      <c r="E30" s="11" t="s">
-        <v>57</v>
+      <c r="E30" s="10" t="s">
+        <v>79</v>
       </c>
       <c r="F30" s="8">
         <v>7.4</v>
       </c>
-      <c r="G30" s="9">
-        <v>15.1</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G30" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H30" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1596,7 +1669,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="B32" s="5">
         <v>15.9</v>
@@ -1613,28 +1686,28 @@
       <c r="F32" s="8">
         <v>4</v>
       </c>
-      <c r="G32" s="9">
-        <v>20.1</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>15</v>
+      <c r="G32" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H32" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B33" s="5">
         <v>8.9</v>
       </c>
-      <c r="C33" s="11" t="s">
-        <v>61</v>
+      <c r="C33" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="D33" s="7">
         <v>9.9</v>
@@ -1645,22 +1718,22 @@
       <c r="F33" s="8">
         <v>1</v>
       </c>
-      <c r="G33" s="9">
-        <v>10.1</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>15</v>
+      <c r="G33" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H33" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="B34" s="5">
         <v>5.9</v>
@@ -1677,22 +1750,22 @@
       <c r="F34" s="8">
         <v>3</v>
       </c>
-      <c r="G34" s="9">
-        <v>33.7</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>15</v>
+      <c r="G34" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H34" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="B35" s="5">
         <v>9.9</v>
@@ -1709,22 +1782,22 @@
       <c r="F35" s="8">
         <v>3</v>
       </c>
-      <c r="G35" s="9">
-        <v>23.3</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>15</v>
+      <c r="G35" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H35" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="B36" s="5">
         <v>4.9</v>
@@ -1741,54 +1814,54 @@
       <c r="F36" s="8">
         <v>1</v>
       </c>
-      <c r="G36" s="9">
-        <v>16.9</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B37" s="14">
+      <c r="G36" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H36" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" s="13">
         <v>484.51</v>
       </c>
-      <c r="C37" s="15"/>
-      <c r="D37" s="14">
+      <c r="C37" s="14"/>
+      <c r="D37" s="13">
         <v>593.37</v>
       </c>
-      <c r="E37" s="15"/>
-      <c r="F37" s="14">
+      <c r="E37" s="14"/>
+      <c r="F37" s="13">
         <v>108.86</v>
       </c>
-      <c r="G37" s="16">
-        <v>18.3</v>
-      </c>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
+      <c r="G37" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
     </row>
     <row r="38" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
+      <c r="A38" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="94">
-  <si>
-    <t>מעקב מחירים יומי — 2026-10-18</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="93">
+  <si>
+    <t>מעקב מחירים יומי — 2026-10-19</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -178,9 +178,6 @@
     <t>רביולי גבינה קלאסי שטראוס 400 גרם</t>
   </si>
   <si>
-    <t>12.90</t>
-  </si>
-  <si>
     <t>17.5%</t>
   </si>
   <si>
@@ -226,9 +223,6 @@
     <t>מגבוני האגיס ללא בישום 4X56</t>
   </si>
   <si>
-    <t>16.67 (3 ב-50)</t>
-  </si>
-  <si>
     <t>20.9%</t>
   </si>
   <si>
@@ -250,9 +244,6 @@
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
-    <t>33.33 (3 ב-100)</t>
-  </si>
-  <si>
     <t>15.1%</t>
   </si>
   <si>
@@ -265,13 +256,19 @@
     <t>עגבניה (ק"ג)</t>
   </si>
   <si>
+    <t>7.90</t>
+  </si>
+  <si>
     <t>10.1%</t>
   </si>
   <si>
     <t>מלפפון (ק"ג)</t>
   </si>
   <si>
-    <t>33.7%</t>
+    <t>22.5%</t>
+  </si>
+  <si>
+    <t>⬆ +1.00 ₪</t>
   </si>
   <si>
     <t>בננות (ק"ג)</t>
@@ -289,10 +286,10 @@
     <t>סה"כ</t>
   </si>
   <si>
-    <t>18.3%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-18 מול 2026-10-17 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>18.2%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-19 מול 2026-10-18 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -324,7 +321,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -368,6 +365,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -384,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -399,26 +401,14 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -841,28 +831,28 @@
       <c r="B4" s="5">
         <v>7.2</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="7">
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="6">
         <v>7.35</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="8">
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="7">
         <v>0.15</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" t="s">
         <v>14</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="9" t="s">
+      <c r="I4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -873,28 +863,28 @@
       <c r="B5" s="5">
         <v>5.9</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="7">
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="6">
         <v>6.4</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="8">
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="7">
         <v>0.5</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" t="s">
         <v>18</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="9" t="s">
+      <c r="I5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -905,28 +895,28 @@
       <c r="B6" s="5">
         <v>19.5</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="7">
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="6">
         <v>20.9</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="8">
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="7">
         <v>1.4</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" t="s">
         <v>20</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="9" t="s">
+      <c r="I6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -951,28 +941,28 @@
       <c r="B8" s="5">
         <v>21.9</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="6">
         <v>26.9</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <v>5</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" t="s">
         <v>24</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="9" t="s">
+      <c r="I8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -983,28 +973,28 @@
       <c r="B9" s="5">
         <v>35.9</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="6">
         <v>39.9</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="8">
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="7">
         <v>4</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" t="s">
         <v>26</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="9" t="s">
+      <c r="I9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1015,28 +1005,28 @@
       <c r="B10" s="5">
         <v>13.07</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="6">
         <v>14.24</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="8">
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="7">
         <v>1.17</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" t="s">
         <v>28</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="9" t="s">
+      <c r="I10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1044,31 +1034,31 @@
       <c r="A11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>8.2</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="5">
         <v>7.98</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="8">
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="7">
         <v>0.22</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" t="s">
         <v>30</v>
       </c>
       <c r="H11" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="9" t="s">
+      <c r="I11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1079,28 +1069,28 @@
       <c r="B12" s="5">
         <v>9.9</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="6">
         <v>13.9</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="8">
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="7">
         <v>4</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" t="s">
         <v>33</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="9" t="s">
+      <c r="I12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1111,28 +1101,28 @@
       <c r="B13" s="5">
         <v>19.9</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="6">
         <v>24.9</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="8">
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="7">
         <v>5</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" t="s">
         <v>35</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="9" t="s">
+      <c r="I13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1143,28 +1133,28 @@
       <c r="B14" s="5">
         <v>42.9</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>45.9</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="7">
         <v>3</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" t="s">
         <v>39</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="9" t="s">
+      <c r="I14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1175,28 +1165,28 @@
       <c r="B15" s="5">
         <v>11.9</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="7">
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="6">
         <v>14.9</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="7">
         <v>3</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" t="s">
         <v>35</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="9" t="s">
+      <c r="I15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1207,28 +1197,28 @@
       <c r="B16" s="5">
         <v>13.9</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="7">
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="6">
         <v>16.9</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="8">
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="7">
         <v>3</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" t="s">
         <v>43</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="9" t="s">
+      <c r="I16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1239,28 +1229,28 @@
       <c r="B17" s="5">
         <v>5.7</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
         <v>7.9</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="7">
         <v>2.2</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" t="s">
         <v>47</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="9" t="s">
+      <c r="I17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1271,28 +1261,28 @@
       <c r="B18" s="5">
         <v>7.9</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="6">
         <v>9.9</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="8">
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="7">
         <v>2</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" t="s">
         <v>50</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
       </c>
-      <c r="I18" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="9" t="s">
+      <c r="I18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1303,28 +1293,28 @@
       <c r="B19" s="5">
         <v>8.9</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="7">
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="6">
         <v>16.9</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="7">
         <v>8</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" t="s">
         <v>53</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="9" t="s">
+      <c r="I19" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1335,34 +1325,34 @@
       <c r="B20" s="5">
         <v>18.9</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="6">
+        <v>22.9</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="7">
+        <v>4</v>
+      </c>
+      <c r="G20" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="7">
-        <v>22.9</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="8">
-        <v>4</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>56</v>
-      </c>
       <c r="H20" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="9" t="s">
+      <c r="I20" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1376,286 +1366,295 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="11">
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="10">
         <v>13.9</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>13</v>
+      <c r="E22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" t="s">
+        <v>58</v>
       </c>
       <c r="I22" t="s">
-        <v>59</v>
-      </c>
-      <c r="J22" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J22" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" s="5">
         <v>39.9</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="7">
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="6">
         <v>43.9</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="8">
+      <c r="E23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="7">
         <v>4</v>
       </c>
-      <c r="G23" s="6" t="s">
-        <v>61</v>
+      <c r="G23" t="s">
+        <v>60</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
       </c>
-      <c r="I23" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="9" t="s">
+      <c r="I23" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B24" s="5">
         <v>15.9</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="7">
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="6">
         <v>17.9</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="8">
+      <c r="E24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="7">
         <v>2</v>
       </c>
-      <c r="G24" s="6" t="s">
-        <v>63</v>
+      <c r="G24" t="s">
+        <v>62</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
       </c>
-      <c r="I24" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="9" t="s">
+      <c r="I24" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B25" s="5">
         <v>18.8</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="6">
+        <v>19.9</v>
+      </c>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="7">
+        <v>1.1</v>
+      </c>
+      <c r="G25" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="7">
-        <v>19.9</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="8">
-        <v>1.1</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>66</v>
-      </c>
       <c r="H25" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="9" t="s">
+      <c r="I25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B26" s="5">
         <v>14.8</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="7">
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="6">
         <v>18.9</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26" s="7">
+        <v>4.1</v>
+      </c>
+      <c r="G26" t="s">
         <v>68</v>
       </c>
-      <c r="F26" s="8">
-        <v>4.1</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="H26" t="s">
         <v>15</v>
       </c>
-      <c r="I26" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="9" t="s">
+      <c r="I26" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B27" s="5">
         <v>19.7</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="7">
+      <c r="C27" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="6">
         <v>24.9</v>
       </c>
-      <c r="E27" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="F27" s="8">
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="7">
         <v>5.2</v>
       </c>
-      <c r="G27" s="6" t="s">
-        <v>72</v>
+      <c r="G27" t="s">
+        <v>70</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
       </c>
-      <c r="I27" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="9" t="s">
+      <c r="I27" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B28" s="5">
         <v>21.9</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="7">
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="6">
         <v>26.9</v>
       </c>
-      <c r="E28" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" s="8">
+      <c r="E28" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F28" s="7">
         <v>5</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" t="s">
         <v>24</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
       </c>
-      <c r="I28" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="9" t="s">
+      <c r="I28" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B29" s="5">
         <v>14.94</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="7">
+      <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="6">
         <v>22.9</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="F29" s="8">
+      <c r="E29" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" s="7">
         <v>7.96</v>
       </c>
-      <c r="G29" s="6" t="s">
-        <v>77</v>
+      <c r="G29" t="s">
+        <v>75</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
       </c>
-      <c r="I29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="9" t="s">
+      <c r="I29" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B30" s="5">
         <v>41.5</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="7">
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="6">
         <v>48.9</v>
       </c>
-      <c r="E30" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F30" s="8">
+      <c r="E30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="7">
         <v>7.4</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>80</v>
+      <c r="G30" t="s">
+        <v>77</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
       </c>
-      <c r="I30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="9" t="s">
+      <c r="I30" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1669,199 +1668,209 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B32" s="5">
         <v>15.9</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="7">
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="6">
         <v>19.9</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="8">
+      <c r="E32" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="7">
         <v>4</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" t="s">
         <v>35</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
       </c>
-      <c r="I32" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="9" t="s">
+      <c r="I32" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B33" s="5">
         <v>8.9</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="7">
+      <c r="C33" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="6">
         <v>9.9</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="8">
+      <c r="E33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="7">
         <v>1</v>
       </c>
-      <c r="G33" s="6" t="s">
-        <v>84</v>
+      <c r="G33" t="s">
+        <v>82</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="9" t="s">
+      <c r="I33" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="5">
+        <v>6.9</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="6">
+        <v>8.9</v>
+      </c>
+      <c r="E34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="7">
+        <v>2</v>
+      </c>
+      <c r="G34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H34" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="5">
-        <v>5.9</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="7">
-        <v>8.9</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="8">
-        <v>3</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="H34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="9" t="s">
+      <c r="J34" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B35" s="5">
         <v>9.9</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="7">
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="6">
         <v>12.9</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="8">
+      <c r="E35" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="7">
         <v>3</v>
       </c>
-      <c r="G35" s="6" t="s">
-        <v>88</v>
+      <c r="G35" t="s">
+        <v>87</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
       </c>
-      <c r="I35" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="9" t="s">
+      <c r="I35" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B36" s="5">
         <v>4.9</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="7">
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="6">
         <v>5.9</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="8">
+      <c r="E36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="7">
         <v>1</v>
       </c>
-      <c r="G36" s="6" t="s">
-        <v>90</v>
+      <c r="G36" t="s">
+        <v>89</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
       </c>
-      <c r="I36" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="9" t="s">
+      <c r="I36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B37" s="13">
-        <v>484.51</v>
-      </c>
-      <c r="C37" s="14"/>
+        <v>485.51</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>58</v>
+      </c>
       <c r="D37" s="13">
         <v>593.37</v>
       </c>
-      <c r="E37" s="14"/>
+      <c r="E37" s="12" t="s">
+        <v>58</v>
+      </c>
       <c r="F37" s="13">
-        <v>108.86</v>
-      </c>
-      <c r="G37" s="15" t="s">
+        <v>107.86</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-    </row>
-    <row r="38" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="93">
-  <si>
-    <t>מעקב מחירים יומי — 2026-10-19</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="95">
+  <si>
+    <t>מחירי מוצרים - 2026-10-20</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -178,6 +178,9 @@
     <t>רביולי גבינה קלאסי שטראוס 400 גרם</t>
   </si>
   <si>
+    <t>12.90</t>
+  </si>
+  <si>
     <t>17.5%</t>
   </si>
   <si>
@@ -244,6 +247,9 @@
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
+    <t>29.90</t>
+  </si>
+  <si>
     <t>15.1%</t>
   </si>
   <si>
@@ -265,10 +271,10 @@
     <t>מלפפון (ק"ג)</t>
   </si>
   <si>
-    <t>22.5%</t>
-  </si>
-  <si>
-    <t>⬆ +1.00 ₪</t>
+    <t>33.7%</t>
+  </si>
+  <si>
+    <t>⬇ -1.00 ₪</t>
   </si>
   <si>
     <t>בננות (ק"ג)</t>
@@ -286,10 +292,10 @@
     <t>סה"כ</t>
   </si>
   <si>
-    <t>18.2%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-19 מול 2026-10-18 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>18.3%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-20 מול 2026-10-19 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -365,7 +371,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -386,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -400,15 +406,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -754,7 +784,7 @@
   <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -778,7 +808,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -810,7 +840,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -831,28 +861,28 @@
       <c r="B4" s="5">
         <v>7.2</v>
       </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="C4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="7">
         <v>7.35</v>
       </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="E4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="8">
         <v>0.15</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="8" t="s">
+      <c r="H4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -863,28 +893,28 @@
       <c r="B5" s="5">
         <v>5.9</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="7">
         <v>6.4</v>
       </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="E5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="8">
         <v>0.5</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="8" t="s">
+      <c r="H5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -895,32 +925,32 @@
       <c r="B6" s="5">
         <v>19.5</v>
       </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="6">
+      <c r="C6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="7">
         <v>20.9</v>
       </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="E6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="8">
         <v>1.4</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
@@ -941,28 +971,28 @@
       <c r="B8" s="5">
         <v>21.9</v>
       </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="7">
         <v>26.9</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <v>5</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="8" t="s">
+      <c r="H8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -973,28 +1003,28 @@
       <c r="B9" s="5">
         <v>35.9</v>
       </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="7">
         <v>39.9</v>
       </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="E9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="8">
         <v>4</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="8" t="s">
+      <c r="H9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1005,28 +1035,28 @@
       <c r="B10" s="5">
         <v>13.07</v>
       </c>
-      <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="7">
         <v>14.24</v>
       </c>
-      <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="E10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="8">
         <v>1.17</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="8" t="s">
+      <c r="H10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1034,31 +1064,31 @@
       <c r="A11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>8.2</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="5">
         <v>7.98</v>
       </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="E11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="8">
         <v>0.22</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="8" t="s">
+      <c r="I11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1069,28 +1099,28 @@
       <c r="B12" s="5">
         <v>9.9</v>
       </c>
-      <c r="C12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="7">
         <v>13.9</v>
       </c>
-      <c r="E12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="E12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="8">
         <v>4</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="8" t="s">
+      <c r="H12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1101,28 +1131,28 @@
       <c r="B13" s="5">
         <v>19.9</v>
       </c>
-      <c r="C13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="7">
         <v>24.9</v>
       </c>
-      <c r="E13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="E13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="8">
         <v>5</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H13" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="8" t="s">
+      <c r="H13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1133,28 +1163,28 @@
       <c r="B14" s="5">
         <v>42.9</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="7">
         <v>45.9</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="8">
         <v>3</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="8" t="s">
+      <c r="H14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1165,28 +1195,28 @@
       <c r="B15" s="5">
         <v>11.9</v>
       </c>
-      <c r="C15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="7">
         <v>14.9</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="8">
         <v>3</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H15" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="8" t="s">
+      <c r="H15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1197,28 +1227,28 @@
       <c r="B16" s="5">
         <v>13.9</v>
       </c>
-      <c r="C16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="7">
         <v>16.9</v>
       </c>
-      <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="7">
+      <c r="E16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="8">
         <v>3</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="8" t="s">
+      <c r="H16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1229,28 +1259,28 @@
       <c r="B17" s="5">
         <v>5.7</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="7">
         <v>7.9</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="8">
         <v>2.2</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H17" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="8" t="s">
+      <c r="H17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1261,28 +1291,28 @@
       <c r="B18" s="5">
         <v>7.9</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="7">
         <v>9.9</v>
       </c>
-      <c r="E18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="7">
+      <c r="E18" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="8">
         <v>2</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="H18" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="8" t="s">
+      <c r="H18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1293,28 +1323,28 @@
       <c r="B19" s="5">
         <v>8.9</v>
       </c>
-      <c r="C19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="7">
         <v>16.9</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="8">
         <v>8</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="8" t="s">
+      <c r="H19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1325,34 +1355,34 @@
       <c r="B20" s="5">
         <v>18.9</v>
       </c>
-      <c r="C20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="7">
         <v>22.9</v>
       </c>
-      <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="7">
+      <c r="E20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="8">
         <v>4</v>
       </c>
-      <c r="G20" t="s">
-        <v>55</v>
-      </c>
-      <c r="H20" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G20" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1366,295 +1396,293 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="10">
+      <c r="B22" s="8"/>
+      <c r="C22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="11">
         <v>13.9</v>
       </c>
-      <c r="E22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22" t="s">
-        <v>58</v>
-      </c>
-      <c r="H22" t="s">
-        <v>58</v>
-      </c>
-      <c r="I22" t="s">
-        <v>58</v>
-      </c>
-      <c r="J22" s="8" t="s">
+      <c r="E22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23" s="5">
         <v>39.9</v>
       </c>
-      <c r="C23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="7">
         <v>43.9</v>
       </c>
-      <c r="E23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="7">
+      <c r="E23" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="8">
         <v>4</v>
       </c>
-      <c r="G23" t="s">
-        <v>60</v>
-      </c>
-      <c r="H23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="8" t="s">
+      <c r="G23" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="5">
         <v>15.9</v>
       </c>
-      <c r="C24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="7">
         <v>17.9</v>
       </c>
-      <c r="E24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="7">
+      <c r="E24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="8">
         <v>2</v>
       </c>
-      <c r="G24" t="s">
-        <v>62</v>
-      </c>
-      <c r="H24" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="8" t="s">
+      <c r="G24" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B25" s="5">
         <v>18.8</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="7">
         <v>19.9</v>
       </c>
-      <c r="E25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="7">
+      <c r="E25" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="8">
         <v>1.1</v>
       </c>
-      <c r="G25" t="s">
-        <v>65</v>
-      </c>
-      <c r="H25" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="8" t="s">
+      <c r="G25" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B26" s="5">
         <v>14.8</v>
       </c>
-      <c r="C26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="7">
         <v>18.9</v>
       </c>
-      <c r="E26" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F26" s="7">
+      <c r="E26" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="8">
         <v>4.1</v>
       </c>
-      <c r="G26" t="s">
-        <v>68</v>
-      </c>
-      <c r="H26" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="8" t="s">
+      <c r="G26" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B27" s="5">
         <v>19.7</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C27" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="7">
         <v>24.9</v>
       </c>
-      <c r="E27" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="7">
+      <c r="E27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="8">
         <v>5.2</v>
       </c>
-      <c r="G27" t="s">
-        <v>70</v>
-      </c>
-      <c r="H27" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="8" t="s">
+      <c r="G27" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B28" s="5">
         <v>21.9</v>
       </c>
-      <c r="C28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="7">
         <v>26.9</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="F28" s="7">
+      <c r="E28" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28" s="8">
         <v>5</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="8" t="s">
+      <c r="H28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B29" s="5">
         <v>14.94</v>
       </c>
-      <c r="C29" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="7">
         <v>22.9</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="F29" s="7">
+      <c r="E29" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F29" s="8">
         <v>7.96</v>
       </c>
-      <c r="G29" t="s">
-        <v>75</v>
-      </c>
-      <c r="H29" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="8" t="s">
+      <c r="G29" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B30" s="5">
         <v>41.5</v>
       </c>
-      <c r="C30" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" s="7">
         <v>48.9</v>
       </c>
-      <c r="E30" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="7">
+      <c r="E30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="8">
         <v>7.4</v>
       </c>
-      <c r="G30" t="s">
-        <v>77</v>
-      </c>
-      <c r="H30" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G30" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1668,209 +1696,209 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B32" s="5">
         <v>15.9</v>
       </c>
-      <c r="C32" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="7">
         <v>19.9</v>
       </c>
-      <c r="E32" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="7">
+      <c r="E32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="8">
         <v>4</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H32" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="8" t="s">
+      <c r="H32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B33" s="5">
         <v>8.9</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" s="6">
+      <c r="C33" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="7">
         <v>9.9</v>
       </c>
-      <c r="E33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="7">
+      <c r="E33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="8">
         <v>1</v>
       </c>
-      <c r="G33" t="s">
-        <v>82</v>
-      </c>
-      <c r="H33" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="8" t="s">
+      <c r="G33" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B34" s="5">
-        <v>6.9</v>
-      </c>
-      <c r="C34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="6">
+        <v>5.9</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="7">
         <v>8.9</v>
       </c>
-      <c r="E34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="7">
-        <v>2</v>
-      </c>
-      <c r="G34" t="s">
-        <v>84</v>
-      </c>
-      <c r="H34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="J34" s="8" t="s">
+      <c r="E34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="8">
+        <v>3</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="J34" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B35" s="5">
         <v>9.9</v>
       </c>
-      <c r="C35" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="6">
+      <c r="C35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="7">
         <v>12.9</v>
       </c>
-      <c r="E35" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="7">
+      <c r="E35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="8">
         <v>3</v>
       </c>
-      <c r="G35" t="s">
-        <v>87</v>
-      </c>
-      <c r="H35" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="8" t="s">
+      <c r="G35" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B36" s="5">
         <v>4.9</v>
       </c>
-      <c r="C36" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="6">
+      <c r="C36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="7">
         <v>5.9</v>
       </c>
-      <c r="E36" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="7">
+      <c r="E36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="8">
         <v>1</v>
       </c>
-      <c r="G36" t="s">
-        <v>89</v>
-      </c>
-      <c r="H36" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="8" t="s">
+      <c r="G36" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="B37" s="13">
-        <v>485.51</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D37" s="13">
+      <c r="A37" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B37" s="14">
+        <v>484.51</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" s="14">
         <v>593.37</v>
       </c>
-      <c r="E37" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="F37" s="13">
-        <v>107.86</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>58</v>
+      <c r="E37" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F37" s="14">
+        <v>108.86</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
+      <c r="A38" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="95">
-  <si>
-    <t>מחירי מוצרים - 2026-10-20</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="96">
+  <si>
+    <t>מחירי מוצרים - 2026-10-21</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -190,112 +190,115 @@
     <t>מגבות נייר ניקול 6 גלילים</t>
   </si>
   <si>
+    <t>אין נתון קודם</t>
+  </si>
+  <si>
+    <t>נייר טואלט לילי פסטל 32 גלילים</t>
+  </si>
+  <si>
+    <t>9.1%</t>
+  </si>
+  <si>
+    <t>אקונומיקה סנו גאוול 4 ליטר</t>
+  </si>
+  <si>
+    <t>11.2%</t>
+  </si>
+  <si>
+    <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
+  </si>
+  <si>
+    <t>9.90</t>
+  </si>
+  <si>
+    <t>5.5%</t>
+  </si>
+  <si>
+    <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
+  </si>
+  <si>
+    <t>16.00 (2 ב-32)</t>
+  </si>
+  <si>
+    <t>21.7%</t>
+  </si>
+  <si>
+    <t>מגבוני האגיס ללא בישום 4X56</t>
+  </si>
+  <si>
+    <t>15.00 (2 ב-30)</t>
+  </si>
+  <si>
+    <t>20.9%</t>
+  </si>
+  <si>
+    <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
+  </si>
+  <si>
+    <t>21.00 (2 ב-42)</t>
+  </si>
+  <si>
+    <t>שמפו פנטן משקם 600 מ"ל</t>
+  </si>
+  <si>
+    <t>19.00 (2 ב-38)</t>
+  </si>
+  <si>
+    <t>34.8%</t>
+  </si>
+  <si>
+    <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
+  </si>
+  <si>
+    <t>29.90</t>
+  </si>
+  <si>
+    <t>15.1%</t>
+  </si>
+  <si>
+    <t>פירות וירקות</t>
+  </si>
+  <si>
+    <t>תפוח עץ פינק ליידי 1 ק"ג</t>
+  </si>
+  <si>
+    <t>עגבניה (ק"ג)</t>
+  </si>
+  <si>
+    <t>7.90</t>
+  </si>
+  <si>
+    <t>10.1%</t>
+  </si>
+  <si>
+    <t>מלפפון (ק"ג)</t>
+  </si>
+  <si>
+    <t>33.7%</t>
+  </si>
+  <si>
+    <t>בננות (ק"ג)</t>
+  </si>
+  <si>
+    <t>23.3%</t>
+  </si>
+  <si>
+    <t>בצל יבש (ק"ג)</t>
+  </si>
+  <si>
+    <t>16.9%</t>
+  </si>
+  <si>
+    <t>סה"כ</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>נייר טואלט לילי פסטל 32 גלילים</t>
-  </si>
-  <si>
-    <t>9.1%</t>
-  </si>
-  <si>
-    <t>אקונומיקה סנו גאוול 4 ליטר</t>
-  </si>
-  <si>
-    <t>11.2%</t>
-  </si>
-  <si>
-    <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
-  </si>
-  <si>
-    <t>15.00 (2 ב-30)</t>
-  </si>
-  <si>
-    <t>5.5%</t>
-  </si>
-  <si>
-    <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
-  </si>
-  <si>
-    <t>16.00 (2 ב-32)</t>
-  </si>
-  <si>
-    <t>21.7%</t>
-  </si>
-  <si>
-    <t>מגבוני האגיס ללא בישום 4X56</t>
-  </si>
-  <si>
-    <t>20.9%</t>
-  </si>
-  <si>
-    <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
-  </si>
-  <si>
-    <t>21.00 (2 ב-42)</t>
-  </si>
-  <si>
-    <t>שמפו פנטן משקם 600 מ"ל</t>
-  </si>
-  <si>
-    <t>19.00 (2 ב-38)</t>
-  </si>
-  <si>
-    <t>34.8%</t>
-  </si>
-  <si>
-    <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
-  </si>
-  <si>
-    <t>29.90</t>
-  </si>
-  <si>
-    <t>15.1%</t>
-  </si>
-  <si>
-    <t>פירות וירקות</t>
-  </si>
-  <si>
-    <t>תפוח עץ פינק ליידי 1 ק"ג</t>
-  </si>
-  <si>
-    <t>עגבניה (ק"ג)</t>
-  </si>
-  <si>
-    <t>7.90</t>
-  </si>
-  <si>
-    <t>10.1%</t>
-  </si>
-  <si>
-    <t>מלפפון (ק"ג)</t>
-  </si>
-  <si>
-    <t>33.7%</t>
-  </si>
-  <si>
-    <t>⬇ -1.00 ₪</t>
-  </si>
-  <si>
-    <t>בננות (ק"ג)</t>
-  </si>
-  <si>
-    <t>23.3%</t>
-  </si>
-  <si>
-    <t>בצל יבש (ק"ג)</t>
-  </si>
-  <si>
-    <t>16.9%</t>
-  </si>
-  <si>
-    <t>סה"כ</t>
-  </si>
-  <si>
     <t>18.3%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-20 מול 2026-10-19 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-21 מול 2026-10-20 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -324,10 +327,9 @@
     </font>
     <font>
       <i/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -371,11 +373,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -395,13 +392,13 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -428,20 +425,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1408,15 +1401,9 @@
       <c r="E22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>59</v>
-      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
       <c r="I22" s="6" t="s">
         <v>59</v>
       </c>
@@ -1560,7 +1547,7 @@
         <v>19.7</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D27" s="7">
         <v>24.9</v>
@@ -1572,7 +1559,7 @@
         <v>5.2</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>15</v>
@@ -1586,7 +1573,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B28" s="5">
         <v>21.9</v>
@@ -1598,7 +1585,7 @@
         <v>26.9</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F28" s="8">
         <v>5</v>
@@ -1618,7 +1605,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B29" s="5">
         <v>14.94</v>
@@ -1630,13 +1617,13 @@
         <v>22.9</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F29" s="8">
         <v>7.96</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>15</v>
@@ -1650,13 +1637,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B30" s="5">
         <v>41.5</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D30" s="7">
         <v>48.9</v>
@@ -1668,7 +1655,7 @@
         <v>7.4</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>15</v>
@@ -1682,7 +1669,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1696,7 +1683,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B32" s="5">
         <v>15.9</v>
@@ -1728,13 +1715,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B33" s="5">
         <v>8.9</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D33" s="7">
         <v>9.9</v>
@@ -1746,7 +1733,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>15</v>
@@ -1760,7 +1747,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B34" s="5">
         <v>5.9</v>
@@ -1778,13 +1765,13 @@
         <v>3</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I34" s="12" t="s">
-        <v>87</v>
+      <c r="I34" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="J34" s="9" t="s">
         <v>16</v>
@@ -1855,40 +1842,40 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B37" s="14">
+      <c r="B37" s="13">
         <v>484.51</v>
       </c>
-      <c r="C37" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D37" s="14">
+      <c r="C37" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37" s="13">
         <v>593.37</v>
       </c>
-      <c r="E37" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F37" s="14">
+      <c r="E37" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="F37" s="13">
         <v>108.86</v>
       </c>
       <c r="G37" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="H37" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="J37" s="15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J37" s="14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="96">
-  <si>
-    <t>מחירי מוצרים - 2026-10-21</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="95">
+  <si>
+    <t>מחירי מוצרים - 2026-10-22</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -190,7 +190,7 @@
     <t>מגבות נייר ניקול 6 גלילים</t>
   </si>
   <si>
-    <t>אין נתון קודם</t>
+    <t/>
   </si>
   <si>
     <t>נייר טואלט לילי פסטל 32 גלילים</t>
@@ -292,13 +292,10 @@
     <t>סה"כ</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>18.3%</t>
   </si>
   <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-21 מול 2026-10-20 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-22 מול 2026-10-21 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -389,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -398,9 +395,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -425,13 +419,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -787,7 +777,7 @@
     <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -848,98 +838,98 @@
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>7.2</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="7">
+      <c r="C4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="6">
         <v>7.35</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="8">
+      <c r="E4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="7">
         <v>0.15</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="9" t="s">
+      <c r="H4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>5.9</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="7">
+      <c r="C5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="6">
         <v>6.4</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="8">
+      <c r="E5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="7">
         <v>0.5</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="9" t="s">
+      <c r="H5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>19.5</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="7">
+      <c r="C6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="6">
         <v>20.9</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="8">
+      <c r="E6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="7">
         <v>1.4</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="9" t="s">
+      <c r="H6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -958,418 +948,418 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>21.9</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="C8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="6">
         <v>26.9</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <v>5</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="9" t="s">
+      <c r="H8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>35.9</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="6">
         <v>39.9</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="8">
+      <c r="E9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="7">
         <v>4</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="9" t="s">
+      <c r="H9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>13.07</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="C10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="6">
         <v>14.24</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="8">
+      <c r="E10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="7">
         <v>1.17</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="9" t="s">
+      <c r="H10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>8.2</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4">
         <v>7.98</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="8">
+      <c r="E11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="7">
         <v>0.22</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="9" t="s">
+      <c r="I11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>9.9</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="C12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="6">
         <v>13.9</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="8">
+      <c r="E12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="7">
         <v>4</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="9" t="s">
+      <c r="H12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="4">
         <v>19.9</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="C13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="6">
         <v>24.9</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="8">
+      <c r="E13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="7">
         <v>5</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="9" t="s">
+      <c r="H13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>42.9</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>45.9</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="7">
         <v>3</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="9" t="s">
+      <c r="H14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="A15" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <v>11.9</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="7">
+      <c r="C15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="6">
         <v>14.9</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="7">
         <v>3</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="9" t="s">
+      <c r="H15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>13.9</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="7">
+      <c r="C16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="6">
         <v>16.9</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="8">
+      <c r="E16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="7">
         <v>3</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H16" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="9" t="s">
+      <c r="H16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>5.7</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
         <v>7.9</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="7">
         <v>2.2</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="9" t="s">
+      <c r="H17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="A18" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>7.9</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="6">
         <v>9.9</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="8">
+      <c r="E18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="7">
         <v>2</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H18" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="9" t="s">
+      <c r="H18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="A19" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>8.9</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="7">
+      <c r="C19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="6">
         <v>16.9</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="7">
         <v>8</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="9" t="s">
+      <c r="H19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="A20" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>18.9</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="6">
         <v>22.9</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="8">
+      <c r="E20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="7">
         <v>4</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="9" t="s">
+      <c r="H20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1388,282 +1378,282 @@
       <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="A22" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="11">
+      <c r="B22" s="7"/>
+      <c r="C22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="10">
         <v>13.9</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6" t="s">
+      <c r="E22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="J22" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="A23" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="4">
         <v>39.9</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="7">
+      <c r="C23" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="6">
         <v>43.9</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="8">
+      <c r="E23" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="7">
         <v>4</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="9" t="s">
+      <c r="H23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="A24" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="4">
         <v>15.9</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="7">
+      <c r="C24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="6">
         <v>17.9</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="8">
+      <c r="E24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="7">
         <v>2</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H24" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="9" t="s">
+      <c r="H24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="4">
         <v>18.8</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="6">
         <v>19.9</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="8">
+      <c r="E25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="7">
         <v>1.1</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H25" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="9" t="s">
+      <c r="H25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="A26" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="4">
         <v>14.8</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="7">
+      <c r="C26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="6">
         <v>18.9</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="7">
         <v>4.1</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="H26" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="9" t="s">
+      <c r="H26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="A27" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="4">
         <v>19.7</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="6">
         <v>24.9</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="8">
+      <c r="E27" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="7">
         <v>5.2</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H27" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="9" t="s">
+      <c r="H27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="A28" t="s">
         <v>73</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="4">
         <v>21.9</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="7">
+      <c r="C28" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="6">
         <v>26.9</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="7">
         <v>5</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H28" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="9" t="s">
+      <c r="H28" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="A29" t="s">
         <v>75</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="4">
         <v>14.94</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="7">
+      <c r="C29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="6">
         <v>22.9</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="7">
         <v>7.96</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H29" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="9" t="s">
+      <c r="H29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="A30" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="4">
         <v>41.5</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="6">
         <v>48.9</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="8">
+      <c r="E30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="7">
         <v>7.4</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H30" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="9" t="s">
+      <c r="H30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1682,210 +1672,210 @@
       <c r="J31" s="3"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="A32" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="4">
         <v>15.9</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="7">
+      <c r="C32" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="6">
         <v>19.9</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="8">
+      <c r="E32" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="7">
         <v>4</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H32" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="9" t="s">
+      <c r="H32" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+      <c r="A33" t="s">
         <v>83</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="4">
         <v>8.9</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="6">
         <v>9.9</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="8">
+      <c r="E33" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="7">
         <v>1</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="H33" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="9" t="s">
+      <c r="H33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="A34" t="s">
         <v>86</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="4">
         <v>5.9</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="7">
+      <c r="C34" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="6">
         <v>8.9</v>
       </c>
-      <c r="E34" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="8">
+      <c r="E34" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="7">
         <v>3</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H34" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="9" t="s">
+      <c r="H34" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="A35" t="s">
         <v>88</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="4">
         <v>9.9</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="7">
+      <c r="C35" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="6">
         <v>12.9</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="8">
+      <c r="E35" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="7">
         <v>3</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="H35" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="9" t="s">
+      <c r="H35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="A36" t="s">
         <v>90</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="4">
         <v>4.9</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="7">
+      <c r="C36" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="6">
         <v>5.9</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="8">
+      <c r="E36" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="7">
         <v>1</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="H36" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="9" t="s">
+      <c r="H36" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="12">
         <v>484.51</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" s="12">
+        <v>593.37</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F37" s="12">
+        <v>108.86</v>
+      </c>
+      <c r="G37" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="D37" s="13">
-        <v>593.37</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="F37" s="13">
-        <v>108.86</v>
-      </c>
-      <c r="G37" s="15" t="s">
+      <c r="H37" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="H37" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="95">
-  <si>
-    <t>מחירי מוצרים - 2026-10-22</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="96">
+  <si>
+    <t>מחירי מוצרים - 2026-10-23</t>
   </si>
   <si>
     <t>מוצר</t>
@@ -202,7 +202,13 @@
     <t>אקונומיקה סנו גאוול 4 ליטר</t>
   </si>
   <si>
-    <t>11.2%</t>
+    <t>15.00 (2 ב-30)</t>
+  </si>
+  <si>
+    <t>5.6%</t>
+  </si>
+  <si>
+    <t>⬆ +1.00 ₪</t>
   </si>
   <si>
     <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
@@ -226,9 +232,6 @@
     <t>מגבוני האגיס ללא בישום 4X56</t>
   </si>
   <si>
-    <t>15.00 (2 ב-30)</t>
-  </si>
-  <si>
     <t>20.9%</t>
   </si>
   <si>
@@ -292,10 +295,10 @@
     <t>סה"כ</t>
   </si>
   <si>
-    <t>18.3%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-22 מול 2026-10-21 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>16.2%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-23 מול 2026-10-22 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -326,7 +329,7 @@
       <i/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -370,6 +373,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -386,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -421,7 +429,10 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1381,7 +1392,7 @@
       <c r="A22" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="7"/>
+      <c r="B22" s="5"/>
       <c r="C22" s="5" t="s">
         <v>13</v>
       </c>
@@ -1438,10 +1449,10 @@
         <v>62</v>
       </c>
       <c r="B24" s="4">
-        <v>15.9</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>13</v>
+        <v>16.9</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="D24" s="6">
         <v>17.9</v>
@@ -1450,16 +1461,16 @@
         <v>13</v>
       </c>
       <c r="F24" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I24" s="8" t="s">
-        <v>16</v>
+      <c r="I24" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>16</v>
@@ -1467,13 +1478,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B25" s="4">
         <v>18.8</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D25" s="6">
         <v>19.9</v>
@@ -1485,7 +1496,7 @@
         <v>1.1</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>15</v>
@@ -1499,7 +1510,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B26" s="4">
         <v>14.8</v>
@@ -1511,13 +1522,13 @@
         <v>18.9</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F26" s="7">
         <v>4.1</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>15</v>
@@ -1531,13 +1542,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B27" s="4">
         <v>19.7</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D27" s="6">
         <v>24.9</v>
@@ -1549,7 +1560,7 @@
         <v>5.2</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>15</v>
@@ -1563,7 +1574,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B28" s="4">
         <v>21.9</v>
@@ -1575,7 +1586,7 @@
         <v>26.9</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F28" s="7">
         <v>5</v>
@@ -1595,7 +1606,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B29" s="4">
         <v>14.94</v>
@@ -1607,13 +1618,13 @@
         <v>22.9</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F29" s="7">
         <v>7.96</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>15</v>
@@ -1627,13 +1638,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B30" s="4">
         <v>41.5</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D30" s="6">
         <v>48.9</v>
@@ -1645,7 +1656,7 @@
         <v>7.4</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>15</v>
@@ -1659,7 +1670,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1673,7 +1684,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B32" s="4">
         <v>15.9</v>
@@ -1705,13 +1716,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B33" s="4">
         <v>8.9</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D33" s="6">
         <v>9.9</v>
@@ -1723,7 +1734,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>15</v>
@@ -1737,7 +1748,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B34" s="4">
         <v>5.9</v>
@@ -1755,7 +1766,7 @@
         <v>3</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>15</v>
@@ -1769,7 +1780,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B35" s="4">
         <v>9.9</v>
@@ -1787,7 +1798,7 @@
         <v>3</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>15</v>
@@ -1801,7 +1812,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B36" s="4">
         <v>4.9</v>
@@ -1819,7 +1830,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>15</v>
@@ -1832,50 +1843,50 @@
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B37" s="12">
-        <v>484.51</v>
-      </c>
-      <c r="C37" s="11" t="s">
+      <c r="A37" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37" s="13">
+        <v>485.51</v>
+      </c>
+      <c r="C37" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D37" s="12">
-        <v>593.37</v>
-      </c>
-      <c r="E37" s="11" t="s">
+      <c r="D37" s="13">
+        <v>579.47</v>
+      </c>
+      <c r="E37" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="F37" s="12">
-        <v>108.86</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="H37" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="11" t="s">
+      <c r="F37" s="13">
+        <v>93.96</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="J37" s="11" t="s">
+      <c r="J37" s="12" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
+      <c r="A38" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,10 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="96">
-  <si>
-    <t>מחירי מוצרים - 2026-10-23</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
   <si>
     <t>מוצר</t>
   </si>
@@ -208,9 +205,6 @@
     <t>5.6%</t>
   </si>
   <si>
-    <t>⬆ +1.00 ₪</t>
-  </si>
-  <si>
     <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
   </si>
   <si>
@@ -295,17 +289,17 @@
     <t>סה"כ</t>
   </si>
   <si>
-    <t>16.2%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-23 מול 2026-10-22 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>18.2%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-24 מול 2026-10-23 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -316,20 +310,16 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <b/>
     </font>
     <font>
       <i/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -373,11 +363,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -397,45 +382,35 @@
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="2" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -775,1127 +750,1120 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="10" width="20" customWidth="1"/>
+    <col min="9" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
+      <c r="B3" s="4">
+        <v>7.2</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="6">
+        <v>7.35</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
+      <c r="A4" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="B4" s="4">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="6">
-        <v>7.35</v>
+        <v>6.4</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" s="7">
-        <v>0.15</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>15</v>
+        <v>0.5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>17</v>
+      <c r="A5" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="B5" s="4">
-        <v>5.9</v>
+        <v>19.5</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" s="6">
-        <v>6.4</v>
+        <v>20.9</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>15</v>
+        <v>1.4</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="4">
-        <v>19.5</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="6">
-        <v>20.9</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="7">
-        <v>1.4</v>
-      </c>
-      <c r="G6" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>16</v>
-      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="B7" s="4">
+        <v>21.9</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="6">
+        <v>26.9</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="7">
+        <v>5</v>
+      </c>
+      <c r="G7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+      <c r="A8" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="B8" s="4">
-        <v>21.9</v>
+        <v>35.9</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" s="6">
-        <v>26.9</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>23</v>
+        <v>39.9</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="F8" s="7">
+        <v>4</v>
+      </c>
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="4">
+        <v>13.07</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="6">
+        <v>14.24</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="7">
+        <v>1.17</v>
+      </c>
+      <c r="G9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="6">
+        <v>8.2</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="4">
+        <v>7.98</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="4">
+        <v>9.9</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="6">
+        <v>13.9</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="7">
+        <v>4</v>
+      </c>
+      <c r="G11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="4">
+        <v>19.9</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="6">
+        <v>24.9</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="7">
         <v>5</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="4">
-        <v>35.9</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="6">
-        <v>39.9</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="7">
-        <v>4</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="4">
-        <v>13.07</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="6">
-        <v>14.24</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="7">
-        <v>1.17</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="6">
-        <v>8.2</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="4">
-        <v>7.98</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="7">
-        <v>0.22</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="4">
-        <v>9.9</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="6">
-        <v>13.9</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="7">
-        <v>4</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>15</v>
+      <c r="G12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" t="s">
+        <v>14</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>34</v>
+      <c r="A13" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="B13" s="4">
-        <v>19.9</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>13</v>
+        <v>42.9</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="D13" s="6">
-        <v>24.9</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>13</v>
+        <v>45.9</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="F13" s="7">
-        <v>5</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>15</v>
+        <v>3</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" t="s">
+        <v>14</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>36</v>
+      <c r="A14" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="B14" s="4">
-        <v>42.9</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>37</v>
+        <v>11.9</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="D14" s="6">
-        <v>45.9</v>
+        <v>14.9</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F14" s="7">
         <v>3</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>15</v>
+      <c r="G14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" t="s">
+        <v>14</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>40</v>
+      <c r="A15" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="B15" s="4">
-        <v>11.9</v>
+        <v>13.9</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D15" s="6">
-        <v>14.9</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>41</v>
+        <v>16.9</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="F15" s="7">
         <v>3</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>15</v>
+      <c r="G15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" t="s">
+        <v>14</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>42</v>
+      <c r="A16" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="B16" s="4">
-        <v>13.9</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>13</v>
+        <v>5.7</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>44</v>
       </c>
       <c r="D16" s="6">
+        <v>7.9</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="7">
+        <v>2.2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="4">
+        <v>7.9</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="6">
+        <v>9.9</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="7">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="4">
+        <v>8.9</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="6">
         <v>16.9</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="7">
-        <v>3</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="4">
-        <v>5.7</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="6">
-        <v>7.9</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="7">
-        <v>2.2</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="4">
-        <v>7.9</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="6">
-        <v>9.9</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>13</v>
+      <c r="E18" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="F18" s="7">
-        <v>2</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
+      </c>
+      <c r="G18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" t="s">
+        <v>14</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>51</v>
+      <c r="A19" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="B19" s="4">
-        <v>8.9</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>13</v>
+        <v>18.9</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="D19" s="6">
-        <v>16.9</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>52</v>
+        <v>22.9</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="F19" s="7">
-        <v>8</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>15</v>
+        <v>4</v>
+      </c>
+      <c r="G19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" t="s">
+        <v>14</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" s="4">
-        <v>18.9</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="6">
-        <v>22.9</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="7">
-        <v>4</v>
-      </c>
-      <c r="G20" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>16</v>
-      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="10">
+        <v>13.9</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H21" t="s">
+        <v>58</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="5"/>
+      <c r="A22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="4">
+        <v>39.9</v>
+      </c>
       <c r="C22" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="10">
-        <v>13.9</v>
+        <v>12</v>
+      </c>
+      <c r="D22" s="6">
+        <v>43.9</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5" t="s">
-        <v>59</v>
+        <v>12</v>
+      </c>
+      <c r="F22" s="7">
+        <v>4</v>
+      </c>
+      <c r="G22" t="s">
+        <v>60</v>
+      </c>
+      <c r="H22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>60</v>
+      <c r="A23" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="B23" s="4">
-        <v>39.9</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>13</v>
+        <v>16.9</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>62</v>
       </c>
       <c r="D23" s="6">
-        <v>43.9</v>
+        <v>17.9</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F23" s="7">
-        <v>4</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>15</v>
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>63</v>
+      </c>
+      <c r="H23" t="s">
+        <v>14</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="4">
+        <v>18.8</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" s="6">
+        <v>19.9</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="7">
+        <v>1.1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>66</v>
+      </c>
+      <c r="H24" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="4">
+        <v>14.8</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="6">
+        <v>18.9</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="7">
+        <v>4.1</v>
+      </c>
+      <c r="G25" t="s">
+        <v>69</v>
+      </c>
+      <c r="H25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="4">
+        <v>19.7</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="4">
-        <v>16.9</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" s="6">
-        <v>17.9</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="7">
-        <v>1</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25" s="4">
-        <v>18.8</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="6">
-        <v>19.9</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="7">
-        <v>1.1</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>69</v>
-      </c>
-      <c r="B26" s="4">
-        <v>14.8</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="D26" s="6">
-        <v>18.9</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>70</v>
+        <v>24.9</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="F26" s="7">
-        <v>4.1</v>
-      </c>
-      <c r="G26" s="5" t="s">
+        <v>5.2</v>
+      </c>
+      <c r="G26" t="s">
         <v>71</v>
       </c>
-      <c r="H26" s="5" t="s">
-        <v>15</v>
+      <c r="H26" t="s">
+        <v>14</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="3" t="s">
         <v>72</v>
       </c>
       <c r="B27" s="4">
-        <v>19.7</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>63</v>
+        <v>21.9</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="D27" s="6">
-        <v>24.9</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>13</v>
+        <v>26.9</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="F27" s="7">
-        <v>5.2</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>15</v>
+        <v>5</v>
+      </c>
+      <c r="G27" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" t="s">
+        <v>14</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="3" t="s">
         <v>74</v>
       </c>
       <c r="B28" s="4">
-        <v>21.9</v>
+        <v>14.94</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D28" s="6">
-        <v>26.9</v>
+        <v>22.9</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>75</v>
       </c>
       <c r="F28" s="7">
-        <v>5</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>15</v>
+        <v>7.96</v>
+      </c>
+      <c r="G28" t="s">
+        <v>76</v>
+      </c>
+      <c r="H28" t="s">
+        <v>14</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>76</v>
+      <c r="A29" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="B29" s="4">
-        <v>14.94</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>13</v>
+        <v>41.5</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="D29" s="6">
-        <v>22.9</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>77</v>
+        <v>48.9</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="F29" s="7">
-        <v>7.96</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>15</v>
+        <v>7.4</v>
+      </c>
+      <c r="G29" t="s">
+        <v>79</v>
+      </c>
+      <c r="H29" t="s">
+        <v>14</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>79</v>
-      </c>
-      <c r="B30" s="4">
-        <v>41.5</v>
-      </c>
-      <c r="C30" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D30" s="6">
-        <v>48.9</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="7">
-        <v>7.4</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>16</v>
-      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" s="4">
+        <v>15.9</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="6">
+        <v>19.9</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="7">
+        <v>4</v>
+      </c>
+      <c r="G31" t="s">
+        <v>34</v>
+      </c>
+      <c r="H31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B32" s="4">
+        <v>8.9</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B32" s="4">
-        <v>15.9</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="D32" s="6">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F32" s="7">
-        <v>4</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>15</v>
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>84</v>
+      </c>
+      <c r="H32" t="s">
+        <v>14</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>84</v>
+      <c r="A33" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="B33" s="4">
+        <v>5.9</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="6">
         <v>8.9</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D33" s="6">
+      <c r="E33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="7">
+        <v>3</v>
+      </c>
+      <c r="G33" t="s">
+        <v>86</v>
+      </c>
+      <c r="H33" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="4">
         <v>9.9</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="7">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>87</v>
-      </c>
-      <c r="B34" s="4">
-        <v>5.9</v>
-      </c>
       <c r="C34" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D34" s="6">
-        <v>8.9</v>
+        <v>12.9</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F34" s="7">
         <v>3</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" t="s">
         <v>88</v>
       </c>
-      <c r="H34" s="5" t="s">
-        <v>15</v>
+      <c r="H34" t="s">
+        <v>14</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" s="3" t="s">
         <v>89</v>
       </c>
       <c r="B35" s="4">
-        <v>9.9</v>
+        <v>4.9</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D35" s="6">
-        <v>12.9</v>
+        <v>5.9</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F35" s="7">
-        <v>3</v>
-      </c>
-      <c r="G35" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G35" t="s">
         <v>90</v>
       </c>
-      <c r="H35" s="5" t="s">
-        <v>15</v>
+      <c r="H35" t="s">
+        <v>14</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="B36" s="4">
-        <v>4.9</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="6">
-        <v>5.9</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="7">
-        <v>1</v>
-      </c>
-      <c r="G36" s="5" t="s">
+      <c r="B36" s="12">
+        <v>485.51</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="12">
+        <v>593.37</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" s="12">
+        <v>107.86</v>
+      </c>
+      <c r="G36" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="H36" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
+      <c r="H36" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B37" s="13">
-        <v>485.51</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D37" s="13">
-        <v>579.47</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F37" s="13">
-        <v>93.96</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A38:J38"/>
+  <mergeCells count="5">
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A37:J37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="95">
   <si>
     <t>מוצר</t>
   </si>
@@ -235,6 +235,12 @@
     <t>21.00 (2 ב-42)</t>
   </si>
   <si>
+    <t>30.5%</t>
+  </si>
+  <si>
+    <t>⬇ -3.21 ₪</t>
+  </si>
+  <si>
     <t>שמפו פנטן משקם 600 מ"ל</t>
   </si>
   <si>
@@ -247,9 +253,6 @@
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
-    <t>29.90</t>
-  </si>
-  <si>
     <t>15.1%</t>
   </si>
   <si>
@@ -289,10 +292,10 @@
     <t>סה"כ</t>
   </si>
   <si>
-    <t>18.2%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-24 מול 2026-10-23 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>18.7%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-25 מול 2026-10-24 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -319,7 +322,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -363,6 +366,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
@@ -385,29 +393,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -753,14 +753,14 @@
   <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="10" width="22" customWidth="1"/>
+    <col min="9" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -795,7 +795,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -816,16 +816,16 @@
       <c r="B3" s="4">
         <v>7.2</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="5">
         <v>7.35</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="6">
         <v>0.15</v>
       </c>
       <c r="G3" t="s">
@@ -834,10 +834,10 @@
       <c r="H3" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="8" t="s">
+      <c r="I3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -848,16 +848,16 @@
       <c r="B4" s="4">
         <v>5.9</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="5">
         <v>6.4</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="6">
         <v>0.5</v>
       </c>
       <c r="G4" t="s">
@@ -866,10 +866,10 @@
       <c r="H4" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="8" t="s">
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -880,16 +880,16 @@
       <c r="B5" s="4">
         <v>19.5</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="5">
         <v>20.9</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="6">
         <v>1.4</v>
       </c>
       <c r="G5" t="s">
@@ -898,14 +898,14 @@
       <c r="H5" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -926,16 +926,16 @@
       <c r="B7" s="4">
         <v>21.9</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="5">
         <v>26.9</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="9">
         <v>5</v>
       </c>
       <c r="G7" t="s">
@@ -944,10 +944,10 @@
       <c r="H7" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="8" t="s">
+      <c r="I7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -958,16 +958,16 @@
       <c r="B8" s="4">
         <v>35.9</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="5">
         <v>39.9</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="9">
         <v>4</v>
       </c>
       <c r="G8" t="s">
@@ -976,10 +976,10 @@
       <c r="H8" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="8" t="s">
+      <c r="I8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -990,16 +990,16 @@
       <c r="B9" s="4">
         <v>13.07</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="5">
         <v>14.24</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="6">
         <v>1.17</v>
       </c>
       <c r="G9" t="s">
@@ -1008,10 +1008,10 @@
       <c r="H9" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="8" t="s">
+      <c r="I9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1019,19 +1019,19 @@
       <c r="A10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>8.2</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="4">
         <v>7.98</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="6">
         <v>0.22</v>
       </c>
       <c r="G10" t="s">
@@ -1040,10 +1040,10 @@
       <c r="H10" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="8" t="s">
+      <c r="I10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1054,16 +1054,16 @@
       <c r="B11" s="4">
         <v>9.9</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="5">
         <v>13.9</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="9">
         <v>4</v>
       </c>
       <c r="G11" t="s">
@@ -1072,10 +1072,10 @@
       <c r="H11" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="8" t="s">
+      <c r="I11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1086,16 +1086,16 @@
       <c r="B12" s="4">
         <v>19.9</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="5">
         <v>24.9</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="9">
         <v>5</v>
       </c>
       <c r="G12" t="s">
@@ -1104,10 +1104,10 @@
       <c r="H12" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="8" t="s">
+      <c r="I12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1118,16 +1118,16 @@
       <c r="B13" s="4">
         <v>42.9</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>45.9</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="9">
         <v>3</v>
       </c>
       <c r="G13" t="s">
@@ -1136,10 +1136,10 @@
       <c r="H13" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="8" t="s">
+      <c r="I13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1150,16 +1150,16 @@
       <c r="B14" s="4">
         <v>11.9</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="5">
         <v>14.9</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="9">
         <v>3</v>
       </c>
       <c r="G14" t="s">
@@ -1168,10 +1168,10 @@
       <c r="H14" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="8" t="s">
+      <c r="I14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1182,16 +1182,16 @@
       <c r="B15" s="4">
         <v>13.9</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="5">
         <v>16.9</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="7">
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="6">
         <v>3</v>
       </c>
       <c r="G15" t="s">
@@ -1200,10 +1200,10 @@
       <c r="H15" t="s">
         <v>14</v>
       </c>
-      <c r="I15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="8" t="s">
+      <c r="I15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1214,16 +1214,16 @@
       <c r="B16" s="4">
         <v>5.7</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <v>7.9</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="6">
         <v>2.2</v>
       </c>
       <c r="G16" t="s">
@@ -1232,10 +1232,10 @@
       <c r="H16" t="s">
         <v>14</v>
       </c>
-      <c r="I16" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="8" t="s">
+      <c r="I16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1246,16 +1246,16 @@
       <c r="B17" s="4">
         <v>7.9</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="5">
         <v>9.9</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="7">
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="9">
         <v>2</v>
       </c>
       <c r="G17" t="s">
@@ -1264,10 +1264,10 @@
       <c r="H17" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="8" t="s">
+      <c r="I17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1278,16 +1278,16 @@
       <c r="B18" s="4">
         <v>8.9</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="5">
         <v>16.9</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="6">
         <v>8</v>
       </c>
       <c r="G18" t="s">
@@ -1296,10 +1296,10 @@
       <c r="H18" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="8" t="s">
+      <c r="I18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1310,16 +1310,16 @@
       <c r="B19" s="4">
         <v>18.9</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>22.9</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="7">
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="9">
         <v>4</v>
       </c>
       <c r="G19" t="s">
@@ -1328,14 +1328,14 @@
       <c r="H19" t="s">
         <v>14</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>56</v>
       </c>
@@ -1353,31 +1353,22 @@
       <c r="A21" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" t="s">
         <v>12</v>
       </c>
       <c r="D21" s="10">
         <v>13.9</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21" t="s">
         <v>58</v>
       </c>
-      <c r="G21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H21" t="s">
-        <v>58</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="J21" s="8" t="s">
+      <c r="J21" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1388,16 +1379,16 @@
       <c r="B22" s="4">
         <v>39.9</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="5">
         <v>43.9</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="7">
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="9">
         <v>4</v>
       </c>
       <c r="G22" t="s">
@@ -1406,10 +1397,10 @@
       <c r="H22" t="s">
         <v>14</v>
       </c>
-      <c r="I22" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="8" t="s">
+      <c r="I22" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1420,16 +1411,16 @@
       <c r="B23" s="4">
         <v>16.9</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="5">
         <v>17.9</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="7">
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="9">
         <v>1</v>
       </c>
       <c r="G23" t="s">
@@ -1438,10 +1429,10 @@
       <c r="H23" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="8" t="s">
+      <c r="I23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1452,16 +1443,16 @@
       <c r="B24" s="4">
         <v>18.8</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="5">
         <v>19.9</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="7">
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="6">
         <v>1.1</v>
       </c>
       <c r="G24" t="s">
@@ -1470,10 +1461,10 @@
       <c r="H24" t="s">
         <v>14</v>
       </c>
-      <c r="I24" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="8" t="s">
+      <c r="I24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1484,16 +1475,16 @@
       <c r="B25" s="4">
         <v>14.8</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="5">
         <v>18.9</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="6">
         <v>4.1</v>
       </c>
       <c r="G25" t="s">
@@ -1502,10 +1493,10 @@
       <c r="H25" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="8" t="s">
+      <c r="I25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1516,16 +1507,16 @@
       <c r="B26" s="4">
         <v>19.7</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="5">
         <v>24.9</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="7">
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="6">
         <v>5.2</v>
       </c>
       <c r="G26" t="s">
@@ -1534,10 +1525,10 @@
       <c r="H26" t="s">
         <v>14</v>
       </c>
-      <c r="I26" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="8" t="s">
+      <c r="I26" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1546,100 +1537,100 @@
         <v>72</v>
       </c>
       <c r="B27" s="4">
-        <v>21.9</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="6">
+        <v>18.69</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="5">
         <v>26.9</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="7">
-        <v>5</v>
+      <c r="F27" s="6">
+        <v>8.21</v>
       </c>
       <c r="G27" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="H27" t="s">
         <v>14</v>
       </c>
-      <c r="I27" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" s="8" t="s">
+      <c r="I27" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="J27" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B28" s="4">
         <v>14.94</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="5">
         <v>22.9</v>
       </c>
-      <c r="E28" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="7">
+      <c r="E28" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F28" s="6">
         <v>7.96</v>
       </c>
       <c r="G28" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s">
         <v>14</v>
       </c>
-      <c r="I28" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" s="8" t="s">
+      <c r="I28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B29" s="4">
         <v>41.5</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="5">
         <v>48.9</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="7">
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="6">
         <v>7.4</v>
       </c>
       <c r="G29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s">
         <v>14</v>
       </c>
-      <c r="I29" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I29" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1653,21 +1644,21 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B31" s="4">
         <v>15.9</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="5">
         <v>19.9</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="7">
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="6">
         <v>4</v>
       </c>
       <c r="G31" t="s">
@@ -1676,176 +1667,172 @@
       <c r="H31" t="s">
         <v>14</v>
       </c>
-      <c r="I31" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" s="8" t="s">
+      <c r="I31" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B32" s="4">
         <v>8.9</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C32" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" s="5">
         <v>9.9</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="7">
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="9">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H32" t="s">
         <v>14</v>
       </c>
-      <c r="I32" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" s="8" t="s">
+      <c r="I32" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B33" s="4">
         <v>5.9</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="6">
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="5">
         <v>8.9</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="7">
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="9">
         <v>3</v>
       </c>
       <c r="G33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s">
         <v>14</v>
       </c>
-      <c r="I33" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" s="8" t="s">
+      <c r="I33" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B34" s="4">
         <v>9.9</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="6">
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="5">
         <v>12.9</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="7">
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="9">
         <v>3</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s">
         <v>14</v>
       </c>
-      <c r="I34" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" s="8" t="s">
+      <c r="I34" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B35" s="4">
         <v>4.9</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="6">
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="5">
         <v>5.9</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="7">
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="9">
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s">
         <v>14</v>
       </c>
-      <c r="I35" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" s="8" t="s">
+      <c r="I35" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B36" s="12">
-        <v>485.51</v>
-      </c>
-      <c r="C36" s="13" t="s">
+      <c r="A36" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="13">
+        <v>482.3</v>
+      </c>
+      <c r="C36" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="13">
         <v>593.37</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E36" s="12" t="s">
         <v>58</v>
       </c>
       <c r="F36" s="12">
-        <v>107.86</v>
-      </c>
-      <c r="G36" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H36" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="J36" s="13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+        <v>111.07</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="96">
   <si>
     <t>מוצר</t>
   </si>
@@ -238,9 +238,6 @@
     <t>30.5%</t>
   </si>
   <si>
-    <t>⬇ -3.21 ₪</t>
-  </si>
-  <si>
     <t>שמפו פנטן משקם 600 מ"ל</t>
   </si>
   <si>
@@ -253,6 +250,9 @@
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
+    <t>33.33 (3 ב-100)</t>
+  </si>
+  <si>
     <t>15.1%</t>
   </si>
   <si>
@@ -274,7 +274,10 @@
     <t>מלפפון (ק"ג)</t>
   </si>
   <si>
-    <t>33.7%</t>
+    <t>22.5%</t>
+  </si>
+  <si>
+    <t>⬆ +1.00 ₪</t>
   </si>
   <si>
     <t>בננות (ק"ג)</t>
@@ -292,10 +295,10 @@
     <t>סה"כ</t>
   </si>
   <si>
-    <t>18.7%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-25 מול 2026-10-24 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>18.5%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-26 מול 2026-10-25 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -366,7 +369,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="FFFFCCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -387,7 +390,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -395,15 +398,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -810,22 +809,22 @@
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>7.2</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <v>7.35</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>0.15</v>
       </c>
       <c r="G3" t="s">
@@ -834,30 +833,30 @@
       <c r="H3" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="7" t="s">
+      <c r="I3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>5.9</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>6.4</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>0.5</v>
       </c>
       <c r="G4" t="s">
@@ -866,30 +865,30 @@
       <c r="H4" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="7" t="s">
+      <c r="I4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>19.5</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>20.9</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>1.4</v>
       </c>
       <c r="G5" t="s">
@@ -898,10 +897,10 @@
       <c r="H5" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="7" t="s">
+      <c r="I5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -920,22 +919,22 @@
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>21.9</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>26.9</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="5">
         <v>5</v>
       </c>
       <c r="G7" t="s">
@@ -944,30 +943,30 @@
       <c r="H7" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="7" t="s">
+      <c r="I7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>35.9</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>39.9</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="5">
         <v>4</v>
       </c>
       <c r="G8" t="s">
@@ -976,30 +975,30 @@
       <c r="H8" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="7" t="s">
+      <c r="I8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>13.07</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <v>14.24</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>1.17</v>
       </c>
       <c r="G9" t="s">
@@ -1008,30 +1007,30 @@
       <c r="H9" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="7" t="s">
+      <c r="I9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>8.2</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>7.98</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>0.22</v>
       </c>
       <c r="G10" t="s">
@@ -1040,30 +1039,30 @@
       <c r="H10" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="7" t="s">
+      <c r="I10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>9.9</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <v>13.9</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="5">
         <v>4</v>
       </c>
       <c r="G11" t="s">
@@ -1072,30 +1071,30 @@
       <c r="H11" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="7" t="s">
+      <c r="I11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>19.9</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>24.9</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="5">
         <v>5</v>
       </c>
       <c r="G12" t="s">
@@ -1104,30 +1103,30 @@
       <c r="H12" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="7" t="s">
+      <c r="I12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>42.9</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>45.9</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="5">
         <v>3</v>
       </c>
       <c r="G13" t="s">
@@ -1136,30 +1135,30 @@
       <c r="H13" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="7" t="s">
+      <c r="I13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="3">
         <v>11.9</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>14.9</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="5">
         <v>3</v>
       </c>
       <c r="G14" t="s">
@@ -1168,30 +1167,30 @@
       <c r="H14" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="7" t="s">
+      <c r="I14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="3">
         <v>13.9</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>16.9</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
         <v>3</v>
       </c>
       <c r="G15" t="s">
@@ -1200,30 +1199,30 @@
       <c r="H15" t="s">
         <v>14</v>
       </c>
-      <c r="I15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="7" t="s">
+      <c r="I15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="3">
         <v>5.7</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <v>7.9</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="5">
         <v>2.2</v>
       </c>
       <c r="G16" t="s">
@@ -1232,30 +1231,30 @@
       <c r="H16" t="s">
         <v>14</v>
       </c>
-      <c r="I16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="7" t="s">
+      <c r="I16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="3">
         <v>7.9</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <v>9.9</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="5">
         <v>2</v>
       </c>
       <c r="G17" t="s">
@@ -1264,30 +1263,30 @@
       <c r="H17" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="7" t="s">
+      <c r="I17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="3">
         <v>8.9</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="4">
         <v>16.9</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="5">
         <v>8</v>
       </c>
       <c r="G18" t="s">
@@ -1296,30 +1295,30 @@
       <c r="H18" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="7" t="s">
+      <c r="I18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="3">
         <v>18.9</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="4">
         <v>22.9</v>
       </c>
       <c r="E19" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="5">
         <v>4</v>
       </c>
       <c r="G19" t="s">
@@ -1328,10 +1327,10 @@
       <c r="H19" t="s">
         <v>14</v>
       </c>
-      <c r="I19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="7" t="s">
+      <c r="I19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1350,16 +1349,16 @@
       <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="A21" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>58</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="8">
         <v>13.9</v>
       </c>
       <c r="E21" t="s">
@@ -1368,27 +1367,27 @@
       <c r="I21" t="s">
         <v>58</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="J21" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="A22" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="3">
         <v>39.9</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="4">
         <v>43.9</v>
       </c>
       <c r="E22" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="5">
         <v>4</v>
       </c>
       <c r="G22" t="s">
@@ -1397,30 +1396,30 @@
       <c r="H22" t="s">
         <v>14</v>
       </c>
-      <c r="I22" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="7" t="s">
+      <c r="I22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="A23" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="3">
         <v>16.9</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="4">
         <v>17.9</v>
       </c>
       <c r="E23" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="5">
         <v>1</v>
       </c>
       <c r="G23" t="s">
@@ -1429,30 +1428,30 @@
       <c r="H23" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="7" t="s">
+      <c r="I23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="3">
         <v>18.8</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="4">
         <v>19.9</v>
       </c>
       <c r="E24" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="5">
         <v>1.1</v>
       </c>
       <c r="G24" t="s">
@@ -1461,30 +1460,30 @@
       <c r="H24" t="s">
         <v>14</v>
       </c>
-      <c r="I24" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="7" t="s">
+      <c r="I24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="3">
         <v>14.8</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="4">
         <v>18.9</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="5">
         <v>4.1</v>
       </c>
       <c r="G25" t="s">
@@ -1493,30 +1492,30 @@
       <c r="H25" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="7" t="s">
+      <c r="I25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="A26" t="s">
         <v>70</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="3">
         <v>19.7</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="4">
         <v>24.9</v>
       </c>
       <c r="E26" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="5">
         <v>5.2</v>
       </c>
       <c r="G26" t="s">
@@ -1525,30 +1524,30 @@
       <c r="H26" t="s">
         <v>14</v>
       </c>
-      <c r="I26" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="7" t="s">
+      <c r="I26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="A27" t="s">
         <v>72</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="3">
         <v>18.69</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="4">
         <v>26.9</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="5">
         <v>8.21</v>
       </c>
       <c r="G27" t="s">
@@ -1557,62 +1556,62 @@
       <c r="H27" t="s">
         <v>14</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>75</v>
       </c>
-      <c r="J27" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="B28" s="3">
+        <v>14.94</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="4">
+        <v>22.9</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B28" s="4">
-        <v>14.94</v>
-      </c>
-      <c r="C28" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="5">
-        <v>22.9</v>
-      </c>
-      <c r="E28" s="8" t="s">
+      <c r="F28" s="5">
+        <v>7.96</v>
+      </c>
+      <c r="G28" t="s">
         <v>77</v>
       </c>
-      <c r="F28" s="6">
-        <v>7.96</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>78</v>
       </c>
-      <c r="H28" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B29" s="3">
+        <v>41.5</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="4">
-        <v>41.5</v>
-      </c>
-      <c r="C29" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="D29" s="4">
         <v>48.9</v>
       </c>
       <c r="E29" t="s">
         <v>12</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="5">
         <v>7.4</v>
       </c>
       <c r="G29" t="s">
@@ -1621,10 +1620,10 @@
       <c r="H29" t="s">
         <v>14</v>
       </c>
-      <c r="I29" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="7" t="s">
+      <c r="I29" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1643,22 +1642,22 @@
       <c r="J30" s="2"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="A31" t="s">
         <v>82</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="3">
         <v>15.9</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="4">
         <v>19.9</v>
       </c>
       <c r="E31" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="5">
         <v>4</v>
       </c>
       <c r="G31" t="s">
@@ -1667,30 +1666,30 @@
       <c r="H31" t="s">
         <v>14</v>
       </c>
-      <c r="I31" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" s="7" t="s">
+      <c r="I31" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="A32" t="s">
         <v>83</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="3">
         <v>8.9</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="4">
         <v>9.9</v>
       </c>
       <c r="E32" t="s">
         <v>12</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F32" s="5">
         <v>1</v>
       </c>
       <c r="G32" t="s">
@@ -1699,31 +1698,31 @@
       <c r="H32" t="s">
         <v>14</v>
       </c>
-      <c r="I32" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" s="7" t="s">
+      <c r="I32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="A33" t="s">
         <v>86</v>
       </c>
-      <c r="B33" s="4">
-        <v>5.9</v>
+      <c r="B33" s="3">
+        <v>6.9</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="4">
         <v>8.9</v>
       </c>
       <c r="E33" t="s">
         <v>12</v>
       </c>
-      <c r="F33" s="9">
-        <v>3</v>
+      <c r="F33" s="5">
+        <v>2</v>
       </c>
       <c r="G33" t="s">
         <v>87</v>
@@ -1731,118 +1730,118 @@
       <c r="H33" t="s">
         <v>14</v>
       </c>
-      <c r="I33" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" s="7" t="s">
+      <c r="I33" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="J33" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B34" s="4">
+      <c r="A34" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="3">
         <v>9.9</v>
       </c>
       <c r="C34" t="s">
         <v>12</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="4">
         <v>12.9</v>
       </c>
       <c r="E34" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F34" s="5">
         <v>3</v>
       </c>
       <c r="G34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s">
         <v>14</v>
       </c>
-      <c r="I34" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" s="7" t="s">
+      <c r="I34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B35" s="4">
+      <c r="A35" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" s="3">
         <v>4.9</v>
       </c>
       <c r="C35" t="s">
         <v>12</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="4">
         <v>5.9</v>
       </c>
       <c r="E35" t="s">
         <v>12</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F35" s="5">
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H35" t="s">
         <v>14</v>
       </c>
-      <c r="I35" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" s="7" t="s">
+      <c r="I35" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B36" s="13">
-        <v>482.3</v>
-      </c>
-      <c r="C36" s="12" t="s">
+      <c r="A36" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" s="11">
+        <v>483.3</v>
+      </c>
+      <c r="C36" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D36" s="13">
+      <c r="D36" s="11">
         <v>593.37</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F36" s="12">
-        <v>111.07</v>
-      </c>
-      <c r="G36" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="H36" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
+      <c r="F36" s="10">
+        <v>110.07</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
+      <c r="A37" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="106">
   <si>
     <t>מוצר</t>
   </si>
@@ -52,12 +52,15 @@
     <t>—</t>
   </si>
   <si>
-    <t>2.0%</t>
+    <t>7.5%</t>
   </si>
   <si>
     <t>אושר עד</t>
   </si>
   <si>
+    <t>⬇ -0.40 ₪</t>
+  </si>
+  <si>
     <t>ללא שינוי</t>
   </si>
   <si>
@@ -70,7 +73,10 @@
     <t>גבינה צהובה 9% פרוסות 200 גרם</t>
   </si>
   <si>
-    <t>6.7%</t>
+    <t>9.6%</t>
+  </si>
+  <si>
+    <t>⬇ -0.60 ₪</t>
   </si>
   <si>
     <t>מאכל ושתיה סגורים</t>
@@ -79,16 +85,25 @@
     <t>טונה סטארקיסט בשמן 4X160 גרם</t>
   </si>
   <si>
+    <t>22.00 (2 ב-44)</t>
+  </si>
+  <si>
     <t>23.00 (2 ב-46)</t>
   </si>
   <si>
-    <t>18.6%</t>
+    <t>7.4%</t>
+  </si>
+  <si>
+    <t>⬆ +3.00 ₪</t>
   </si>
   <si>
     <t>קפה נמס טסטרס צויס 200 גרם</t>
   </si>
   <si>
-    <t>10.0%</t>
+    <t>12.5%</t>
+  </si>
+  <si>
+    <t>⬇ -1.00 ₪</t>
   </si>
   <si>
     <t>ביצים L (מנורמל ל-12 יח')</t>
@@ -100,10 +115,10 @@
     <t>קוקה קולה זירו 1.5 ליטר</t>
   </si>
   <si>
-    <t>2.7%</t>
-  </si>
-  <si>
-    <t>שופרסל</t>
+    <t>1.0%</t>
+  </si>
+  <si>
+    <t>⬇ -0.30 ₪</t>
   </si>
   <si>
     <t>סירופ יכין פטל דיאט 1 ליטר</t>
@@ -139,7 +154,7 @@
     <t>חמאת בוטנים טבעית בטר אנד דיפרנט 350 גרם</t>
   </si>
   <si>
-    <t>17.8%</t>
+    <t>23.7%</t>
   </si>
   <si>
     <t>ספגטי אסם 500 גרם</t>
@@ -151,7 +166,10 @@
     <t>6.00 (3 ב-18)</t>
   </si>
   <si>
-    <t>27.8%</t>
+    <t>38.0%</t>
+  </si>
+  <si>
+    <t>⬇ -0.80 ₪</t>
   </si>
   <si>
     <t>פסטה פנה ריגטה ברילה 500 גרם</t>
@@ -187,118 +205,130 @@
     <t>מגבות נייר ניקול 6 גלילים</t>
   </si>
   <si>
+    <t>21.6%</t>
+  </si>
+  <si>
+    <t>אין נתון קודם</t>
+  </si>
+  <si>
+    <t>נייר טואלט לילי פסטל 32 גלילים</t>
+  </si>
+  <si>
+    <t>15.9%</t>
+  </si>
+  <si>
+    <t>⬇ -3.00 ₪</t>
+  </si>
+  <si>
+    <t>אקונומיקה סנו גאוול 4 ליטר</t>
+  </si>
+  <si>
+    <t>15.00 (2 ב-30)</t>
+  </si>
+  <si>
+    <t>11.2%</t>
+  </si>
+  <si>
+    <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
+  </si>
+  <si>
+    <t>9.90</t>
+  </si>
+  <si>
+    <t>5.5%</t>
+  </si>
+  <si>
+    <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
+  </si>
+  <si>
+    <t>16.00 (2 ב-32)</t>
+  </si>
+  <si>
+    <t>21.7%</t>
+  </si>
+  <si>
+    <t>מגבוני האגיס ללא בישום 4X56</t>
+  </si>
+  <si>
+    <t>19.00 (2 ב-38)</t>
+  </si>
+  <si>
+    <t>20.9%</t>
+  </si>
+  <si>
+    <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
+  </si>
+  <si>
+    <t>21.00 (2 ב-42)</t>
+  </si>
+  <si>
+    <t>30.5%</t>
+  </si>
+  <si>
+    <t>שמפו פנטן משקם 600 מ"ל</t>
+  </si>
+  <si>
+    <t>34.8%</t>
+  </si>
+  <si>
+    <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
+  </si>
+  <si>
+    <t>21.90</t>
+  </si>
+  <si>
+    <t>33.33 (3 ב-100)</t>
+  </si>
+  <si>
+    <t>15.1%</t>
+  </si>
+  <si>
+    <t>פירות וירקות</t>
+  </si>
+  <si>
+    <t>תפוח עץ פינק ליידי 1 ק"ג</t>
+  </si>
+  <si>
+    <t>עגבניה (ק"ג)</t>
+  </si>
+  <si>
+    <t>7.90</t>
+  </si>
+  <si>
+    <t>מלפפון (ק"ג)</t>
+  </si>
+  <si>
+    <t>22.5%</t>
+  </si>
+  <si>
+    <t>בננות (ק"ג)</t>
+  </si>
+  <si>
+    <t>31.0%</t>
+  </si>
+  <si>
+    <t>בצל יבש (ק"ג)</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>שווה</t>
+  </si>
+  <si>
+    <t>⬆ +1.00 ₪</t>
+  </si>
+  <si>
+    <t>סה"כ</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>נייר טואלט לילי פסטל 32 גלילים</t>
-  </si>
-  <si>
-    <t>9.1%</t>
-  </si>
-  <si>
-    <t>אקונומיקה סנו גאוול 4 ליטר</t>
-  </si>
-  <si>
-    <t>15.00 (2 ב-30)</t>
-  </si>
-  <si>
-    <t>5.6%</t>
-  </si>
-  <si>
-    <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
-  </si>
-  <si>
-    <t>9.90</t>
-  </si>
-  <si>
-    <t>5.5%</t>
-  </si>
-  <si>
-    <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
-  </si>
-  <si>
-    <t>16.00 (2 ב-32)</t>
-  </si>
-  <si>
-    <t>21.7%</t>
-  </si>
-  <si>
-    <t>מגבוני האגיס ללא בישום 4X56</t>
-  </si>
-  <si>
-    <t>20.9%</t>
-  </si>
-  <si>
-    <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
-  </si>
-  <si>
-    <t>21.00 (2 ב-42)</t>
-  </si>
-  <si>
-    <t>30.5%</t>
-  </si>
-  <si>
-    <t>שמפו פנטן משקם 600 מ"ל</t>
-  </si>
-  <si>
-    <t>19.00 (2 ב-38)</t>
-  </si>
-  <si>
-    <t>34.8%</t>
-  </si>
-  <si>
-    <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
-  </si>
-  <si>
-    <t>33.33 (3 ב-100)</t>
-  </si>
-  <si>
-    <t>15.1%</t>
-  </si>
-  <si>
-    <t>פירות וירקות</t>
-  </si>
-  <si>
-    <t>תפוח עץ פינק ליידי 1 ק"ג</t>
-  </si>
-  <si>
-    <t>עגבניה (ק"ג)</t>
-  </si>
-  <si>
-    <t>7.90</t>
-  </si>
-  <si>
-    <t>10.1%</t>
-  </si>
-  <si>
-    <t>מלפפון (ק"ג)</t>
-  </si>
-  <si>
-    <t>22.5%</t>
-  </si>
-  <si>
-    <t>⬆ +1.00 ₪</t>
-  </si>
-  <si>
-    <t>בננות (ק"ג)</t>
-  </si>
-  <si>
-    <t>23.3%</t>
-  </si>
-  <si>
-    <t>בצל יבש (ק"ג)</t>
-  </si>
-  <si>
-    <t>16.9%</t>
-  </si>
-  <si>
-    <t>סה"כ</t>
-  </si>
-  <si>
-    <t>18.5%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-26 מול 2026-10-25 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>17.7%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-27 מול 2026-10-26 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -325,7 +355,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -354,6 +384,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
@@ -364,12 +399,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFFFCCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -390,7 +425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -401,12 +436,13 @@
     <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -813,7 +849,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="3">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -825,7 +861,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="5">
-        <v>0.15</v>
+        <v>0.55</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -836,13 +872,13 @@
       <c r="I3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="6" t="s">
-        <v>15</v>
+      <c r="J3" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3">
         <v>5.9</v>
@@ -860,24 +896,24 @@
         <v>0.5</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>15</v>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>19.5</v>
+        <v>18.9</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
@@ -889,24 +925,24 @@
         <v>12</v>
       </c>
       <c r="F5" s="5">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -920,42 +956,42 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B7" s="3">
-        <v>21.9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
+        <v>24.9</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="D7" s="4">
         <v>26.9</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>22</v>
+      <c r="E7" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="F7" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>15</v>
+      <c r="I7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3">
-        <v>35.9</v>
+        <v>34.9</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
@@ -967,24 +1003,24 @@
         <v>12</v>
       </c>
       <c r="F8" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H8" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B9" s="3">
         <v>13.07</v>
@@ -1002,53 +1038,53 @@
         <v>1.17</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>15</v>
+      <c r="I9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="4">
-        <v>8.2</v>
+        <v>33</v>
+      </c>
+      <c r="B10" s="3">
+        <v>7.9</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="4">
         <v>7.98</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
       <c r="F10" s="5">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>15</v>
+        <v>35</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B11" s="3">
         <v>9.9</v>
@@ -1066,21 +1102,21 @@
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>15</v>
+      <c r="I11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B12" s="3">
         <v>19.9</v>
@@ -1098,53 +1134,53 @@
         <v>5</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>15</v>
+      <c r="I12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B13" s="3">
         <v>42.9</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>36</v>
+      <c r="C13" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="D13" s="4">
         <v>45.9</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>37</v>
+      <c r="E13" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="F13" s="5">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H13" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>15</v>
+      <c r="I13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B14" s="3">
         <v>11.9</v>
@@ -1155,31 +1191,31 @@
       <c r="D14" s="4">
         <v>14.9</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>40</v>
+      <c r="E14" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="F14" s="5">
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H14" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>15</v>
+      <c r="I14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B15" s="3">
-        <v>13.9</v>
+        <v>12.9</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -1191,62 +1227,62 @@
         <v>12</v>
       </c>
       <c r="F15" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H15" t="s">
         <v>14</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B16" s="3">
-        <v>5.7</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>44</v>
+        <v>4.9</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="D16" s="4">
         <v>7.9</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>45</v>
+      <c r="E16" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="F16" s="5">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="G16" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H16" t="s">
         <v>14</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>15</v>
+        <v>52</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B17" s="3">
         <v>7.9</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>48</v>
+      <c r="C17" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="D17" s="4">
         <v>9.9</v>
@@ -1258,21 +1294,21 @@
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H17" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>15</v>
+      <c r="I17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B18" s="3">
         <v>8.9</v>
@@ -1283,34 +1319,34 @@
       <c r="D18" s="4">
         <v>16.9</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>51</v>
+      <c r="E18" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="F18" s="5">
         <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H18" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>15</v>
+      <c r="I18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B19" s="3">
         <v>18.9</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>54</v>
+      <c r="C19" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="D19" s="4">
         <v>22.9</v>
@@ -1322,21 +1358,21 @@
         <v>4</v>
       </c>
       <c r="G19" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H19" t="s">
         <v>14</v>
       </c>
-      <c r="I19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>15</v>
+      <c r="I19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1350,33 +1386,42 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
+      </c>
+      <c r="B21" s="3">
+        <v>10.9</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="4">
         <v>13.9</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
       </c>
+      <c r="F21" s="5">
+        <v>3</v>
+      </c>
+      <c r="G21" t="s">
+        <v>64</v>
+      </c>
+      <c r="H21" t="s">
+        <v>14</v>
+      </c>
       <c r="I21" t="s">
-        <v>58</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>15</v>
+        <v>65</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B22" s="3">
-        <v>39.9</v>
+        <v>36.9</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -1388,30 +1433,30 @@
         <v>12</v>
       </c>
       <c r="F22" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H22" t="s">
         <v>14</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>15</v>
+        <v>68</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B23" s="3">
-        <v>16.9</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>62</v>
+        <v>15.9</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="D23" s="4">
         <v>17.9</v>
@@ -1420,30 +1465,30 @@
         <v>12</v>
       </c>
       <c r="F23" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H23" t="s">
         <v>14</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B24" s="3">
         <v>18.8</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>65</v>
+      <c r="C24" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="D24" s="4">
         <v>19.9</v>
@@ -1455,85 +1500,85 @@
         <v>1.1</v>
       </c>
       <c r="G24" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H24" t="s">
         <v>14</v>
       </c>
-      <c r="I24" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>15</v>
+      <c r="I24" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B25" s="3">
         <v>14.8</v>
       </c>
-      <c r="C25" t="s">
-        <v>12</v>
+      <c r="C25" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="D25" s="4">
         <v>18.9</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>68</v>
+      <c r="E25" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="F25" s="5">
         <v>4.1</v>
       </c>
       <c r="G25" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>15</v>
+      <c r="I25" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B26" s="3">
         <v>19.7</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>62</v>
+      <c r="C26" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="D26" s="4">
         <v>24.9</v>
       </c>
-      <c r="E26" t="s">
-        <v>12</v>
+      <c r="E26" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="F26" s="5">
         <v>5.2</v>
       </c>
       <c r="G26" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s">
         <v>14</v>
       </c>
-      <c r="I26" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>15</v>
+      <c r="I26" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B27" s="3">
         <v>18.69</v>
@@ -1544,28 +1589,28 @@
       <c r="D27" s="4">
         <v>26.9</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>73</v>
+      <c r="E27" s="8" t="s">
+        <v>82</v>
       </c>
       <c r="F27" s="5">
         <v>8.21</v>
       </c>
       <c r="G27" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s">
         <v>14</v>
       </c>
-      <c r="I27" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>15</v>
+      <c r="I27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B28" s="3">
         <v>14.94</v>
@@ -1576,60 +1621,60 @@
       <c r="D28" s="4">
         <v>22.9</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>76</v>
+      <c r="E28" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="F28" s="5">
         <v>7.96</v>
       </c>
       <c r="G28" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H28" t="s">
         <v>14</v>
       </c>
-      <c r="I28" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>15</v>
+      <c r="I28" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B29" s="3">
         <v>41.5</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>79</v>
+      <c r="C29" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="D29" s="4">
         <v>48.9</v>
       </c>
-      <c r="E29" t="s">
-        <v>12</v>
+      <c r="E29" s="8" t="s">
+        <v>88</v>
       </c>
       <c r="F29" s="5">
         <v>7.4</v>
       </c>
       <c r="G29" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s">
         <v>14</v>
       </c>
-      <c r="I29" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>15</v>
+      <c r="I29" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1643,7 +1688,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B31" s="3">
         <v>15.9</v>
@@ -1661,27 +1706,27 @@
         <v>4</v>
       </c>
       <c r="G31" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H31" t="s">
         <v>14</v>
       </c>
-      <c r="I31" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>15</v>
+      <c r="I31" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B32" s="3">
-        <v>8.9</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>84</v>
+        <v>7.9</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>93</v>
       </c>
       <c r="D32" s="4">
         <v>9.9</v>
@@ -1690,24 +1735,24 @@
         <v>12</v>
       </c>
       <c r="F32" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="H32" t="s">
         <v>14</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B33" s="3">
         <v>6.9</v>
@@ -1725,24 +1770,24 @@
         <v>2</v>
       </c>
       <c r="G33" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H33" t="s">
         <v>14</v>
       </c>
-      <c r="I33" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>15</v>
+      <c r="I33" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B34" s="3">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
       <c r="C34" t="s">
         <v>12</v>
@@ -1754,94 +1799,94 @@
         <v>12</v>
       </c>
       <c r="F34" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H34" t="s">
         <v>14</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>91</v>
-      </c>
-      <c r="B35" s="3">
-        <v>4.9</v>
+        <v>98</v>
+      </c>
+      <c r="B35" s="10">
+        <v>5.9</v>
       </c>
       <c r="C35" t="s">
         <v>12</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="10">
         <v>5.9</v>
       </c>
       <c r="E35" t="s">
         <v>12</v>
       </c>
       <c r="F35" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H35" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>15</v>
+        <v>100</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B36" s="11">
-        <v>483.3</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" s="11">
+      <c r="A36" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="12">
+        <v>488.1</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D36" s="12">
         <v>593.37</v>
       </c>
-      <c r="E36" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F36" s="10">
-        <v>110.07</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
+      <c r="E36" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F36" s="11">
+        <v>105.27</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
+      <c r="A37" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="103">
   <si>
     <t>מוצר</t>
   </si>
@@ -52,13 +52,13 @@
     <t>—</t>
   </si>
   <si>
-    <t>7.5%</t>
+    <t>2.0%</t>
   </si>
   <si>
     <t>אושר עד</t>
   </si>
   <si>
-    <t>⬇ -0.40 ₪</t>
+    <t>⬆ +0.40 ₪</t>
   </si>
   <si>
     <t>ללא שינוי</t>
@@ -73,10 +73,10 @@
     <t>גבינה צהובה 9% פרוסות 200 גרם</t>
   </si>
   <si>
-    <t>9.6%</t>
-  </si>
-  <si>
-    <t>⬇ -0.60 ₪</t>
+    <t>6.7%</t>
+  </si>
+  <si>
+    <t>⬆ +0.60 ₪</t>
   </si>
   <si>
     <t>מאכל ושתיה סגורים</t>
@@ -85,250 +85,241 @@
     <t>טונה סטארקיסט בשמן 4X160 גרם</t>
   </si>
   <si>
-    <t>22.00 (2 ב-44)</t>
-  </si>
-  <si>
     <t>23.00 (2 ב-46)</t>
   </si>
   <si>
-    <t>7.4%</t>
+    <t>18.6%</t>
+  </si>
+  <si>
+    <t>⬇ -3.00 ₪</t>
+  </si>
+  <si>
+    <t>קפה נמס טסטרס צויס 200 גרם</t>
+  </si>
+  <si>
+    <t>10.0%</t>
+  </si>
+  <si>
+    <t>⬆ +1.00 ₪</t>
+  </si>
+  <si>
+    <t>ביצים L (מנורמל ל-12 יח')</t>
+  </si>
+  <si>
+    <t>8.2%</t>
+  </si>
+  <si>
+    <t>קוקה קולה זירו 1.5 ליטר</t>
+  </si>
+  <si>
+    <t>2.7%</t>
+  </si>
+  <si>
+    <t>שופרסל</t>
+  </si>
+  <si>
+    <t>⬆ +0.30 ₪</t>
+  </si>
+  <si>
+    <t>סירופ יכין פטל דיאט 1 ליטר</t>
+  </si>
+  <si>
+    <t>28.8%</t>
+  </si>
+  <si>
+    <t>יין סגל אדום יבש 750 מ"ל</t>
+  </si>
+  <si>
+    <t>20.1%</t>
+  </si>
+  <si>
+    <t>יין טפרברג מוסקטו לבן 750 מ"ל</t>
+  </si>
+  <si>
+    <t>40.00 (2 ב-80)</t>
+  </si>
+  <si>
+    <t>42.50 (2 ב-85)</t>
+  </si>
+  <si>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>שיבולת שועל קוואקר 500 גרם</t>
+  </si>
+  <si>
+    <t>11.00 (2 ב-22)</t>
+  </si>
+  <si>
+    <t>חמאת בוטנים טבעית בטר אנד דיפרנט 350 גרם</t>
+  </si>
+  <si>
+    <t>17.8%</t>
+  </si>
+  <si>
+    <t>ספגטי אסם 500 גרם</t>
+  </si>
+  <si>
+    <t>4.00 (5 ב-20)</t>
+  </si>
+  <si>
+    <t>6.00 (3 ב-18)</t>
+  </si>
+  <si>
+    <t>27.8%</t>
+  </si>
+  <si>
+    <t>⬆ +0.80 ₪</t>
+  </si>
+  <si>
+    <t>פסטה פנה ריגטה ברילה 500 גרם</t>
+  </si>
+  <si>
+    <t>6.67 (3 ב-20)</t>
+  </si>
+  <si>
+    <t>20.2%</t>
+  </si>
+  <si>
+    <t>דבש טבעי עמק חפר 350 גרם</t>
+  </si>
+  <si>
+    <t>14.90</t>
+  </si>
+  <si>
+    <t>47.3%</t>
+  </si>
+  <si>
+    <t>רביולי גבינה קלאסי שטראוס 400 גרם</t>
+  </si>
+  <si>
+    <t>12.90</t>
+  </si>
+  <si>
+    <t>17.5%</t>
+  </si>
+  <si>
+    <t>ניקיון וטואלטיקה</t>
+  </si>
+  <si>
+    <t>מגבות נייר ניקול 6 גלילים</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>נייר טואלט לילי פסטל 32 גלילים</t>
+  </si>
+  <si>
+    <t>9.1%</t>
   </si>
   <si>
     <t>⬆ +3.00 ₪</t>
   </si>
   <si>
-    <t>קפה נמס טסטרס צויס 200 גרם</t>
-  </si>
-  <si>
-    <t>12.5%</t>
+    <t>אקונומיקה סנו גאוול 4 ליטר</t>
+  </si>
+  <si>
+    <t>15.00 (2 ב-30)</t>
+  </si>
+  <si>
+    <t>5.6%</t>
+  </si>
+  <si>
+    <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
+  </si>
+  <si>
+    <t>9.90</t>
+  </si>
+  <si>
+    <t>5.5%</t>
+  </si>
+  <si>
+    <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
+  </si>
+  <si>
+    <t>16.00 (2 ב-32)</t>
+  </si>
+  <si>
+    <t>21.7%</t>
+  </si>
+  <si>
+    <t>מגבוני האגיס ללא בישום 4X56</t>
+  </si>
+  <si>
+    <t>19.00 (2 ב-38)</t>
+  </si>
+  <si>
+    <t>20.9%</t>
+  </si>
+  <si>
+    <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
+  </si>
+  <si>
+    <t>21.00 (2 ב-42)</t>
+  </si>
+  <si>
+    <t>30.5%</t>
+  </si>
+  <si>
+    <t>שמפו פנטן משקם 600 מ"ל</t>
+  </si>
+  <si>
+    <t>34.8%</t>
+  </si>
+  <si>
+    <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
+  </si>
+  <si>
+    <t>33.33 (3 ב-100)</t>
+  </si>
+  <si>
+    <t>15.1%</t>
+  </si>
+  <si>
+    <t>פירות וירקות</t>
+  </si>
+  <si>
+    <t>תפוח עץ פינק ליידי 1 ק"ג</t>
+  </si>
+  <si>
+    <t>עגבניה (ק"ג)</t>
+  </si>
+  <si>
+    <t>6.90</t>
+  </si>
+  <si>
+    <t>30.3%</t>
   </si>
   <si>
     <t>⬇ -1.00 ₪</t>
   </si>
   <si>
-    <t>ביצים L (מנורמל ל-12 יח')</t>
-  </si>
-  <si>
-    <t>8.2%</t>
-  </si>
-  <si>
-    <t>קוקה קולה זירו 1.5 ליטר</t>
-  </si>
-  <si>
-    <t>1.0%</t>
-  </si>
-  <si>
-    <t>⬇ -0.30 ₪</t>
-  </si>
-  <si>
-    <t>סירופ יכין פטל דיאט 1 ליטר</t>
-  </si>
-  <si>
-    <t>28.8%</t>
-  </si>
-  <si>
-    <t>יין סגל אדום יבש 750 מ"ל</t>
-  </si>
-  <si>
-    <t>20.1%</t>
-  </si>
-  <si>
-    <t>יין טפרברג מוסקטו לבן 750 מ"ל</t>
-  </si>
-  <si>
-    <t>40.00 (2 ב-80)</t>
-  </si>
-  <si>
-    <t>42.50 (2 ב-85)</t>
-  </si>
-  <si>
-    <t>6.5%</t>
-  </si>
-  <si>
-    <t>שיבולת שועל קוואקר 500 גרם</t>
-  </si>
-  <si>
-    <t>11.00 (2 ב-22)</t>
-  </si>
-  <si>
-    <t>חמאת בוטנים טבעית בטר אנד דיפרנט 350 גרם</t>
-  </si>
-  <si>
-    <t>23.7%</t>
-  </si>
-  <si>
-    <t>ספגטי אסם 500 גרם</t>
-  </si>
-  <si>
-    <t>4.00 (5 ב-20)</t>
-  </si>
-  <si>
-    <t>6.00 (3 ב-18)</t>
-  </si>
-  <si>
-    <t>38.0%</t>
-  </si>
-  <si>
-    <t>⬇ -0.80 ₪</t>
-  </si>
-  <si>
-    <t>פסטה פנה ריגטה ברילה 500 גרם</t>
-  </si>
-  <si>
-    <t>6.67 (3 ב-20)</t>
-  </si>
-  <si>
-    <t>20.2%</t>
-  </si>
-  <si>
-    <t>דבש טבעי עמק חפר 350 גרם</t>
-  </si>
-  <si>
-    <t>14.90</t>
-  </si>
-  <si>
-    <t>47.3%</t>
-  </si>
-  <si>
-    <t>רביולי גבינה קלאסי שטראוס 400 גרם</t>
-  </si>
-  <si>
-    <t>12.90</t>
-  </si>
-  <si>
-    <t>17.5%</t>
-  </si>
-  <si>
-    <t>ניקיון וטואלטיקה</t>
-  </si>
-  <si>
-    <t>מגבות נייר ניקול 6 גלילים</t>
-  </si>
-  <si>
-    <t>21.6%</t>
-  </si>
-  <si>
-    <t>אין נתון קודם</t>
-  </si>
-  <si>
-    <t>נייר טואלט לילי פסטל 32 גלילים</t>
-  </si>
-  <si>
-    <t>15.9%</t>
-  </si>
-  <si>
-    <t>⬇ -3.00 ₪</t>
-  </si>
-  <si>
-    <t>אקונומיקה סנו גאוול 4 ליטר</t>
-  </si>
-  <si>
-    <t>15.00 (2 ב-30)</t>
-  </si>
-  <si>
-    <t>11.2%</t>
-  </si>
-  <si>
-    <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
-  </si>
-  <si>
-    <t>9.90</t>
-  </si>
-  <si>
-    <t>5.5%</t>
-  </si>
-  <si>
-    <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
-  </si>
-  <si>
-    <t>16.00 (2 ב-32)</t>
-  </si>
-  <si>
-    <t>21.7%</t>
-  </si>
-  <si>
-    <t>מגבוני האגיס ללא בישום 4X56</t>
-  </si>
-  <si>
-    <t>19.00 (2 ב-38)</t>
-  </si>
-  <si>
-    <t>20.9%</t>
-  </si>
-  <si>
-    <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
-  </si>
-  <si>
-    <t>21.00 (2 ב-42)</t>
-  </si>
-  <si>
-    <t>30.5%</t>
-  </si>
-  <si>
-    <t>שמפו פנטן משקם 600 מ"ל</t>
-  </si>
-  <si>
-    <t>34.8%</t>
-  </si>
-  <si>
-    <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
-  </si>
-  <si>
-    <t>21.90</t>
-  </si>
-  <si>
-    <t>33.33 (3 ב-100)</t>
-  </si>
-  <si>
-    <t>15.1%</t>
-  </si>
-  <si>
-    <t>פירות וירקות</t>
-  </si>
-  <si>
-    <t>תפוח עץ פינק ליידי 1 ק"ג</t>
-  </si>
-  <si>
-    <t>עגבניה (ק"ג)</t>
-  </si>
-  <si>
-    <t>7.90</t>
-  </si>
-  <si>
     <t>מלפפון (ק"ג)</t>
   </si>
   <si>
-    <t>22.5%</t>
+    <t>33.7%</t>
   </si>
   <si>
     <t>בננות (ק"ג)</t>
   </si>
   <si>
-    <t>31.0%</t>
+    <t>23.3%</t>
   </si>
   <si>
     <t>בצל יבש (ק"ג)</t>
   </si>
   <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>שווה</t>
-  </si>
-  <si>
-    <t>⬆ +1.00 ₪</t>
+    <t>16.9%</t>
   </si>
   <si>
     <t>סה"כ</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>17.7%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-27 מול 2026-10-26 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>19.1%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-28 מול 2026-10-27 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -384,7 +375,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
+        <fgColor rgb="FFFFCCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -399,7 +390,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -849,7 +840,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -861,7 +852,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="5">
-        <v>0.55</v>
+        <v>0.15</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -913,7 +904,7 @@
         <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>18.9</v>
+        <v>19.5</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
@@ -925,7 +916,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="5">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="G5" t="s">
         <v>20</v>
@@ -959,28 +950,28 @@
         <v>23</v>
       </c>
       <c r="B7" s="3">
-        <v>24.9</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>24</v>
+        <v>21.9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
       </c>
       <c r="D7" s="4">
         <v>26.9</v>
       </c>
       <c r="E7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="5">
+        <v>5</v>
+      </c>
+      <c r="G7" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="5">
-        <v>2</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>26</v>
-      </c>
-      <c r="H7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>27</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>16</v>
@@ -988,10 +979,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="3">
-        <v>34.9</v>
+        <v>35.9</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
@@ -1003,16 +994,16 @@
         <v>12</v>
       </c>
       <c r="F8" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="H8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>16</v>
@@ -1020,7 +1011,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="3">
         <v>13.07</v>
@@ -1038,7 +1029,7 @@
         <v>1.17</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
@@ -1052,28 +1043,28 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="4">
+        <v>8.2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="3">
+        <v>7.98</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="G10" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="3">
-        <v>7.9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="4">
-        <v>7.98</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>34</v>
-      </c>
-      <c r="H10" t="s">
-        <v>14</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>35</v>
@@ -1215,7 +1206,7 @@
         <v>46</v>
       </c>
       <c r="B15" s="3">
-        <v>12.9</v>
+        <v>13.9</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -1227,7 +1218,7 @@
         <v>12</v>
       </c>
       <c r="F15" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" t="s">
         <v>47</v>
@@ -1236,7 +1227,7 @@
         <v>14</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J15" s="7" t="s">
         <v>16</v>
@@ -1247,7 +1238,7 @@
         <v>48</v>
       </c>
       <c r="B16" s="3">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>49</v>
@@ -1259,7 +1250,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="5">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="G16" t="s">
         <v>51</v>
@@ -1388,29 +1379,23 @@
       <c r="A21" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="3">
-        <v>10.9</v>
-      </c>
       <c r="C21" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="10">
         <v>13.9</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
-      </c>
-      <c r="F21" s="5">
-        <v>3</v>
       </c>
       <c r="G21" t="s">
         <v>64</v>
       </c>
       <c r="H21" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="I21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J21" s="7" t="s">
         <v>16</v>
@@ -1418,10 +1403,10 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B22" s="3">
-        <v>36.9</v>
+        <v>39.9</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -1433,16 +1418,16 @@
         <v>12</v>
       </c>
       <c r="F22" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G22" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="H22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>16</v>
@@ -1450,13 +1435,13 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="3">
+        <v>16.9</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="B23" s="3">
-        <v>15.9</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>70</v>
       </c>
       <c r="D23" s="4">
         <v>17.9</v>
@@ -1465,16 +1450,16 @@
         <v>12</v>
       </c>
       <c r="F23" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H23" t="s">
         <v>14</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J23" s="7" t="s">
         <v>16</v>
@@ -1482,13 +1467,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B24" s="3">
         <v>18.8</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D24" s="4">
         <v>19.9</v>
@@ -1500,7 +1485,7 @@
         <v>1.1</v>
       </c>
       <c r="G24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H24" t="s">
         <v>14</v>
@@ -1514,25 +1499,25 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B25" s="3">
         <v>14.8</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D25" s="4">
         <v>18.9</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F25" s="5">
         <v>4.1</v>
       </c>
       <c r="G25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H25" t="s">
         <v>14</v>
@@ -1546,25 +1531,25 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B26" s="3">
         <v>19.7</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D26" s="4">
         <v>24.9</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F26" s="5">
         <v>5.2</v>
       </c>
       <c r="G26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s">
         <v>14</v>
@@ -1578,7 +1563,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B27" s="3">
         <v>18.69</v>
@@ -1590,13 +1575,13 @@
         <v>26.9</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F27" s="5">
         <v>8.21</v>
       </c>
       <c r="G27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s">
         <v>14</v>
@@ -1610,7 +1595,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B28" s="3">
         <v>14.94</v>
@@ -1622,13 +1607,13 @@
         <v>22.9</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F28" s="5">
         <v>7.96</v>
       </c>
       <c r="G28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s">
         <v>14</v>
@@ -1642,25 +1627,25 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B29" s="3">
         <v>41.5</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D29" s="4">
         <v>48.9</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F29" s="5">
         <v>7.4</v>
       </c>
       <c r="G29" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s">
         <v>14</v>
@@ -1674,7 +1659,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1688,7 +1673,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B31" s="3">
         <v>15.9</v>
@@ -1720,13 +1705,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B32" s="3">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D32" s="4">
         <v>9.9</v>
@@ -1735,16 +1720,16 @@
         <v>12</v>
       </c>
       <c r="F32" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="H32" t="s">
         <v>14</v>
       </c>
-      <c r="I32" s="6" t="s">
-        <v>30</v>
+      <c r="I32" s="9" t="s">
+        <v>93</v>
       </c>
       <c r="J32" s="7" t="s">
         <v>16</v>
@@ -1755,7 +1740,7 @@
         <v>94</v>
       </c>
       <c r="B33" s="3">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
@@ -1767,7 +1752,7 @@
         <v>12</v>
       </c>
       <c r="F33" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" t="s">
         <v>95</v>
@@ -1775,8 +1760,8 @@
       <c r="H33" t="s">
         <v>14</v>
       </c>
-      <c r="I33" s="7" t="s">
-        <v>16</v>
+      <c r="I33" s="9" t="s">
+        <v>93</v>
       </c>
       <c r="J33" s="7" t="s">
         <v>16</v>
@@ -1787,7 +1772,7 @@
         <v>96</v>
       </c>
       <c r="B34" s="3">
-        <v>8.9</v>
+        <v>9.9</v>
       </c>
       <c r="C34" t="s">
         <v>12</v>
@@ -1799,7 +1784,7 @@
         <v>12</v>
       </c>
       <c r="F34" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G34" t="s">
         <v>97</v>
@@ -1808,7 +1793,7 @@
         <v>14</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J34" s="7" t="s">
         <v>16</v>
@@ -1818,29 +1803,29 @@
       <c r="A35" t="s">
         <v>98</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="3">
+        <v>4.9</v>
+      </c>
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="4">
         <v>5.9</v>
       </c>
-      <c r="C35" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="10">
-        <v>5.9</v>
-      </c>
       <c r="E35" t="s">
         <v>12</v>
       </c>
       <c r="F35" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="s">
         <v>99</v>
       </c>
       <c r="H35" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="J35" s="7" t="s">
         <v>16</v>
@@ -1848,25 +1833,25 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B36" s="12">
-        <v>488.1</v>
+        <v>480.3</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="D36" s="12">
         <v>593.37</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="F36" s="11">
-        <v>105.27</v>
+        <v>64</v>
+      </c>
+      <c r="F36" s="12">
+        <v>113.07</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H36" s="11" t="s">
         <v>14</v>
@@ -1876,7 +1861,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="95">
   <si>
     <t>מוצר</t>
   </si>
@@ -58,9 +58,6 @@
     <t>אושר עד</t>
   </si>
   <si>
-    <t>⬆ +0.40 ₪</t>
-  </si>
-  <si>
     <t>ללא שינוי</t>
   </si>
   <si>
@@ -76,9 +73,6 @@
     <t>6.7%</t>
   </si>
   <si>
-    <t>⬆ +0.60 ₪</t>
-  </si>
-  <si>
     <t>מאכל ושתיה סגורים</t>
   </si>
   <si>
@@ -91,18 +85,12 @@
     <t>18.6%</t>
   </si>
   <si>
-    <t>⬇ -3.00 ₪</t>
-  </si>
-  <si>
     <t>קפה נמס טסטרס צויס 200 גרם</t>
   </si>
   <si>
     <t>10.0%</t>
   </si>
   <si>
-    <t>⬆ +1.00 ₪</t>
-  </si>
-  <si>
     <t>ביצים L (מנורמל ל-12 יח')</t>
   </si>
   <si>
@@ -118,9 +106,6 @@
     <t>שופרסל</t>
   </si>
   <si>
-    <t>⬆ +0.30 ₪</t>
-  </si>
-  <si>
     <t>סירופ יכין פטל דיאט 1 ליטר</t>
   </si>
   <si>
@@ -169,9 +154,6 @@
     <t>27.8%</t>
   </si>
   <si>
-    <t>⬆ +0.80 ₪</t>
-  </si>
-  <si>
     <t>פסטה פנה ריגטה ברילה 500 גרם</t>
   </si>
   <si>
@@ -214,9 +196,6 @@
     <t>9.1%</t>
   </si>
   <si>
-    <t>⬆ +3.00 ₪</t>
-  </si>
-  <si>
     <t>אקונומיקה סנו גאוול 4 ליטר</t>
   </si>
   <si>
@@ -292,9 +271,6 @@
     <t>30.3%</t>
   </si>
   <si>
-    <t>⬇ -1.00 ₪</t>
-  </si>
-  <si>
     <t>מלפפון (ק"ג)</t>
   </si>
   <si>
@@ -316,10 +292,10 @@
     <t>סה"כ</t>
   </si>
   <si>
-    <t>19.1%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-28 מול 2026-10-27 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>17.1%</t>
+  </si>
+  <si>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-29 מול 2026-10-28 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -346,7 +322,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -375,22 +351,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -416,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -427,13 +393,11 @@
     <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -863,13 +827,13 @@
       <c r="I3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>16</v>
+      <c r="J3" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="3">
         <v>5.9</v>
@@ -887,21 +851,21 @@
         <v>0.5</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>16</v>
+      <c r="I4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="3">
         <v>19.5</v>
@@ -919,21 +883,21 @@
         <v>1.4</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -947,7 +911,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" s="3">
         <v>21.9</v>
@@ -958,28 +922,28 @@
       <c r="D7" s="4">
         <v>26.9</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>24</v>
+      <c r="E7" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="F7" s="5">
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>16</v>
+      <c r="I7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B8" s="3">
         <v>35.9</v>
@@ -997,21 +961,21 @@
         <v>4</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H8" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B9" s="3">
         <v>13.07</v>
@@ -1029,21 +993,21 @@
         <v>1.17</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>16</v>
+      <c r="I9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B10" s="4">
         <v>8.2</v>
@@ -1061,21 +1025,21 @@
         <v>0.22</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B11" s="3">
         <v>9.9</v>
@@ -1093,21 +1057,21 @@
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>16</v>
+      <c r="I11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B12" s="3">
         <v>19.9</v>
@@ -1125,53 +1089,53 @@
         <v>5</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H12" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>16</v>
+      <c r="I12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B13" s="3">
         <v>42.9</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>41</v>
+      <c r="C13" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="D13" s="4">
         <v>45.9</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>42</v>
+      <c r="E13" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="F13" s="5">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H13" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>16</v>
+      <c r="I13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B14" s="3">
         <v>11.9</v>
@@ -1182,28 +1146,28 @@
       <c r="D14" s="4">
         <v>14.9</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>45</v>
+      <c r="E14" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="F14" s="5">
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H14" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>16</v>
+      <c r="I14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B15" s="3">
         <v>13.9</v>
@@ -1221,59 +1185,59 @@
         <v>3</v>
       </c>
       <c r="G15" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H15" t="s">
         <v>14</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B16" s="3">
         <v>5.7</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>49</v>
+      <c r="C16" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="D16" s="4">
         <v>7.9</v>
       </c>
-      <c r="E16" s="8" t="s">
-        <v>50</v>
+      <c r="E16" s="7" t="s">
+        <v>45</v>
       </c>
       <c r="F16" s="5">
         <v>2.2</v>
       </c>
       <c r="G16" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H16" t="s">
         <v>14</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B17" s="3">
         <v>7.9</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>54</v>
+      <c r="C17" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="D17" s="4">
         <v>9.9</v>
@@ -1285,21 +1249,21 @@
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H17" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>16</v>
+      <c r="I17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B18" s="3">
         <v>8.9</v>
@@ -1310,34 +1274,34 @@
       <c r="D18" s="4">
         <v>16.9</v>
       </c>
-      <c r="E18" s="8" t="s">
-        <v>57</v>
+      <c r="E18" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="F18" s="5">
         <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H18" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>16</v>
+      <c r="I18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B19" s="3">
         <v>18.9</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>60</v>
+      <c r="C19" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="D19" s="4">
         <v>22.9</v>
@@ -1349,21 +1313,21 @@
         <v>4</v>
       </c>
       <c r="G19" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H19" t="s">
         <v>14</v>
       </c>
-      <c r="I19" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>16</v>
+      <c r="I19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1377,33 +1341,35 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>63</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B21" s="5"/>
       <c r="C21" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="8">
         <v>13.9</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
       </c>
+      <c r="F21" s="5"/>
       <c r="G21" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="H21" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="I21" t="s">
-        <v>64</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>16</v>
+        <v>58</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B22" s="3">
         <v>39.9</v>
@@ -1421,27 +1387,27 @@
         <v>4</v>
       </c>
       <c r="G22" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H22" t="s">
         <v>14</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B23" s="3">
         <v>16.9</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>69</v>
+      <c r="C23" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D23" s="4">
         <v>17.9</v>
@@ -1453,27 +1419,27 @@
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="H23" t="s">
         <v>14</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B24" s="3">
         <v>18.8</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>72</v>
+      <c r="C24" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="D24" s="4">
         <v>19.9</v>
@@ -1485,85 +1451,85 @@
         <v>1.1</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H24" t="s">
         <v>14</v>
       </c>
-      <c r="I24" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>16</v>
+      <c r="I24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B25" s="3">
         <v>14.8</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>72</v>
+      <c r="C25" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="D25" s="4">
         <v>18.9</v>
       </c>
-      <c r="E25" s="8" t="s">
-        <v>75</v>
+      <c r="E25" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="F25" s="5">
         <v>4.1</v>
       </c>
       <c r="G25" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H25" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>16</v>
+      <c r="I25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B26" s="3">
         <v>19.7</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>69</v>
+      <c r="C26" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="D26" s="4">
         <v>24.9</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>78</v>
+      <c r="E26" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="F26" s="5">
         <v>5.2</v>
       </c>
       <c r="G26" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H26" t="s">
         <v>14</v>
       </c>
-      <c r="I26" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>16</v>
+      <c r="I26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B27" s="3">
         <v>18.69</v>
@@ -1574,28 +1540,28 @@
       <c r="D27" s="4">
         <v>26.9</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>81</v>
+      <c r="E27" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="F27" s="5">
         <v>8.21</v>
       </c>
       <c r="G27" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H27" t="s">
         <v>14</v>
       </c>
-      <c r="I27" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>16</v>
+      <c r="I27" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B28" s="3">
         <v>14.94</v>
@@ -1606,60 +1572,60 @@
       <c r="D28" s="4">
         <v>22.9</v>
       </c>
-      <c r="E28" s="8" t="s">
-        <v>78</v>
+      <c r="E28" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="F28" s="5">
         <v>7.96</v>
       </c>
       <c r="G28" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s">
         <v>14</v>
       </c>
-      <c r="I28" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>16</v>
+      <c r="I28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B29" s="3">
         <v>41.5</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>86</v>
+      <c r="C29" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="D29" s="4">
         <v>48.9</v>
       </c>
-      <c r="E29" s="8" t="s">
-        <v>86</v>
+      <c r="E29" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="F29" s="5">
         <v>7.4</v>
       </c>
       <c r="G29" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s">
         <v>14</v>
       </c>
-      <c r="I29" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>16</v>
+      <c r="I29" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1673,7 +1639,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B31" s="3">
         <v>15.9</v>
@@ -1691,27 +1657,27 @@
         <v>4</v>
       </c>
       <c r="G31" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H31" t="s">
         <v>14</v>
       </c>
-      <c r="I31" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>16</v>
+      <c r="I31" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B32" s="3">
         <v>6.9</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>91</v>
+      <c r="C32" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="D32" s="4">
         <v>9.9</v>
@@ -1723,21 +1689,21 @@
         <v>3</v>
       </c>
       <c r="G32" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H32" t="s">
         <v>14</v>
       </c>
-      <c r="I32" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>16</v>
+      <c r="I32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B33" s="3">
         <v>5.9</v>
@@ -1755,21 +1721,21 @@
         <v>3</v>
       </c>
       <c r="G33" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s">
         <v>14</v>
       </c>
-      <c r="I33" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>16</v>
+      <c r="I33" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B34" s="3">
         <v>9.9</v>
@@ -1787,21 +1753,21 @@
         <v>3</v>
       </c>
       <c r="G34" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s">
         <v>14</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B35" s="3">
         <v>4.9</v>
@@ -1819,59 +1785,59 @@
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s">
         <v>14</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="I35" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="10">
+        <v>480.3</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="10">
+        <v>579.47</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" s="10">
+        <v>99.17</v>
+      </c>
+      <c r="G36" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="J35" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B36" s="12">
-        <v>480.3</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D36" s="12">
-        <v>593.37</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F36" s="12">
-        <v>113.07</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
+      <c r="H36" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
+      <c r="A37" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/grocery-prices/latest.xlsx
+++ b/grocery-prices/latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="58">
   <si>
     <t>מוצר</t>
   </si>
@@ -52,10 +52,7 @@
     <t>—</t>
   </si>
   <si>
-    <t>2.0%</t>
-  </si>
-  <si>
-    <t>אושר עד</t>
+    <t/>
   </si>
   <si>
     <t>ללא שינוי</t>
@@ -64,15 +61,9 @@
     <t>קוטג' תנובה 5% 250 גרם</t>
   </si>
   <si>
-    <t>7.8%</t>
-  </si>
-  <si>
     <t>גבינה צהובה 9% פרוסות 200 גרם</t>
   </si>
   <si>
-    <t>6.7%</t>
-  </si>
-  <si>
     <t>מאכל ושתיה סגורים</t>
   </si>
   <si>
@@ -82,54 +73,27 @@
     <t>23.00 (2 ב-46)</t>
   </si>
   <si>
-    <t>18.6%</t>
-  </si>
-  <si>
     <t>קפה נמס טסטרס צויס 200 גרם</t>
   </si>
   <si>
-    <t>10.0%</t>
-  </si>
-  <si>
     <t>ביצים L (מנורמל ל-12 יח')</t>
   </si>
   <si>
-    <t>8.2%</t>
-  </si>
-  <si>
     <t>קוקה קולה זירו 1.5 ליטר</t>
   </si>
   <si>
-    <t>2.7%</t>
-  </si>
-  <si>
-    <t>שופרסל</t>
-  </si>
-  <si>
     <t>סירופ יכין פטל דיאט 1 ליטר</t>
   </si>
   <si>
-    <t>28.8%</t>
-  </si>
-  <si>
     <t>יין סגל אדום יבש 750 מ"ל</t>
   </si>
   <si>
-    <t>20.1%</t>
-  </si>
-  <si>
     <t>יין טפרברג מוסקטו לבן 750 מ"ל</t>
   </si>
   <si>
-    <t>40.00 (2 ב-80)</t>
-  </si>
-  <si>
     <t>42.50 (2 ב-85)</t>
   </si>
   <si>
-    <t>6.5%</t>
-  </si>
-  <si>
     <t>שיבולת שועל קוואקר 500 גרם</t>
   </si>
   <si>
@@ -139,123 +103,66 @@
     <t>חמאת בוטנים טבעית בטר אנד דיפרנט 350 גרם</t>
   </si>
   <si>
-    <t>17.8%</t>
-  </si>
-  <si>
     <t>ספגטי אסם 500 גרם</t>
   </si>
   <si>
-    <t>4.00 (5 ב-20)</t>
-  </si>
-  <si>
     <t>6.00 (3 ב-18)</t>
   </si>
   <si>
-    <t>27.8%</t>
-  </si>
-  <si>
     <t>פסטה פנה ריגטה ברילה 500 גרם</t>
   </si>
   <si>
-    <t>6.67 (3 ב-20)</t>
-  </si>
-  <si>
-    <t>20.2%</t>
-  </si>
-  <si>
     <t>דבש טבעי עמק חפר 350 גרם</t>
   </si>
   <si>
     <t>14.90</t>
   </si>
   <si>
-    <t>47.3%</t>
-  </si>
-  <si>
     <t>רביולי גבינה קלאסי שטראוס 400 גרם</t>
   </si>
   <si>
-    <t>12.90</t>
-  </si>
-  <si>
-    <t>17.5%</t>
-  </si>
-  <si>
     <t>ניקיון וטואלטיקה</t>
   </si>
   <si>
     <t>מגבות נייר ניקול 6 גלילים</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>נייר טואלט לילי פסטל 32 גלילים</t>
   </si>
   <si>
-    <t>9.1%</t>
-  </si>
-  <si>
     <t>אקונומיקה סנו גאוול 4 ליטר</t>
   </si>
   <si>
-    <t>15.00 (2 ב-30)</t>
-  </si>
-  <si>
-    <t>5.6%</t>
-  </si>
-  <si>
     <t>מרכך כביסה מקסימה מרוכז 1 ליטר</t>
   </si>
   <si>
-    <t>9.90</t>
-  </si>
-  <si>
-    <t>5.5%</t>
-  </si>
-  <si>
     <t>כדוריות ניקוי אסלה סוד לימון 150 גרם</t>
   </si>
   <si>
     <t>16.00 (2 ב-32)</t>
   </si>
   <si>
-    <t>21.7%</t>
-  </si>
-  <si>
     <t>מגבוני האגיס ללא בישום 4X56</t>
   </si>
   <si>
     <t>19.00 (2 ב-38)</t>
   </si>
   <si>
-    <t>20.9%</t>
-  </si>
-  <si>
     <t>שמפו הד&amp;שולדרס קלאסי 625 מ"ל</t>
   </si>
   <si>
     <t>21.00 (2 ב-42)</t>
   </si>
   <si>
-    <t>30.5%</t>
-  </si>
-  <si>
     <t>שמפו פנטן משקם 600 מ"ל</t>
   </si>
   <si>
-    <t>34.8%</t>
-  </si>
-  <si>
     <t>חיתולי האגיס פרידום מידה 4, 38 יח'</t>
   </si>
   <si>
     <t>33.33 (3 ב-100)</t>
   </si>
   <si>
-    <t>15.1%</t>
-  </si>
-  <si>
     <t>פירות וירקות</t>
   </si>
   <si>
@@ -265,37 +172,19 @@
     <t>עגבניה (ק"ג)</t>
   </si>
   <si>
-    <t>6.90</t>
-  </si>
-  <si>
-    <t>30.3%</t>
-  </si>
-  <si>
     <t>מלפפון (ק"ג)</t>
   </si>
   <si>
-    <t>33.7%</t>
-  </si>
-  <si>
     <t>בננות (ק"ג)</t>
   </si>
   <si>
-    <t>23.3%</t>
-  </si>
-  <si>
     <t>בצל יבש (ק"ג)</t>
   </si>
   <si>
-    <t>16.9%</t>
-  </si>
-  <si>
     <t>סה"כ</t>
   </si>
   <si>
-    <t>17.1%</t>
-  </si>
-  <si>
-    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-29 מול 2026-10-28 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
+    <t>מקרא: עמודות 'שינוי' משוות את מחיר 2026-10-30 מול 2026-10-29 — אדום = מחיר עלה, ירוק = מחיר ירד, אפור = ללא שינוי. עמודות 'מבצע' = מחיר ליחידה במבצע אוטומטי בקופה (לא כולל מבצעי מועדון/קופון); המיון וההפרש מבוססים על מחיר המדף בלבד.</t>
   </si>
 </sst>
 </file>
@@ -322,7 +211,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -341,12 +230,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6E0B4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8CBAD"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -357,11 +241,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -382,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -390,14 +269,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -803,9 +680,7 @@
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3">
-        <v>7.2</v>
-      </c>
+      <c r="B3" s="3"/>
       <c r="C3" t="s">
         <v>12</v>
       </c>
@@ -815,29 +690,25 @@
       <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="5">
-        <v>0.15</v>
-      </c>
+      <c r="F3" s="3"/>
       <c r="G3" t="s">
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="3">
-        <v>5.9</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B4" s="3"/>
       <c r="C4" t="s">
         <v>12</v>
       </c>
@@ -847,29 +718,25 @@
       <c r="E4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="5">
-        <v>0.5</v>
-      </c>
+      <c r="F4" s="3"/>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3">
-        <v>19.5</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B5" s="3"/>
       <c r="C5" t="s">
         <v>12</v>
       </c>
@@ -879,25 +746,23 @@
       <c r="E5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="5">
-        <v>1.4</v>
-      </c>
+      <c r="F5" s="3"/>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -911,43 +776,37 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="3">
-        <v>21.9</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B7" s="3"/>
       <c r="C7" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="4">
         <v>26.9</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="5">
-        <v>5</v>
-      </c>
+      <c r="E7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="3">
-        <v>35.9</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B8" s="3"/>
       <c r="C8" t="s">
         <v>12</v>
       </c>
@@ -957,29 +816,25 @@
       <c r="E8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="5">
-        <v>4</v>
-      </c>
+      <c r="F8" s="3"/>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="3">
-        <v>13.07</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B9" s="3"/>
       <c r="C9" t="s">
         <v>12</v>
       </c>
@@ -989,61 +844,53 @@
       <c r="E9" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="5">
-        <v>1.17</v>
-      </c>
+      <c r="F9" s="3"/>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="4">
-        <v>8.2</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B10" s="3"/>
       <c r="C10" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="4">
         <v>7.98</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="5">
-        <v>0.22</v>
-      </c>
+      <c r="F10" s="3"/>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="3">
-        <v>9.9</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B11" s="3"/>
       <c r="C11" t="s">
         <v>12</v>
       </c>
@@ -1053,29 +900,25 @@
       <c r="E11" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="5">
-        <v>4</v>
-      </c>
+      <c r="F11" s="3"/>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="3">
-        <v>19.9</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B12" s="3"/>
       <c r="C12" t="s">
         <v>12</v>
       </c>
@@ -1085,93 +928,81 @@
       <c r="E12" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="5">
-        <v>5</v>
-      </c>
+      <c r="F12" s="3"/>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="3">
-        <v>42.9</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>36</v>
+        <v>25</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" t="s">
+        <v>12</v>
       </c>
       <c r="D13" s="4">
         <v>45.9</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="5">
-        <v>3</v>
-      </c>
+      <c r="E13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="3"/>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="3">
-        <v>11.9</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B14" s="3"/>
       <c r="C14" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="4">
         <v>14.9</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="5">
-        <v>3</v>
-      </c>
+      <c r="E14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="3"/>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="3">
-        <v>13.9</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B15" s="3"/>
       <c r="C15" t="s">
         <v>12</v>
       </c>
@@ -1181,63 +1012,55 @@
       <c r="E15" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="5">
-        <v>3</v>
-      </c>
+      <c r="F15" s="3"/>
       <c r="G15" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="3">
-        <v>5.7</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>44</v>
+        <v>30</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" t="s">
+        <v>12</v>
       </c>
       <c r="D16" s="4">
         <v>7.9</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="5">
-        <v>2.2</v>
-      </c>
+      <c r="E16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="3"/>
       <c r="G16" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="3">
-        <v>7.9</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>48</v>
+        <v>32</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" t="s">
+        <v>12</v>
       </c>
       <c r="D17" s="4">
         <v>9.9</v>
@@ -1245,63 +1068,55 @@
       <c r="E17" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="5">
-        <v>2</v>
-      </c>
+      <c r="F17" s="3"/>
       <c r="G17" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="3">
-        <v>8.9</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B18" s="3"/>
       <c r="C18" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="4">
         <v>16.9</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="5">
-        <v>8</v>
-      </c>
+      <c r="E18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="3"/>
       <c r="G18" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="3">
-        <v>18.9</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>54</v>
+        <v>35</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" t="s">
+        <v>12</v>
       </c>
       <c r="D19" s="4">
         <v>22.9</v>
@@ -1309,25 +1124,23 @@
       <c r="E19" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="5">
-        <v>4</v>
-      </c>
+      <c r="F19" s="3"/>
       <c r="G19" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="H19" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1341,39 +1154,37 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="B21" s="3"/>
       <c r="C21" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="4">
         <v>13.9</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="5"/>
+      <c r="F21" s="3"/>
       <c r="G21" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="H21" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="I21" t="s">
-        <v>58</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="3">
-        <v>39.9</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B22" s="3"/>
       <c r="C22" t="s">
         <v>12</v>
       </c>
@@ -1383,31 +1194,27 @@
       <c r="E22" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="5">
-        <v>4</v>
-      </c>
+      <c r="F22" s="3"/>
       <c r="G22" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="H22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I22" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23" s="3">
-        <v>16.9</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>62</v>
+        <v>39</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" t="s">
+        <v>12</v>
       </c>
       <c r="D23" s="4">
         <v>17.9</v>
@@ -1415,31 +1222,27 @@
       <c r="E23" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="5">
-        <v>1</v>
-      </c>
+      <c r="F23" s="3"/>
       <c r="G23" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I23" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>64</v>
-      </c>
-      <c r="B24" s="3">
-        <v>18.8</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>65</v>
+        <v>40</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" t="s">
+        <v>12</v>
       </c>
       <c r="D24" s="4">
         <v>19.9</v>
@@ -1447,185 +1250,163 @@
       <c r="E24" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="5">
-        <v>1.1</v>
-      </c>
+      <c r="F24" s="3"/>
       <c r="G24" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="H24" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" s="3">
-        <v>14.8</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>65</v>
+        <v>41</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" t="s">
+        <v>12</v>
       </c>
       <c r="D25" s="4">
         <v>18.9</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25" s="5">
-        <v>4.1</v>
-      </c>
+      <c r="E25" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="3"/>
       <c r="G25" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="H25" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I25" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" s="3">
-        <v>19.7</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>62</v>
+        <v>43</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" t="s">
+        <v>12</v>
       </c>
       <c r="D26" s="4">
         <v>24.9</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F26" s="5">
-        <v>5.2</v>
-      </c>
+      <c r="E26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="3"/>
       <c r="G26" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="H26" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I26" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="3">
-        <v>18.69</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B27" s="3"/>
       <c r="C27" t="s">
         <v>12</v>
       </c>
       <c r="D27" s="4">
         <v>26.9</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="5">
-        <v>8.21</v>
-      </c>
+      <c r="E27" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="3"/>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="H27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I27" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>76</v>
-      </c>
-      <c r="B28" s="3">
-        <v>14.94</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B28" s="3"/>
       <c r="C28" t="s">
         <v>12</v>
       </c>
       <c r="D28" s="4">
         <v>22.9</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F28" s="5">
-        <v>7.96</v>
-      </c>
+      <c r="E28" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" s="3"/>
       <c r="G28" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="H28" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I28" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>78</v>
-      </c>
-      <c r="B29" s="3">
-        <v>41.5</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>79</v>
+        <v>48</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" t="s">
+        <v>12</v>
       </c>
       <c r="D29" s="4">
         <v>48.9</v>
       </c>
-      <c r="E29" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F29" s="5">
-        <v>7.4</v>
-      </c>
+      <c r="E29" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F29" s="3"/>
       <c r="G29" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="H29" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I29" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1639,11 +1420,9 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>82</v>
-      </c>
-      <c r="B31" s="3">
-        <v>15.9</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B31" s="3"/>
       <c r="C31" t="s">
         <v>12</v>
       </c>
@@ -1653,31 +1432,27 @@
       <c r="E31" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="5">
-        <v>4</v>
-      </c>
+      <c r="F31" s="3"/>
       <c r="G31" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="H31" t="s">
-        <v>14</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I31" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>83</v>
-      </c>
-      <c r="B32" s="3">
-        <v>6.9</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>84</v>
+        <v>52</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" t="s">
+        <v>12</v>
       </c>
       <c r="D32" s="4">
         <v>9.9</v>
@@ -1685,29 +1460,25 @@
       <c r="E32" t="s">
         <v>12</v>
       </c>
-      <c r="F32" s="5">
-        <v>3</v>
-      </c>
+      <c r="F32" s="3"/>
       <c r="G32" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="H32" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>86</v>
-      </c>
-      <c r="B33" s="3">
-        <v>5.9</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B33" s="3"/>
       <c r="C33" t="s">
         <v>12</v>
       </c>
@@ -1717,29 +1488,25 @@
       <c r="E33" t="s">
         <v>12</v>
       </c>
-      <c r="F33" s="5">
-        <v>3</v>
-      </c>
+      <c r="F33" s="3"/>
       <c r="G33" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="H33" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I33" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>88</v>
-      </c>
-      <c r="B34" s="3">
-        <v>9.9</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B34" s="3"/>
       <c r="C34" t="s">
         <v>12</v>
       </c>
@@ -1749,29 +1516,25 @@
       <c r="E34" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="5">
-        <v>3</v>
-      </c>
+      <c r="F34" s="3"/>
       <c r="G34" t="s">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="H34" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I34" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>90</v>
-      </c>
-      <c r="B35" s="3">
-        <v>4.9</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B35" s="3"/>
       <c r="C35" t="s">
         <v>12</v>
       </c>
@@ -1781,63 +1544,56 @@
       <c r="E35" t="s">
         <v>12</v>
       </c>
-      <c r="F35" s="5">
-        <v>1</v>
-      </c>
+      <c r="F35" s="3"/>
       <c r="G35" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="H35" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B36" s="10">
-        <v>480.3</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" s="10">
-        <v>579.47</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F36" s="10">
-        <v>99.17</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="I35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="8">
+        <v>593.37</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="8"/>
+      <c r="G36" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="7"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
+      <c r="A37" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="5">
